--- a/files/availability-list-2026.xlsx
+++ b/files/availability-list-2026.xlsx
@@ -46,8 +46,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,7 +491,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>16249</t>
         </is>
@@ -523,7 +524,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>16220</t>
         </is>
@@ -556,7 +557,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>12550</t>
         </is>
@@ -589,7 +590,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>10735</t>
         </is>
@@ -622,7 +623,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>16423</t>
         </is>
@@ -655,7 +656,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>14389</t>
         </is>
@@ -688,7 +689,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>11635</t>
         </is>
@@ -721,7 +722,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>12538</t>
         </is>
@@ -754,7 +755,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>12235</t>
         </is>
@@ -787,7 +788,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>15656</t>
         </is>
@@ -820,7 +821,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>15657</t>
         </is>
@@ -853,7 +854,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>10736</t>
         </is>
@@ -886,7 +887,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>12226</t>
         </is>
@@ -919,7 +920,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>11916</t>
         </is>
@@ -952,7 +953,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>16237</t>
         </is>
@@ -985,7 +986,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>10737</t>
         </is>
@@ -1018,7 +1019,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>12560</t>
         </is>
@@ -1051,7 +1052,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>10060</t>
         </is>
@@ -1084,7 +1085,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>1158</t>
         </is>
@@ -1117,7 +1118,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>11483</t>
         </is>
@@ -1150,7 +1151,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>12848</t>
         </is>
@@ -1173,11 +1174,6 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1188,7 +1184,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>16435</t>
         </is>
@@ -1226,7 +1222,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>16503</t>
         </is>
@@ -1264,7 +1260,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>16263</t>
         </is>
@@ -1287,11 +1283,6 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1302,7 +1293,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>10945</t>
         </is>
@@ -1340,7 +1331,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>16410</t>
         </is>
@@ -1378,7 +1369,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>13990</t>
         </is>
@@ -1416,7 +1407,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>14388</t>
         </is>
@@ -1454,7 +1445,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>11707</t>
         </is>
@@ -1477,11 +1468,6 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1492,7 +1478,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>1149</t>
         </is>
@@ -1530,7 +1516,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>11830</t>
         </is>
@@ -1568,7 +1554,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>16411</t>
         </is>
@@ -1606,7 +1592,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>11743</t>
         </is>
@@ -1629,11 +1615,6 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -1644,7 +1625,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>15631</t>
         </is>
@@ -1682,7 +1663,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>16412</t>
         </is>
@@ -1720,7 +1701,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>11771</t>
         </is>
@@ -1743,11 +1724,6 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1758,7 +1734,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>16413</t>
         </is>
@@ -1796,7 +1772,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>11769</t>
         </is>
@@ -1829,7 +1805,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>17191</t>
         </is>
@@ -1862,7 +1838,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>16346</t>
         </is>
@@ -1885,11 +1861,6 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -1900,7 +1871,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>11694</t>
         </is>
@@ -1938,7 +1909,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>15638</t>
         </is>
@@ -1976,7 +1947,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>16414</t>
         </is>
@@ -2014,7 +1985,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>16415</t>
         </is>
@@ -2052,7 +2023,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>13993</t>
         </is>
@@ -2090,7 +2061,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>11727</t>
         </is>
@@ -2128,7 +2099,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>15751</t>
         </is>
@@ -2166,7 +2137,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="1" t="inlineStr">
         <is>
           <t>12311</t>
         </is>
@@ -2204,7 +2175,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="1" t="inlineStr">
         <is>
           <t>12310</t>
         </is>
@@ -2242,7 +2213,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="1" t="inlineStr">
         <is>
           <t>13785</t>
         </is>
@@ -2280,7 +2251,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="1" t="inlineStr">
         <is>
           <t>11778</t>
         </is>
@@ -2318,7 +2289,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="1" t="inlineStr">
         <is>
           <t>16416</t>
         </is>
@@ -2356,7 +2327,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="1" t="inlineStr">
         <is>
           <t>16507</t>
         </is>
@@ -2394,7 +2365,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="1" t="inlineStr">
         <is>
           <t>13916</t>
         </is>
@@ -2432,7 +2403,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="1" t="inlineStr">
         <is>
           <t>12846</t>
         </is>
@@ -2470,7 +2441,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="1" t="inlineStr">
         <is>
           <t>11165</t>
         </is>
@@ -2508,7 +2479,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="1" t="inlineStr">
         <is>
           <t>13187</t>
         </is>
@@ -2531,11 +2502,6 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2546,7 +2512,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="1" t="inlineStr">
         <is>
           <t>15752</t>
         </is>
@@ -2569,11 +2535,6 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2584,7 +2545,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="1" t="inlineStr">
         <is>
           <t>17356</t>
         </is>
@@ -2622,7 +2583,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="1" t="inlineStr">
         <is>
           <t>16210</t>
         </is>
@@ -2660,7 +2621,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="1" t="inlineStr">
         <is>
           <t>11833</t>
         </is>
@@ -2683,11 +2644,6 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>150-175cm</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -2698,7 +2654,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="1" t="inlineStr">
         <is>
           <t>17192</t>
         </is>
@@ -2736,7 +2692,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="1" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
@@ -2759,11 +2715,6 @@
       <c r="E65" t="inlineStr">
         <is>
           <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -2774,7 +2725,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="1" t="inlineStr">
         <is>
           <t>16417</t>
         </is>
@@ -2812,7 +2763,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="1" t="inlineStr">
         <is>
           <t>16313</t>
         </is>
@@ -2835,11 +2786,6 @@
       <c r="E67" t="inlineStr">
         <is>
           <t>200-250 cm</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -2850,7 +2796,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="1" t="inlineStr">
         <is>
           <t>16434</t>
         </is>
@@ -2888,7 +2834,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="1" t="inlineStr">
         <is>
           <t>15753</t>
         </is>
@@ -2911,11 +2857,6 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -2926,7 +2867,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="1" t="inlineStr">
         <is>
           <t>12333</t>
         </is>
@@ -2959,7 +2900,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="1" t="inlineStr">
         <is>
           <t>15755</t>
         </is>
@@ -2992,7 +2933,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="1" t="inlineStr">
         <is>
           <t>15757</t>
         </is>
@@ -3025,7 +2966,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="1" t="inlineStr">
         <is>
           <t>15759</t>
         </is>
@@ -3058,7 +2999,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="1" t="inlineStr">
         <is>
           <t>15761</t>
         </is>
@@ -3091,7 +3032,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="1" t="inlineStr">
         <is>
           <t>16333</t>
         </is>
@@ -3129,7 +3070,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="1" t="inlineStr">
         <is>
           <t>11613</t>
         </is>
@@ -3167,7 +3108,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="1" t="inlineStr">
         <is>
           <t>13205</t>
         </is>
@@ -3205,7 +3146,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="1" t="inlineStr">
         <is>
           <t>13192</t>
         </is>
@@ -3243,7 +3184,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="1" t="inlineStr">
         <is>
           <t>10950</t>
         </is>
@@ -3281,7 +3222,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="1" t="inlineStr">
         <is>
           <t>13193</t>
         </is>
@@ -3319,7 +3260,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="1" t="inlineStr">
         <is>
           <t>1175</t>
         </is>
@@ -3357,7 +3298,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="1" t="inlineStr">
         <is>
           <t>12414</t>
         </is>
@@ -3395,7 +3336,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="1" t="inlineStr">
         <is>
           <t>16308</t>
         </is>
@@ -3433,7 +3374,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="1" t="inlineStr">
         <is>
           <t>16438</t>
         </is>
@@ -3471,7 +3412,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="1" t="inlineStr">
         <is>
           <t>17193</t>
         </is>
@@ -3494,11 +3435,6 @@
       <c r="E85" t="inlineStr">
         <is>
           <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -3509,7 +3445,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="1" t="inlineStr">
         <is>
           <t>16510</t>
         </is>
@@ -3547,7 +3483,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="1" t="inlineStr">
         <is>
           <t>16509</t>
         </is>
@@ -3585,7 +3521,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="1" t="inlineStr">
         <is>
           <t>17194</t>
         </is>
@@ -3608,11 +3544,6 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -3623,7 +3554,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="1" t="inlineStr">
         <is>
           <t>15736</t>
         </is>
@@ -3661,7 +3592,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="1" t="inlineStr">
         <is>
           <t>16436</t>
         </is>
@@ -3699,7 +3630,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="1" t="inlineStr">
         <is>
           <t>17195</t>
         </is>
@@ -3732,7 +3663,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="1" t="inlineStr">
         <is>
           <t>17196</t>
         </is>
@@ -3765,7 +3696,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="1" t="inlineStr">
         <is>
           <t>15738</t>
         </is>
@@ -3803,7 +3734,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="1" t="inlineStr">
         <is>
           <t>16439</t>
         </is>
@@ -3841,7 +3772,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="1" t="inlineStr">
         <is>
           <t>12331</t>
         </is>
@@ -3879,7 +3810,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="1" t="inlineStr">
         <is>
           <t>17197</t>
         </is>
@@ -3917,7 +3848,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="1" t="inlineStr">
         <is>
           <t>12299</t>
         </is>
@@ -3940,11 +3871,6 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -3955,7 +3881,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="1" t="inlineStr">
         <is>
           <t>16437</t>
         </is>
@@ -3993,7 +3919,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="1" t="inlineStr">
         <is>
           <t>16257</t>
         </is>
@@ -4016,11 +3942,6 @@
       <c r="E99" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -4031,7 +3952,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="1" t="inlineStr">
         <is>
           <t>13918</t>
         </is>
@@ -4069,7 +3990,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="1" t="inlineStr">
         <is>
           <t>16443</t>
         </is>
@@ -4107,7 +4028,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="1" t="inlineStr">
         <is>
           <t>16442</t>
         </is>
@@ -4145,7 +4066,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="1" t="inlineStr">
         <is>
           <t>16441</t>
         </is>
@@ -4183,7 +4104,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="1" t="inlineStr">
         <is>
           <t>16282</t>
         </is>
@@ -4221,7 +4142,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="1" t="inlineStr">
         <is>
           <t>17199</t>
         </is>
@@ -4259,7 +4180,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="1" t="inlineStr">
         <is>
           <t>11834</t>
         </is>
@@ -4282,11 +4203,6 @@
       <c r="E106" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -4297,7 +4213,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="1" t="inlineStr">
         <is>
           <t>15633</t>
         </is>
@@ -4335,7 +4251,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="1" t="inlineStr">
         <is>
           <t>17046</t>
         </is>
@@ -4373,7 +4289,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="1" t="inlineStr">
         <is>
           <t>17045</t>
         </is>
@@ -4411,7 +4327,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="1" t="inlineStr">
         <is>
           <t>16401</t>
         </is>
@@ -4449,7 +4365,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="1" t="inlineStr">
         <is>
           <t>17359</t>
         </is>
@@ -4472,11 +4388,6 @@
       <c r="E111" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -4487,7 +4398,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="1" t="inlineStr">
         <is>
           <t>16446</t>
         </is>
@@ -4525,7 +4436,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="1" t="inlineStr">
         <is>
           <t>16445</t>
         </is>
@@ -4563,7 +4474,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="1" t="inlineStr">
         <is>
           <t>16444</t>
         </is>
@@ -4601,7 +4512,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="1" t="inlineStr">
         <is>
           <t>11603</t>
         </is>
@@ -4639,7 +4550,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="1" t="inlineStr">
         <is>
           <t>16448</t>
         </is>
@@ -4677,7 +4588,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="1" t="inlineStr">
         <is>
           <t>16447</t>
         </is>
@@ -4715,7 +4626,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="1" t="inlineStr">
         <is>
           <t>11837</t>
         </is>
@@ -4753,7 +4664,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="1" t="inlineStr">
         <is>
           <t>16409</t>
         </is>
@@ -4776,11 +4687,6 @@
       <c r="E119" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -4791,7 +4697,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="1" t="inlineStr">
         <is>
           <t>11602</t>
         </is>
@@ -4829,7 +4735,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="1" t="inlineStr">
         <is>
           <t>16449</t>
         </is>
@@ -4867,7 +4773,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="1" t="inlineStr">
         <is>
           <t>16217</t>
         </is>
@@ -4905,7 +4811,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="1" t="inlineStr">
         <is>
           <t>16512</t>
         </is>
@@ -4943,7 +4849,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="1" t="inlineStr">
         <is>
           <t>16511</t>
         </is>
@@ -4981,7 +4887,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="1" t="inlineStr">
         <is>
           <t>16336</t>
         </is>
@@ -5019,7 +4925,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="1" t="inlineStr">
         <is>
           <t>15636</t>
         </is>
@@ -5057,7 +4963,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="1" t="inlineStr">
         <is>
           <t>1070</t>
         </is>
@@ -5095,7 +5001,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="1" t="inlineStr">
         <is>
           <t>10086</t>
         </is>
@@ -5133,7 +5039,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="1" t="inlineStr">
         <is>
           <t>13923</t>
         </is>
@@ -5171,7 +5077,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="1" t="inlineStr">
         <is>
           <t>12849</t>
         </is>
@@ -5209,7 +5115,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="1" t="inlineStr">
         <is>
           <t>15632</t>
         </is>
@@ -5247,7 +5153,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="1" t="inlineStr">
         <is>
           <t>16516</t>
         </is>
@@ -5285,7 +5191,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="1" t="inlineStr">
         <is>
           <t>16515</t>
         </is>
@@ -5323,7 +5229,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="1" t="inlineStr">
         <is>
           <t>16514</t>
         </is>
@@ -5361,7 +5267,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="1" t="inlineStr">
         <is>
           <t>13924</t>
         </is>
@@ -5399,7 +5305,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="1" t="inlineStr">
         <is>
           <t>13925</t>
         </is>
@@ -5437,7 +5343,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="1" t="inlineStr">
         <is>
           <t>11693</t>
         </is>
@@ -5475,7 +5381,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="1" t="inlineStr">
         <is>
           <t>16307</t>
         </is>
@@ -5513,7 +5419,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="1" t="inlineStr">
         <is>
           <t>16266</t>
         </is>
@@ -5536,11 +5442,6 @@
       <c r="E139" t="inlineStr">
         <is>
           <t>60-90cm</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -5551,7 +5452,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="1" t="inlineStr">
         <is>
           <t>11059</t>
         </is>
@@ -5584,7 +5485,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="1" t="inlineStr">
         <is>
           <t>11773</t>
         </is>
@@ -5617,7 +5518,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="1" t="inlineStr">
         <is>
           <t>15762</t>
         </is>
@@ -5650,7 +5551,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="1" t="inlineStr">
         <is>
           <t>11715</t>
         </is>
@@ -5683,7 +5584,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="1" t="inlineStr">
         <is>
           <t>16295</t>
         </is>
@@ -5706,11 +5607,6 @@
       <c r="E144" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -5721,7 +5617,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="1" t="inlineStr">
         <is>
           <t>16517</t>
         </is>
@@ -5759,7 +5655,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="1" t="inlineStr">
         <is>
           <t>14005</t>
         </is>
@@ -5797,7 +5693,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="1" t="inlineStr">
         <is>
           <t>16518</t>
         </is>
@@ -5835,7 +5731,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="1" t="inlineStr">
         <is>
           <t>11706</t>
         </is>
@@ -5873,7 +5769,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="1" t="inlineStr">
         <is>
           <t>16285</t>
         </is>
@@ -5911,7 +5807,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="1" t="inlineStr">
         <is>
           <t>14415</t>
         </is>
@@ -5949,7 +5845,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="1" t="inlineStr">
         <is>
           <t>11496</t>
         </is>
@@ -5972,11 +5868,6 @@
       <c r="E151" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -5987,7 +5878,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="1" t="inlineStr">
         <is>
           <t>14414</t>
         </is>
@@ -6025,7 +5916,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="1" t="inlineStr">
         <is>
           <t>16451</t>
         </is>
@@ -6063,7 +5954,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="1" t="inlineStr">
         <is>
           <t>11532</t>
         </is>
@@ -6101,7 +5992,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="1" t="inlineStr">
         <is>
           <t>16450</t>
         </is>
@@ -6139,7 +6030,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="1" t="inlineStr">
         <is>
           <t>14007</t>
         </is>
@@ -6177,7 +6068,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="1" t="inlineStr">
         <is>
           <t>15763</t>
         </is>
@@ -6200,11 +6091,6 @@
       <c r="E157" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -6215,7 +6101,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="1" t="inlineStr">
         <is>
           <t>11494</t>
         </is>
@@ -6253,7 +6139,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="1" t="inlineStr">
         <is>
           <t>16453</t>
         </is>
@@ -6291,7 +6177,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="1" t="inlineStr">
         <is>
           <t>16452</t>
         </is>
@@ -6329,7 +6215,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="1" t="inlineStr">
         <is>
           <t>12519</t>
         </is>
@@ -6362,7 +6248,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="1" t="inlineStr">
         <is>
           <t>15764</t>
         </is>
@@ -6385,11 +6271,6 @@
       <c r="E162" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -6400,7 +6281,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="1" t="inlineStr">
         <is>
           <t>11084</t>
         </is>
@@ -6438,7 +6319,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="1" t="inlineStr">
         <is>
           <t>11840</t>
         </is>
@@ -6461,11 +6342,6 @@
       <c r="E164" t="inlineStr">
         <is>
           <t>140-160cm</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -6476,7 +6352,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
+      <c r="A165" s="1" t="inlineStr">
         <is>
           <t>11065</t>
         </is>
@@ -6499,11 +6375,6 @@
       <c r="E165" t="inlineStr">
         <is>
           <t>200-225cm</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -6514,7 +6385,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="A166" s="1" t="inlineStr">
         <is>
           <t>15655</t>
         </is>
@@ -6552,7 +6423,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
+      <c r="A167" s="1" t="inlineStr">
         <is>
           <t>1073</t>
         </is>
@@ -6585,7 +6456,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="A168" s="1" t="inlineStr">
         <is>
           <t>15765</t>
         </is>
@@ -6618,7 +6489,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
+      <c r="A169" s="1" t="inlineStr">
         <is>
           <t>10413</t>
         </is>
@@ -6651,7 +6522,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="1" t="inlineStr">
         <is>
           <t>16228</t>
         </is>
@@ -6684,7 +6555,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="1" t="inlineStr">
         <is>
           <t>17348</t>
         </is>
@@ -6717,7 +6588,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="1" t="inlineStr">
         <is>
           <t>16272</t>
         </is>
@@ -6755,7 +6626,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
+      <c r="A173" s="1" t="inlineStr">
         <is>
           <t>10815</t>
         </is>
@@ -6788,7 +6659,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="1" t="inlineStr">
         <is>
           <t>15654</t>
         </is>
@@ -6826,7 +6697,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="1" t="inlineStr">
         <is>
           <t>17054</t>
         </is>
@@ -6859,7 +6730,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="1" t="inlineStr">
         <is>
           <t>11523</t>
         </is>
@@ -6897,7 +6768,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="1" t="inlineStr">
         <is>
           <t>13927</t>
         </is>
@@ -6935,7 +6806,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="1" t="inlineStr">
         <is>
           <t>16520</t>
         </is>
@@ -6973,7 +6844,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
+      <c r="A179" s="1" t="inlineStr">
         <is>
           <t>16519</t>
         </is>
@@ -7011,7 +6882,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
+      <c r="A180" s="1" t="inlineStr">
         <is>
           <t>11668</t>
         </is>
@@ -7044,7 +6915,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
+      <c r="A181" s="1" t="inlineStr">
         <is>
           <t>11667</t>
         </is>
@@ -7077,7 +6948,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="A182" s="1" t="inlineStr">
         <is>
           <t>10891</t>
         </is>
@@ -7110,7 +6981,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="1" t="inlineStr">
         <is>
           <t>16407</t>
         </is>
@@ -7143,7 +7014,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="1" t="inlineStr">
         <is>
           <t>11690</t>
         </is>
@@ -7181,7 +7052,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="1" t="inlineStr">
         <is>
           <t>12583</t>
         </is>
@@ -7219,7 +7090,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="1" t="inlineStr">
         <is>
           <t>10092</t>
         </is>
@@ -7252,7 +7123,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="1" t="inlineStr">
         <is>
           <t>11238</t>
         </is>
@@ -7290,7 +7161,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
+      <c r="A188" s="1" t="inlineStr">
         <is>
           <t>16523</t>
         </is>
@@ -7328,7 +7199,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
+      <c r="A189" s="1" t="inlineStr">
         <is>
           <t>16522</t>
         </is>
@@ -7366,7 +7237,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
+      <c r="A190" s="1" t="inlineStr">
         <is>
           <t>16521</t>
         </is>
@@ -7404,7 +7275,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="1" t="inlineStr">
         <is>
           <t>1229</t>
         </is>
@@ -7442,7 +7313,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="1" t="inlineStr">
         <is>
           <t>14351</t>
         </is>
@@ -7475,7 +7346,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
+      <c r="A193" s="1" t="inlineStr">
         <is>
           <t>11717</t>
         </is>
@@ -7508,7 +7379,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="1" t="inlineStr">
         <is>
           <t>17232</t>
         </is>
@@ -7546,7 +7417,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="A195" s="1" t="inlineStr">
         <is>
           <t>16455</t>
         </is>
@@ -7584,7 +7455,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="1" t="inlineStr">
         <is>
           <t>16454</t>
         </is>
@@ -7622,7 +7493,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
+      <c r="A197" s="1" t="inlineStr">
         <is>
           <t>16219</t>
         </is>
@@ -7660,7 +7531,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
+      <c r="A198" s="1" t="inlineStr">
         <is>
           <t>16258</t>
         </is>
@@ -7683,11 +7554,6 @@
       <c r="E198" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -7698,7 +7564,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
+      <c r="A199" s="1" t="inlineStr">
         <is>
           <t>10809</t>
         </is>
@@ -7731,7 +7597,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="A200" s="1" t="inlineStr">
         <is>
           <t>16972</t>
         </is>
@@ -7769,7 +7635,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="A201" s="1" t="inlineStr">
         <is>
           <t>16302</t>
         </is>
@@ -7807,7 +7673,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
+      <c r="A202" s="1" t="inlineStr">
         <is>
           <t>10785</t>
         </is>
@@ -7830,11 +7696,6 @@
       <c r="E202" t="inlineStr">
         <is>
           <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -7845,7 +7706,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
+      <c r="A203" s="1" t="inlineStr">
         <is>
           <t>16971</t>
         </is>
@@ -7883,7 +7744,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
+      <c r="A204" s="1" t="inlineStr">
         <is>
           <t>16527</t>
         </is>
@@ -7921,7 +7782,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
+      <c r="A205" s="1" t="inlineStr">
         <is>
           <t>16526</t>
         </is>
@@ -7959,7 +7820,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
+      <c r="A206" s="1" t="inlineStr">
         <is>
           <t>16525</t>
         </is>
@@ -7997,7 +7858,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
+      <c r="A207" s="1" t="inlineStr">
         <is>
           <t>16524</t>
         </is>
@@ -8035,7 +7896,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
+      <c r="A208" s="1" t="inlineStr">
         <is>
           <t>11810</t>
         </is>
@@ -8073,7 +7934,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
+      <c r="A209" s="1" t="inlineStr">
         <is>
           <t>16262</t>
         </is>
@@ -8111,7 +7972,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
+      <c r="A210" s="1" t="inlineStr">
         <is>
           <t>13946</t>
         </is>
@@ -8149,7 +8010,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
+      <c r="A211" s="1" t="inlineStr">
         <is>
           <t>13182</t>
         </is>
@@ -8182,7 +8043,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
+      <c r="A212" s="1" t="inlineStr">
         <is>
           <t>16338</t>
         </is>
@@ -8220,7 +8081,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
+      <c r="A213" s="1" t="inlineStr">
         <is>
           <t>16339</t>
         </is>
@@ -8258,7 +8119,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
+      <c r="A214" s="1" t="inlineStr">
         <is>
           <t>11562</t>
         </is>
@@ -8291,7 +8152,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
+      <c r="A215" s="1" t="inlineStr">
         <is>
           <t>11750</t>
         </is>
@@ -8329,7 +8190,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
+      <c r="A216" s="1" t="inlineStr">
         <is>
           <t>16106</t>
         </is>
@@ -8352,11 +8213,6 @@
       <c r="E216" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -8367,7 +8223,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
+      <c r="A217" s="1" t="inlineStr">
         <is>
           <t>1124</t>
         </is>
@@ -8390,11 +8246,6 @@
       <c r="E217" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -8405,7 +8256,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="A218" s="1" t="inlineStr">
         <is>
           <t>10808</t>
         </is>
@@ -8428,11 +8279,6 @@
       <c r="E218" t="inlineStr">
         <is>
           <t>150-175cm</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -8443,7 +8289,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
+      <c r="A219" s="1" t="inlineStr">
         <is>
           <t>17200</t>
         </is>
@@ -8481,7 +8327,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
+      <c r="A220" s="1" t="inlineStr">
         <is>
           <t>11841</t>
         </is>
@@ -8504,11 +8350,6 @@
       <c r="E220" t="inlineStr">
         <is>
           <t>250-300cm</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -8519,7 +8360,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="A221" s="1" t="inlineStr">
         <is>
           <t>16457</t>
         </is>
@@ -8557,7 +8398,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="A222" s="1" t="inlineStr">
         <is>
           <t>16456</t>
         </is>
@@ -8595,7 +8436,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
+      <c r="A223" s="1" t="inlineStr">
         <is>
           <t>12335</t>
         </is>
@@ -8633,7 +8474,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
+      <c r="A224" s="1" t="inlineStr">
         <is>
           <t>13045</t>
         </is>
@@ -8671,7 +8512,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
+      <c r="A225" s="1" t="inlineStr">
         <is>
           <t>1260</t>
         </is>
@@ -8694,11 +8535,6 @@
       <c r="E225" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -8709,7 +8545,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
+      <c r="A226" s="1" t="inlineStr">
         <is>
           <t>13054</t>
         </is>
@@ -8747,7 +8583,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
+      <c r="A227" s="1" t="inlineStr">
         <is>
           <t>16296</t>
         </is>
@@ -8785,7 +8621,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
+      <c r="A228" s="1" t="inlineStr">
         <is>
           <t>11746</t>
         </is>
@@ -8818,7 +8654,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
+      <c r="A229" s="1" t="inlineStr">
         <is>
           <t>16975</t>
         </is>
@@ -8856,7 +8692,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
+      <c r="A230" s="1" t="inlineStr">
         <is>
           <t>16974</t>
         </is>
@@ -8894,7 +8730,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
+      <c r="A231" s="1" t="inlineStr">
         <is>
           <t>16973</t>
         </is>
@@ -8932,7 +8768,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
+      <c r="A232" s="1" t="inlineStr">
         <is>
           <t>14455</t>
         </is>
@@ -8970,7 +8806,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
+      <c r="A233" s="1" t="inlineStr">
         <is>
           <t>17201</t>
         </is>
@@ -8993,11 +8829,6 @@
       <c r="E233" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -9008,7 +8839,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
+      <c r="A234" s="1" t="inlineStr">
         <is>
           <t>12374</t>
         </is>
@@ -9046,7 +8877,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
+      <c r="A235" s="1" t="inlineStr">
         <is>
           <t>16277</t>
         </is>
@@ -9079,7 +8910,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="A236" s="1" t="inlineStr">
         <is>
           <t>15768</t>
         </is>
@@ -9102,11 +8933,6 @@
       <c r="E236" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -9117,7 +8943,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
+      <c r="A237" s="1" t="inlineStr">
         <is>
           <t>11843</t>
         </is>
@@ -9140,11 +8966,6 @@
       <c r="E237" t="inlineStr">
         <is>
           <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -9155,7 +8976,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
+      <c r="A238" s="1" t="inlineStr">
         <is>
           <t>15628</t>
         </is>
@@ -9193,7 +9014,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
+      <c r="A239" s="1" t="inlineStr">
         <is>
           <t>16459</t>
         </is>
@@ -9231,7 +9052,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
+      <c r="A240" s="1" t="inlineStr">
         <is>
           <t>16458</t>
         </is>
@@ -9269,7 +9090,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="A241" s="1" t="inlineStr">
         <is>
           <t>11871</t>
         </is>
@@ -9292,11 +9113,6 @@
       <c r="E241" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -9307,7 +9123,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
+      <c r="A242" s="1" t="inlineStr">
         <is>
           <t>13046</t>
         </is>
@@ -9330,11 +9146,6 @@
       <c r="E242" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -9345,7 +9156,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
+      <c r="A243" s="1" t="inlineStr">
         <is>
           <t>1265</t>
         </is>
@@ -9368,11 +9179,6 @@
       <c r="E243" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -9383,7 +9189,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="A244" s="1" t="inlineStr">
         <is>
           <t>16977</t>
         </is>
@@ -9421,7 +9227,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="A245" s="1" t="inlineStr">
         <is>
           <t>15769</t>
         </is>
@@ -9459,7 +9265,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
+      <c r="A246" s="1" t="inlineStr">
         <is>
           <t>11626</t>
         </is>
@@ -9482,11 +9288,6 @@
       <c r="E246" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -9497,7 +9298,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
+      <c r="A247" s="1" t="inlineStr">
         <is>
           <t>16424</t>
         </is>
@@ -9520,11 +9321,6 @@
       <c r="E247" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -9535,7 +9331,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
+      <c r="A248" s="1" t="inlineStr">
         <is>
           <t>14425</t>
         </is>
@@ -9573,7 +9369,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
+      <c r="A249" s="1" t="inlineStr">
         <is>
           <t>14008</t>
         </is>
@@ -9611,7 +9407,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
+      <c r="A250" s="1" t="inlineStr">
         <is>
           <t>15770</t>
         </is>
@@ -9649,7 +9445,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
+      <c r="A251" s="1" t="inlineStr">
         <is>
           <t>1013</t>
         </is>
@@ -9672,11 +9468,6 @@
       <c r="E251" t="inlineStr">
         <is>
           <t>200-250 cm</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -9687,7 +9478,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
+      <c r="A252" s="1" t="inlineStr">
         <is>
           <t>12376</t>
         </is>
@@ -9725,7 +9516,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
+      <c r="A253" s="1" t="inlineStr">
         <is>
           <t>16980</t>
         </is>
@@ -9763,7 +9554,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
+      <c r="A254" s="1" t="inlineStr">
         <is>
           <t>14011</t>
         </is>
@@ -9801,7 +9592,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
+      <c r="A255" s="1" t="inlineStr">
         <is>
           <t>15726</t>
         </is>
@@ -9839,7 +9630,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
+      <c r="A256" s="1" t="inlineStr">
         <is>
           <t>11446</t>
         </is>
@@ -9862,11 +9653,6 @@
       <c r="E256" t="inlineStr">
         <is>
           <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -9877,7 +9663,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
+      <c r="A257" s="1" t="inlineStr">
         <is>
           <t>17203</t>
         </is>
@@ -9900,11 +9686,6 @@
       <c r="E257" t="inlineStr">
         <is>
           <t>30-40cm</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -9915,7 +9696,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="A258" s="1" t="inlineStr">
         <is>
           <t>14426</t>
         </is>
@@ -9953,7 +9734,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
+      <c r="A259" s="1" t="inlineStr">
         <is>
           <t>16315</t>
         </is>
@@ -9991,7 +9772,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
+      <c r="A260" s="1" t="inlineStr">
         <is>
           <t>1278</t>
         </is>
@@ -10029,7 +9810,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
+      <c r="A261" s="1" t="inlineStr">
         <is>
           <t>16982</t>
         </is>
@@ -10067,7 +9848,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
+      <c r="A262" s="1" t="inlineStr">
         <is>
           <t>16981</t>
         </is>
@@ -10105,7 +9886,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
+      <c r="A263" s="1" t="inlineStr">
         <is>
           <t>15771</t>
         </is>
@@ -10143,7 +9924,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
+      <c r="A264" s="1" t="inlineStr">
         <is>
           <t>16983</t>
         </is>
@@ -10181,7 +9962,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
+      <c r="A265" s="1" t="inlineStr">
         <is>
           <t>17202</t>
         </is>
@@ -10204,11 +9985,6 @@
       <c r="E265" t="inlineStr">
         <is>
           <t>50-75cm</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -10219,7 +9995,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
+      <c r="A266" s="1" t="inlineStr">
         <is>
           <t>11757</t>
         </is>
@@ -10257,7 +10033,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
+      <c r="A267" s="1" t="inlineStr">
         <is>
           <t>11761</t>
         </is>
@@ -10295,7 +10071,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
+      <c r="A268" s="1" t="inlineStr">
         <is>
           <t>17340</t>
         </is>
@@ -10328,7 +10104,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
+      <c r="A269" s="1" t="inlineStr">
         <is>
           <t>12241</t>
         </is>
@@ -10366,7 +10142,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
+      <c r="A270" s="1" t="inlineStr">
         <is>
           <t>10104</t>
         </is>
@@ -10404,7 +10180,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
+      <c r="A271" s="1" t="inlineStr">
         <is>
           <t>12231</t>
         </is>
@@ -10442,7 +10218,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
+      <c r="A272" s="1" t="inlineStr">
         <is>
           <t>12457</t>
         </is>
@@ -10480,7 +10256,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
+      <c r="A273" s="1" t="inlineStr">
         <is>
           <t>14009</t>
         </is>
@@ -10518,7 +10294,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
+      <c r="A274" s="1" t="inlineStr">
         <is>
           <t>11064</t>
         </is>
@@ -10551,7 +10327,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
+      <c r="A275" s="1" t="inlineStr">
         <is>
           <t>12850</t>
         </is>
@@ -10584,7 +10360,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
+      <c r="A276" s="1" t="inlineStr">
         <is>
           <t>16225</t>
         </is>
@@ -10617,7 +10393,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
+      <c r="A277" s="1" t="inlineStr">
         <is>
           <t>16224</t>
         </is>
@@ -10650,7 +10426,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
+      <c r="A278" s="1" t="inlineStr">
         <is>
           <t>16265</t>
         </is>
@@ -10688,7 +10464,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
+      <c r="A279" s="1" t="inlineStr">
         <is>
           <t>16985</t>
         </is>
@@ -10726,7 +10502,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr">
+      <c r="A280" s="1" t="inlineStr">
         <is>
           <t>10885</t>
         </is>
@@ -10749,11 +10525,6 @@
       <c r="E280" t="inlineStr">
         <is>
           <t>150-200 cm</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -10764,7 +10535,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
+      <c r="A281" s="1" t="inlineStr">
         <is>
           <t>13952</t>
         </is>
@@ -10802,7 +10573,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr">
+      <c r="A282" s="1" t="inlineStr">
         <is>
           <t>10884</t>
         </is>
@@ -10825,11 +10596,6 @@
       <c r="E282" t="inlineStr">
         <is>
           <t>200- 250cm</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -10840,7 +10606,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
+      <c r="A283" s="1" t="inlineStr">
         <is>
           <t>13953</t>
         </is>
@@ -10878,7 +10644,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
+      <c r="A284" s="1" t="inlineStr">
         <is>
           <t>16462</t>
         </is>
@@ -10916,7 +10682,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
+      <c r="A285" s="1" t="inlineStr">
         <is>
           <t>16461</t>
         </is>
@@ -10954,7 +10720,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
+      <c r="A286" s="1" t="inlineStr">
         <is>
           <t>16986</t>
         </is>
@@ -10992,7 +10758,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
+      <c r="A287" s="1" t="inlineStr">
         <is>
           <t>12586</t>
         </is>
@@ -11015,11 +10781,6 @@
       <c r="E287" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -11030,7 +10791,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr">
+      <c r="A288" s="1" t="inlineStr">
         <is>
           <t>1128</t>
         </is>
@@ -11053,11 +10814,6 @@
       <c r="E288" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -11068,7 +10824,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr">
+      <c r="A289" s="1" t="inlineStr">
         <is>
           <t>17233</t>
         </is>
@@ -11106,7 +10862,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
+      <c r="A290" s="1" t="inlineStr">
         <is>
           <t>15774</t>
         </is>
@@ -11144,7 +10900,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr">
+      <c r="A291" s="1" t="inlineStr">
         <is>
           <t>15772</t>
         </is>
@@ -11182,7 +10938,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr">
+      <c r="A292" s="1" t="inlineStr">
         <is>
           <t>10742</t>
         </is>
@@ -11215,7 +10971,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr">
+      <c r="A293" s="1" t="inlineStr">
         <is>
           <t>11816</t>
         </is>
@@ -11248,7 +11004,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr">
+      <c r="A294" s="1" t="inlineStr">
         <is>
           <t>12346</t>
         </is>
@@ -11286,7 +11042,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr">
+      <c r="A295" s="1" t="inlineStr">
         <is>
           <t>10112</t>
         </is>
@@ -11319,7 +11075,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr">
+      <c r="A296" s="1" t="inlineStr">
         <is>
           <t>11672</t>
         </is>
@@ -11357,7 +11113,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr">
+      <c r="A297" s="1" t="inlineStr">
         <is>
           <t>10591</t>
         </is>
@@ -11395,7 +11151,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr">
+      <c r="A298" s="1" t="inlineStr">
         <is>
           <t>17205</t>
         </is>
@@ -11418,11 +11174,6 @@
       <c r="E298" t="inlineStr">
         <is>
           <t>40-60cm</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -11433,7 +11184,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
+      <c r="A299" s="1" t="inlineStr">
         <is>
           <t>16107</t>
         </is>
@@ -11471,7 +11222,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
+      <c r="A300" s="1" t="inlineStr">
         <is>
           <t>17188</t>
         </is>
@@ -11504,7 +11255,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
+      <c r="A301" s="1" t="inlineStr">
         <is>
           <t>15658</t>
         </is>
@@ -11542,7 +11293,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
+      <c r="A302" s="1" t="inlineStr">
         <is>
           <t>10888</t>
         </is>
@@ -11575,7 +11326,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr">
+      <c r="A303" s="1" t="inlineStr">
         <is>
           <t>15776</t>
         </is>
@@ -11608,7 +11359,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr">
+      <c r="A304" s="1" t="inlineStr">
         <is>
           <t>1293</t>
         </is>
@@ -11641,7 +11392,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr">
+      <c r="A305" s="1" t="inlineStr">
         <is>
           <t>10116</t>
         </is>
@@ -11674,7 +11425,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr">
+      <c r="A306" s="1" t="inlineStr">
         <is>
           <t>16317</t>
         </is>
@@ -11707,7 +11458,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr">
+      <c r="A307" s="1" t="inlineStr">
         <is>
           <t>17235</t>
         </is>
@@ -11745,7 +11496,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr">
+      <c r="A308" s="1" t="inlineStr">
         <is>
           <t>11697</t>
         </is>
@@ -11778,7 +11529,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr">
+      <c r="A309" s="1" t="inlineStr">
         <is>
           <t>16212</t>
         </is>
@@ -11811,7 +11562,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr">
+      <c r="A310" s="1" t="inlineStr">
         <is>
           <t>12459</t>
         </is>
@@ -11844,7 +11595,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr">
+      <c r="A311" s="1" t="inlineStr">
         <is>
           <t>12454</t>
         </is>
@@ -11877,7 +11628,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr">
+      <c r="A312" s="1" t="inlineStr">
         <is>
           <t>15777</t>
         </is>
@@ -11910,7 +11661,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr">
+      <c r="A313" s="1" t="inlineStr">
         <is>
           <t>13229</t>
         </is>
@@ -11943,7 +11694,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="inlineStr">
+      <c r="A314" s="1" t="inlineStr">
         <is>
           <t>16064</t>
         </is>
@@ -11976,7 +11727,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr">
+      <c r="A315" s="1" t="inlineStr">
         <is>
           <t>12855</t>
         </is>
@@ -12009,7 +11760,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr">
+      <c r="A316" s="1" t="inlineStr">
         <is>
           <t>15778</t>
         </is>
@@ -12042,7 +11793,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr">
+      <c r="A317" s="1" t="inlineStr">
         <is>
           <t>16406</t>
         </is>
@@ -12075,7 +11826,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr">
+      <c r="A318" s="1" t="inlineStr">
         <is>
           <t>16291</t>
         </is>
@@ -12098,11 +11849,6 @@
       <c r="E318" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -12113,7 +11859,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr">
+      <c r="A319" s="1" t="inlineStr">
         <is>
           <t>10831</t>
         </is>
@@ -12146,7 +11892,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr">
+      <c r="A320" s="1" t="inlineStr">
         <is>
           <t>16283</t>
         </is>
@@ -12179,7 +11925,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr">
+      <c r="A321" s="1" t="inlineStr">
         <is>
           <t>17355</t>
         </is>
@@ -12217,7 +11963,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr">
+      <c r="A322" s="1" t="inlineStr">
         <is>
           <t>12339</t>
         </is>
@@ -12250,7 +11996,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr">
+      <c r="A323" s="1" t="inlineStr">
         <is>
           <t>17240</t>
         </is>
@@ -12283,7 +12029,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
+      <c r="A324" s="1" t="inlineStr">
         <is>
           <t>11762</t>
         </is>
@@ -12316,7 +12062,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr">
+      <c r="A325" s="1" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
@@ -12349,7 +12095,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="inlineStr">
+      <c r="A326" s="1" t="inlineStr">
         <is>
           <t>11597</t>
         </is>
@@ -12387,7 +12133,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="inlineStr">
+      <c r="A327" s="1" t="inlineStr">
         <is>
           <t>11695</t>
         </is>
@@ -12425,7 +12171,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="inlineStr">
+      <c r="A328" s="1" t="inlineStr">
         <is>
           <t>13047</t>
         </is>
@@ -12448,11 +12194,6 @@
       <c r="E328" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -12463,7 +12204,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="inlineStr">
+      <c r="A329" s="1" t="inlineStr">
         <is>
           <t>11844</t>
         </is>
@@ -12486,11 +12227,6 @@
       <c r="E329" t="inlineStr">
         <is>
           <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -12501,7 +12237,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr">
+      <c r="A330" s="1" t="inlineStr">
         <is>
           <t>12588</t>
         </is>
@@ -12524,11 +12260,6 @@
       <c r="E330" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -12539,7 +12270,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="inlineStr">
+      <c r="A331" s="1" t="inlineStr">
         <is>
           <t>14453</t>
         </is>
@@ -12577,7 +12308,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="inlineStr">
+      <c r="A332" s="1" t="inlineStr">
         <is>
           <t>15781</t>
         </is>
@@ -12600,11 +12331,6 @@
       <c r="E332" t="inlineStr">
         <is>
           <t>150-175cm</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -12615,7 +12341,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr">
+      <c r="A333" s="1" t="inlineStr">
         <is>
           <t>16987</t>
         </is>
@@ -12653,7 +12379,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr">
+      <c r="A334" s="1" t="inlineStr">
         <is>
           <t>15782</t>
         </is>
@@ -12691,7 +12417,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr">
+      <c r="A335" s="1" t="inlineStr">
         <is>
           <t>15649</t>
         </is>
@@ -12729,7 +12455,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr">
+      <c r="A336" s="1" t="inlineStr">
         <is>
           <t>1315</t>
         </is>
@@ -12767,7 +12493,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr">
+      <c r="A337" s="1" t="inlineStr">
         <is>
           <t>12381</t>
         </is>
@@ -12790,11 +12516,6 @@
       <c r="E337" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -12805,7 +12526,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr">
+      <c r="A338" s="1" t="inlineStr">
         <is>
           <t>13191</t>
         </is>
@@ -12838,7 +12559,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr">
+      <c r="A339" s="1" t="inlineStr">
         <is>
           <t>12856</t>
         </is>
@@ -12861,11 +12582,6 @@
       <c r="E339" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -12876,7 +12592,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr">
+      <c r="A340" s="1" t="inlineStr">
         <is>
           <t>15650</t>
         </is>
@@ -12914,7 +12630,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr">
+      <c r="A341" s="1" t="inlineStr">
         <is>
           <t>16463</t>
         </is>
@@ -12952,7 +12668,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="inlineStr">
+      <c r="A342" s="1" t="inlineStr">
         <is>
           <t>12182</t>
         </is>
@@ -12990,7 +12706,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr">
+      <c r="A343" s="1" t="inlineStr">
         <is>
           <t>11627</t>
         </is>
@@ -13023,7 +12739,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
+      <c r="A344" s="1" t="inlineStr">
         <is>
           <t>16244</t>
         </is>
@@ -13056,7 +12772,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr">
+      <c r="A345" s="1" t="inlineStr">
         <is>
           <t>12533</t>
         </is>
@@ -13089,7 +12805,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
+      <c r="A346" s="1" t="inlineStr">
         <is>
           <t>16152</t>
         </is>
@@ -13127,7 +12843,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr">
+      <c r="A347" s="1" t="inlineStr">
         <is>
           <t>11648</t>
         </is>
@@ -13150,11 +12866,6 @@
       <c r="E347" t="inlineStr">
         <is>
           <t>200-250 cm</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G347" t="n">
@@ -13165,7 +12876,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr">
+      <c r="A348" s="1" t="inlineStr">
         <is>
           <t>15640</t>
         </is>
@@ -13203,7 +12914,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
+      <c r="A349" s="1" t="inlineStr">
         <is>
           <t>16206</t>
         </is>
@@ -13241,7 +12952,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
+      <c r="A350" s="1" t="inlineStr">
         <is>
           <t>13264</t>
         </is>
@@ -13274,7 +12985,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
+      <c r="A351" s="1" t="inlineStr">
         <is>
           <t>11146</t>
         </is>
@@ -13307,7 +13018,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr">
+      <c r="A352" s="1" t="inlineStr">
         <is>
           <t>16230</t>
         </is>
@@ -13340,7 +13051,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
+      <c r="A353" s="1" t="inlineStr">
         <is>
           <t>16066</t>
         </is>
@@ -13373,7 +13084,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="inlineStr">
+      <c r="A354" s="1" t="inlineStr">
         <is>
           <t>11150</t>
         </is>
@@ -13406,7 +13117,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr">
+      <c r="A355" s="1" t="inlineStr">
         <is>
           <t>11148</t>
         </is>
@@ -13439,7 +13150,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr">
+      <c r="A356" s="1" t="inlineStr">
         <is>
           <t>11845</t>
         </is>
@@ -13472,7 +13183,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr">
+      <c r="A357" s="1" t="inlineStr">
         <is>
           <t>1331</t>
         </is>
@@ -13505,7 +13216,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr">
+      <c r="A358" s="1" t="inlineStr">
         <is>
           <t>12050</t>
         </is>
@@ -13538,7 +13249,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
+      <c r="A359" s="1" t="inlineStr">
         <is>
           <t>11580</t>
         </is>
@@ -13576,7 +13287,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr">
+      <c r="A360" s="1" t="inlineStr">
         <is>
           <t>10769</t>
         </is>
@@ -13599,11 +13310,6 @@
       <c r="E360" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -13614,7 +13320,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr">
+      <c r="A361" s="1" t="inlineStr">
         <is>
           <t>16402</t>
         </is>
@@ -13637,11 +13343,6 @@
       <c r="E361" t="inlineStr">
         <is>
           <t>150-175cm</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G361" t="n">
@@ -13652,7 +13353,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr">
+      <c r="A362" s="1" t="inlineStr">
         <is>
           <t>14441</t>
         </is>
@@ -13690,7 +13391,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
+      <c r="A363" s="1" t="inlineStr">
         <is>
           <t>16067</t>
         </is>
@@ -13728,7 +13429,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
+      <c r="A364" s="1" t="inlineStr">
         <is>
           <t>11188</t>
         </is>
@@ -13766,7 +13467,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr">
+      <c r="A365" s="1" t="inlineStr">
         <is>
           <t>10771</t>
         </is>
@@ -13789,11 +13490,6 @@
       <c r="E365" t="inlineStr">
         <is>
           <t>150-175cm</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G365" t="n">
@@ -13804,7 +13500,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr">
+      <c r="A366" s="1" t="inlineStr">
         <is>
           <t>14440</t>
         </is>
@@ -13842,7 +13538,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr">
+      <c r="A367" s="1" t="inlineStr">
         <is>
           <t>10772</t>
         </is>
@@ -13865,11 +13561,6 @@
       <c r="E367" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -13880,7 +13571,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr">
+      <c r="A368" s="1" t="inlineStr">
         <is>
           <t>14002</t>
         </is>
@@ -13903,11 +13594,6 @@
       <c r="E368" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G368" t="n">
@@ -13918,7 +13604,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="inlineStr">
+      <c r="A369" s="1" t="inlineStr">
         <is>
           <t>11797</t>
         </is>
@@ -13951,7 +13637,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr">
+      <c r="A370" s="1" t="inlineStr">
         <is>
           <t>1110</t>
         </is>
@@ -13989,7 +13675,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
+      <c r="A371" s="1" t="inlineStr">
         <is>
           <t>11088</t>
         </is>
@@ -14012,11 +13698,6 @@
       <c r="E371" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G371" t="n">
@@ -14027,7 +13708,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr">
+      <c r="A372" s="1" t="inlineStr">
         <is>
           <t>16201</t>
         </is>
@@ -14065,7 +13746,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr">
+      <c r="A373" s="1" t="inlineStr">
         <is>
           <t>16205</t>
         </is>
@@ -14103,7 +13784,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr">
+      <c r="A374" s="1" t="inlineStr">
         <is>
           <t>16304</t>
         </is>
@@ -14126,11 +13807,6 @@
       <c r="E374" t="inlineStr">
         <is>
           <t>60-90cm</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G374" t="n">
@@ -14141,7 +13817,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="inlineStr">
+      <c r="A375" s="1" t="inlineStr">
         <is>
           <t>12334</t>
         </is>
@@ -14174,7 +13850,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
+      <c r="A376" s="1" t="inlineStr">
         <is>
           <t>15785</t>
         </is>
@@ -14207,7 +13883,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
+      <c r="A377" s="1" t="inlineStr">
         <is>
           <t>12503</t>
         </is>
@@ -14240,7 +13916,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="inlineStr">
+      <c r="A378" s="1" t="inlineStr">
         <is>
           <t>16418</t>
         </is>
@@ -14268,7 +13944,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="inlineStr">
+      <c r="A379" s="1" t="inlineStr">
         <is>
           <t>17049</t>
         </is>
@@ -14306,7 +13982,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" t="inlineStr">
+      <c r="A380" s="1" t="inlineStr">
         <is>
           <t>17048</t>
         </is>
@@ -14344,6 +14020,11 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
           <t>Gift Card</t>
@@ -14369,7 +14050,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="inlineStr">
+      <c r="A382" s="1" t="inlineStr">
         <is>
           <t>16189</t>
         </is>
@@ -14392,11 +14073,6 @@
       <c r="E382" t="inlineStr">
         <is>
           <t>125-150 cm</t>
-        </is>
-      </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G382" t="n">
@@ -14407,7 +14083,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="inlineStr">
+      <c r="A383" s="1" t="inlineStr">
         <is>
           <t>10859</t>
         </is>
@@ -14430,11 +14106,6 @@
       <c r="E383" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G383" t="n">
@@ -14445,7 +14116,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr">
+      <c r="A384" s="1" t="inlineStr">
         <is>
           <t>10861</t>
         </is>
@@ -14483,7 +14154,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
+      <c r="A385" s="1" t="inlineStr">
         <is>
           <t>13276</t>
         </is>
@@ -14521,7 +14192,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr">
+      <c r="A386" s="1" t="inlineStr">
         <is>
           <t>10857</t>
         </is>
@@ -14544,11 +14215,6 @@
       <c r="E386" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G386" t="n">
@@ -14559,7 +14225,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr">
+      <c r="A387" s="1" t="inlineStr">
         <is>
           <t>11775</t>
         </is>
@@ -14592,7 +14258,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="inlineStr">
+      <c r="A388" s="1" t="inlineStr">
         <is>
           <t>16188</t>
         </is>
@@ -14625,7 +14291,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
+      <c r="A389" s="1" t="inlineStr">
         <is>
           <t>11623</t>
         </is>
@@ -14658,7 +14324,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
+      <c r="A390" s="1" t="inlineStr">
         <is>
           <t>1351</t>
         </is>
@@ -14691,7 +14357,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr">
+      <c r="A391" s="1" t="inlineStr">
         <is>
           <t>12383</t>
         </is>
@@ -14724,7 +14390,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="inlineStr">
+      <c r="A392" s="1" t="inlineStr">
         <is>
           <t>12350</t>
         </is>
@@ -14762,7 +14428,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr">
+      <c r="A393" s="1" t="inlineStr">
         <is>
           <t>17206</t>
         </is>
@@ -14800,7 +14466,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr">
+      <c r="A394" s="1" t="inlineStr">
         <is>
           <t>11846</t>
         </is>
@@ -14823,11 +14489,6 @@
       <c r="E394" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G394" t="n">
@@ -14838,7 +14499,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr">
+      <c r="A395" s="1" t="inlineStr">
         <is>
           <t>12341</t>
         </is>
@@ -14861,11 +14522,6 @@
       <c r="E395" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G395" t="n">
@@ -14876,7 +14532,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr">
+      <c r="A396" s="1" t="inlineStr">
         <is>
           <t>15786</t>
         </is>
@@ -14914,7 +14570,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="inlineStr">
+      <c r="A397" s="1" t="inlineStr">
         <is>
           <t>13266</t>
         </is>
@@ -14947,7 +14603,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr">
+      <c r="A398" s="1" t="inlineStr">
         <is>
           <t>16231</t>
         </is>
@@ -14970,11 +14626,6 @@
       <c r="E398" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G398" t="n">
@@ -14985,7 +14636,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
+      <c r="A399" s="1" t="inlineStr">
         <is>
           <t>15668</t>
         </is>
@@ -15023,7 +14674,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr">
+      <c r="A400" s="1" t="inlineStr">
         <is>
           <t>16218</t>
         </is>
@@ -15061,7 +14712,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr">
+      <c r="A401" s="1" t="inlineStr">
         <is>
           <t>13190</t>
         </is>
@@ -15094,7 +14745,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr">
+      <c r="A402" s="1" t="inlineStr">
         <is>
           <t>17207</t>
         </is>
@@ -15132,7 +14783,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr">
+      <c r="A403" s="1" t="inlineStr">
         <is>
           <t>10841</t>
         </is>
@@ -15155,11 +14806,6 @@
       <c r="E403" t="inlineStr">
         <is>
           <t>60-90cm</t>
-        </is>
-      </c>
-      <c r="F403" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G403" t="n">
@@ -15170,7 +14816,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr">
+      <c r="A404" s="1" t="inlineStr">
         <is>
           <t>15788</t>
         </is>
@@ -15203,7 +14849,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="inlineStr">
+      <c r="A405" s="1" t="inlineStr">
         <is>
           <t>10843</t>
         </is>
@@ -15236,7 +14882,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="inlineStr">
+      <c r="A406" s="1" t="inlineStr">
         <is>
           <t>15789</t>
         </is>
@@ -15274,7 +14920,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="inlineStr">
+      <c r="A407" s="1" t="inlineStr">
         <is>
           <t>14427</t>
         </is>
@@ -15312,7 +14958,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr">
+      <c r="A408" s="1" t="inlineStr">
         <is>
           <t>16465</t>
         </is>
@@ -15350,7 +14996,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr">
+      <c r="A409" s="1" t="inlineStr">
         <is>
           <t>16464</t>
         </is>
@@ -15388,7 +15034,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr">
+      <c r="A410" s="1" t="inlineStr">
         <is>
           <t>15790</t>
         </is>
@@ -15411,11 +15057,6 @@
       <c r="E410" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G410" t="n">
@@ -15426,7 +15067,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr">
+      <c r="A411" s="1" t="inlineStr">
         <is>
           <t>11137</t>
         </is>
@@ -15449,11 +15090,6 @@
       <c r="E411" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G411" t="n">
@@ -15464,7 +15100,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr">
+      <c r="A412" s="1" t="inlineStr">
         <is>
           <t>16466</t>
         </is>
@@ -15502,7 +15138,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr">
+      <c r="A413" s="1" t="inlineStr">
         <is>
           <t>17187</t>
         </is>
@@ -15535,7 +15171,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr">
+      <c r="A414" s="1" t="inlineStr">
         <is>
           <t>15791</t>
         </is>
@@ -15568,7 +15204,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
+      <c r="A415" s="1" t="inlineStr">
         <is>
           <t>12384</t>
         </is>
@@ -15601,7 +15237,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
+      <c r="A416" s="1" t="inlineStr">
         <is>
           <t>11089</t>
         </is>
@@ -15639,7 +15275,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr">
+      <c r="A417" s="1" t="inlineStr">
         <is>
           <t>15792</t>
         </is>
@@ -15662,11 +15298,6 @@
       <c r="E417" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G417" t="n">
@@ -15677,7 +15308,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr">
+      <c r="A418" s="1" t="inlineStr">
         <is>
           <t>16467</t>
         </is>
@@ -15715,7 +15346,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr">
+      <c r="A419" s="1" t="inlineStr">
         <is>
           <t>1371</t>
         </is>
@@ -15738,11 +15369,6 @@
       <c r="E419" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G419" t="n">
@@ -15753,7 +15379,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
+      <c r="A420" s="1" t="inlineStr">
         <is>
           <t>16988</t>
         </is>
@@ -15791,7 +15417,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr">
+      <c r="A421" s="1" t="inlineStr">
         <is>
           <t>17208</t>
         </is>
@@ -15814,11 +15440,6 @@
       <c r="E421" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G421" t="n">
@@ -15829,7 +15450,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="inlineStr">
+      <c r="A422" s="1" t="inlineStr">
         <is>
           <t>16214</t>
         </is>
@@ -15862,7 +15483,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="inlineStr">
+      <c r="A423" s="1" t="inlineStr">
         <is>
           <t>12541</t>
         </is>
@@ -15895,7 +15516,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="inlineStr">
+      <c r="A424" s="1" t="inlineStr">
         <is>
           <t>10734</t>
         </is>
@@ -15928,7 +15549,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="inlineStr">
+      <c r="A425" s="1" t="inlineStr">
         <is>
           <t>16216</t>
         </is>
@@ -15961,7 +15582,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="inlineStr">
+      <c r="A426" s="1" t="inlineStr">
         <is>
           <t>11045</t>
         </is>
@@ -15994,7 +15615,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="inlineStr">
+      <c r="A427" s="1" t="inlineStr">
         <is>
           <t>11043</t>
         </is>
@@ -16027,7 +15648,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="inlineStr">
+      <c r="A428" s="1" t="inlineStr">
         <is>
           <t>13954</t>
         </is>
@@ -16065,7 +15686,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="inlineStr">
+      <c r="A429" s="1" t="inlineStr">
         <is>
           <t>13955</t>
         </is>
@@ -16103,7 +15724,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="inlineStr">
+      <c r="A430" s="1" t="inlineStr">
         <is>
           <t>16989</t>
         </is>
@@ -16141,7 +15762,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="inlineStr">
+      <c r="A431" s="1" t="inlineStr">
         <is>
           <t>16990</t>
         </is>
@@ -16179,7 +15800,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="inlineStr">
+      <c r="A432" s="1" t="inlineStr">
         <is>
           <t>12507</t>
         </is>
@@ -16212,7 +15833,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="inlineStr">
+      <c r="A433" s="1" t="inlineStr">
         <is>
           <t>11166</t>
         </is>
@@ -16235,11 +15856,6 @@
       <c r="E433" t="inlineStr">
         <is>
           <t>150-175cm</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G433" t="n">
@@ -16250,7 +15866,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" t="inlineStr">
+      <c r="A434" s="1" t="inlineStr">
         <is>
           <t>16992</t>
         </is>
@@ -16288,7 +15904,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" t="inlineStr">
+      <c r="A435" s="1" t="inlineStr">
         <is>
           <t>16991</t>
         </is>
@@ -16326,7 +15942,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="inlineStr">
+      <c r="A436" s="1" t="inlineStr">
         <is>
           <t>16306</t>
         </is>
@@ -16364,7 +15980,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="inlineStr">
+      <c r="A437" s="1" t="inlineStr">
         <is>
           <t>16259</t>
         </is>
@@ -16402,7 +16018,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="inlineStr">
+      <c r="A438" s="1" t="inlineStr">
         <is>
           <t>16469</t>
         </is>
@@ -16440,7 +16056,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr">
+      <c r="A439" s="1" t="inlineStr">
         <is>
           <t>16468</t>
         </is>
@@ -16478,7 +16094,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" t="inlineStr">
+      <c r="A440" s="1" t="inlineStr">
         <is>
           <t>11541</t>
         </is>
@@ -16516,7 +16132,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="inlineStr">
+      <c r="A441" s="1" t="inlineStr">
         <is>
           <t>16993</t>
         </is>
@@ -16554,7 +16170,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" t="inlineStr">
+      <c r="A442" s="1" t="inlineStr">
         <is>
           <t>16234</t>
         </is>
@@ -16592,7 +16208,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="inlineStr">
+      <c r="A443" s="1" t="inlineStr">
         <is>
           <t>11096</t>
         </is>
@@ -16615,11 +16231,6 @@
       <c r="E443" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F443" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G443" t="n">
@@ -16630,7 +16241,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="inlineStr">
+      <c r="A444" s="1" t="inlineStr">
         <is>
           <t>11095</t>
         </is>
@@ -16653,11 +16264,6 @@
       <c r="E444" t="inlineStr">
         <is>
           <t>200-250 cm</t>
-        </is>
-      </c>
-      <c r="F444" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G444" t="n">
@@ -16668,7 +16274,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr">
+      <c r="A445" s="1" t="inlineStr">
         <is>
           <t>15685</t>
         </is>
@@ -16706,7 +16312,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="inlineStr">
+      <c r="A446" s="1" t="inlineStr">
         <is>
           <t>14000</t>
         </is>
@@ -16744,7 +16350,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="inlineStr">
+      <c r="A447" s="1" t="inlineStr">
         <is>
           <t>12385</t>
         </is>
@@ -16767,11 +16373,6 @@
       <c r="E447" t="inlineStr">
         <is>
           <t>150-175cm</t>
-        </is>
-      </c>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G447" t="n">
@@ -16782,7 +16383,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="inlineStr">
+      <c r="A448" s="1" t="inlineStr">
         <is>
           <t>15794</t>
         </is>
@@ -16820,7 +16421,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="inlineStr">
+      <c r="A449" s="1" t="inlineStr">
         <is>
           <t>16073</t>
         </is>
@@ -16848,7 +16449,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="inlineStr">
+      <c r="A450" s="1" t="inlineStr">
         <is>
           <t>13957</t>
         </is>
@@ -16886,7 +16487,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="inlineStr">
+      <c r="A451" s="1" t="inlineStr">
         <is>
           <t>16995</t>
         </is>
@@ -16924,7 +16525,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="inlineStr">
+      <c r="A452" s="1" t="inlineStr">
         <is>
           <t>16994</t>
         </is>
@@ -16962,7 +16563,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr">
+      <c r="A453" s="1" t="inlineStr">
         <is>
           <t>17349</t>
         </is>
@@ -17000,7 +16601,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="inlineStr">
+      <c r="A454" s="1" t="inlineStr">
         <is>
           <t>16071</t>
         </is>
@@ -17023,11 +16624,6 @@
       <c r="E454" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F454" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G454" t="n">
@@ -17038,7 +16634,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr">
+      <c r="A455" s="1" t="inlineStr">
         <is>
           <t>10476</t>
         </is>
@@ -17071,7 +16667,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="inlineStr">
+      <c r="A456" s="1" t="inlineStr">
         <is>
           <t>15797</t>
         </is>
@@ -17104,7 +16700,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="inlineStr">
+      <c r="A457" s="1" t="inlineStr">
         <is>
           <t>10702</t>
         </is>
@@ -17137,7 +16733,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="inlineStr">
+      <c r="A458" s="1" t="inlineStr">
         <is>
           <t>10140</t>
         </is>
@@ -17170,7 +16766,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="inlineStr">
+      <c r="A459" s="1" t="inlineStr">
         <is>
           <t>10833</t>
         </is>
@@ -17193,11 +16789,6 @@
       <c r="E459" t="inlineStr">
         <is>
           <t>150-175cm</t>
-        </is>
-      </c>
-      <c r="F459" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G459" t="n">
@@ -17208,7 +16799,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="inlineStr">
+      <c r="A460" s="1" t="inlineStr">
         <is>
           <t>17239</t>
         </is>
@@ -17241,7 +16832,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="inlineStr">
+      <c r="A461" s="1" t="inlineStr">
         <is>
           <t>1043</t>
         </is>
@@ -17274,7 +16865,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="inlineStr">
+      <c r="A462" s="1" t="inlineStr">
         <is>
           <t>11651</t>
         </is>
@@ -17307,7 +16898,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="inlineStr">
+      <c r="A463" s="1" t="inlineStr">
         <is>
           <t>10142</t>
         </is>
@@ -17340,7 +16931,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="inlineStr">
+      <c r="A464" s="1" t="inlineStr">
         <is>
           <t>13040</t>
         </is>
@@ -17363,11 +16954,6 @@
       <c r="E464" t="inlineStr">
         <is>
           <t>120-140cm</t>
-        </is>
-      </c>
-      <c r="F464" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G464" t="n">
@@ -17378,7 +16964,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="inlineStr">
+      <c r="A465" s="1" t="inlineStr">
         <is>
           <t>14390</t>
         </is>
@@ -17416,7 +17002,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="inlineStr">
+      <c r="A466" s="1" t="inlineStr">
         <is>
           <t>15725</t>
         </is>
@@ -17454,7 +17040,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="inlineStr">
+      <c r="A467" s="1" t="inlineStr">
         <is>
           <t>13958</t>
         </is>
@@ -17492,7 +17078,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="inlineStr">
+      <c r="A468" s="1" t="inlineStr">
         <is>
           <t>16470</t>
         </is>
@@ -17530,7 +17116,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="inlineStr">
+      <c r="A469" s="1" t="inlineStr">
         <is>
           <t>16996</t>
         </is>
@@ -17568,7 +17154,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="inlineStr">
+      <c r="A470" s="1" t="inlineStr">
         <is>
           <t>13041</t>
         </is>
@@ -17591,11 +17177,6 @@
       <c r="E470" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F470" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G470" t="n">
@@ -17606,7 +17187,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="inlineStr">
+      <c r="A471" s="1" t="inlineStr">
         <is>
           <t>10163</t>
         </is>
@@ -17629,11 +17210,6 @@
       <c r="E471" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F471" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G471" t="n">
@@ -17644,7 +17220,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="inlineStr">
+      <c r="A472" s="1" t="inlineStr">
         <is>
           <t>16471</t>
         </is>
@@ -17682,7 +17258,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="inlineStr">
+      <c r="A473" s="1" t="inlineStr">
         <is>
           <t>16472</t>
         </is>
@@ -17720,7 +17296,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="inlineStr">
+      <c r="A474" s="1" t="inlineStr">
         <is>
           <t>11689</t>
         </is>
@@ -17758,7 +17334,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="inlineStr">
+      <c r="A475" s="1" t="inlineStr">
         <is>
           <t>11600</t>
         </is>
@@ -17796,7 +17372,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="inlineStr">
+      <c r="A476" s="1" t="inlineStr">
         <is>
           <t>16997</t>
         </is>
@@ -17834,7 +17410,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="inlineStr">
+      <c r="A477" s="1" t="inlineStr">
         <is>
           <t>16474</t>
         </is>
@@ -17872,7 +17448,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="inlineStr">
+      <c r="A478" s="1" t="inlineStr">
         <is>
           <t>16473</t>
         </is>
@@ -17910,7 +17486,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="inlineStr">
+      <c r="A479" s="1" t="inlineStr">
         <is>
           <t>16475</t>
         </is>
@@ -17948,7 +17524,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="inlineStr">
+      <c r="A480" s="1" t="inlineStr">
         <is>
           <t>12307</t>
         </is>
@@ -17981,7 +17557,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="inlineStr">
+      <c r="A481" s="1" t="inlineStr">
         <is>
           <t>11794</t>
         </is>
@@ -18014,7 +17590,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="inlineStr">
+      <c r="A482" s="1" t="inlineStr">
         <is>
           <t>1398</t>
         </is>
@@ -18037,11 +17613,6 @@
       <c r="E482" t="inlineStr">
         <is>
           <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F482" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G482" t="n">
@@ -18052,7 +17623,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="inlineStr">
+      <c r="A483" s="1" t="inlineStr">
         <is>
           <t>17001</t>
         </is>
@@ -18090,7 +17661,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="inlineStr">
+      <c r="A484" s="1" t="inlineStr">
         <is>
           <t>12355</t>
         </is>
@@ -18113,11 +17684,6 @@
       <c r="E484" t="inlineStr">
         <is>
           <t>200-225cm</t>
-        </is>
-      </c>
-      <c r="F484" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G484" t="n">
@@ -18128,7 +17694,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="inlineStr">
+      <c r="A485" s="1" t="inlineStr">
         <is>
           <t>14391</t>
         </is>
@@ -18166,7 +17732,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="inlineStr">
+      <c r="A486" s="1" t="inlineStr">
         <is>
           <t>11533</t>
         </is>
@@ -18204,7 +17770,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="inlineStr">
+      <c r="A487" s="1" t="inlineStr">
         <is>
           <t>13200</t>
         </is>
@@ -18242,7 +17808,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" t="inlineStr">
+      <c r="A488" s="1" t="inlineStr">
         <is>
           <t>11822</t>
         </is>
@@ -18280,7 +17846,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" t="inlineStr">
+      <c r="A489" s="1" t="inlineStr">
         <is>
           <t>13042</t>
         </is>
@@ -18318,7 +17884,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="inlineStr">
+      <c r="A490" s="1" t="inlineStr">
         <is>
           <t>11847</t>
         </is>
@@ -18356,7 +17922,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" t="inlineStr">
+      <c r="A491" s="1" t="inlineStr">
         <is>
           <t>11256</t>
         </is>
@@ -18379,11 +17945,6 @@
       <c r="E491" t="inlineStr">
         <is>
           <t>200-225cm</t>
-        </is>
-      </c>
-      <c r="F491" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G491" t="n">
@@ -18394,7 +17955,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="inlineStr">
+      <c r="A492" s="1" t="inlineStr">
         <is>
           <t>11691</t>
         </is>
@@ -18432,7 +17993,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="inlineStr">
+      <c r="A493" s="1" t="inlineStr">
         <is>
           <t>12387</t>
         </is>
@@ -18465,7 +18026,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="inlineStr">
+      <c r="A494" s="1" t="inlineStr">
         <is>
           <t>16030</t>
         </is>
@@ -18488,11 +18049,6 @@
       <c r="E494" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F494" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G494" t="n">
@@ -18503,7 +18059,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="inlineStr">
+      <c r="A495" s="1" t="inlineStr">
         <is>
           <t>16278</t>
         </is>
@@ -18541,7 +18097,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" t="inlineStr">
+      <c r="A496" s="1" t="inlineStr">
         <is>
           <t>16158</t>
         </is>
@@ -18579,7 +18135,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" t="inlineStr">
+      <c r="A497" s="1" t="inlineStr">
         <is>
           <t>16128</t>
         </is>
@@ -18612,7 +18168,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="inlineStr">
+      <c r="A498" s="1" t="inlineStr">
         <is>
           <t>16159</t>
         </is>
@@ -18650,7 +18206,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="inlineStr">
+      <c r="A499" s="1" t="inlineStr">
         <is>
           <t>16130</t>
         </is>
@@ -18683,7 +18239,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="inlineStr">
+      <c r="A500" s="1" t="inlineStr">
         <is>
           <t>16161</t>
         </is>
@@ -18721,7 +18277,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="inlineStr">
+      <c r="A501" s="1" t="inlineStr">
         <is>
           <t>10147</t>
         </is>
@@ -18744,11 +18300,6 @@
       <c r="E501" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F501" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G501" t="n">
@@ -18759,7 +18310,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="inlineStr">
+      <c r="A502" s="1" t="inlineStr">
         <is>
           <t>16041</t>
         </is>
@@ -18792,7 +18343,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="inlineStr">
+      <c r="A503" s="1" t="inlineStr">
         <is>
           <t>16042</t>
         </is>
@@ -18815,11 +18366,6 @@
       <c r="E503" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F503" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G503" t="n">
@@ -18830,7 +18376,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" t="inlineStr">
+      <c r="A504" s="1" t="inlineStr">
         <is>
           <t>11724</t>
         </is>
@@ -18853,11 +18399,6 @@
       <c r="E504" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F504" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G504" t="n">
@@ -18868,7 +18409,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" t="inlineStr">
+      <c r="A505" s="1" t="inlineStr">
         <is>
           <t>16045</t>
         </is>
@@ -18891,11 +18432,6 @@
       <c r="E505" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F505" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G505" t="n">
@@ -18906,7 +18442,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="inlineStr">
+      <c r="A506" s="1" t="inlineStr">
         <is>
           <t>16164</t>
         </is>
@@ -18944,7 +18480,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" t="inlineStr">
+      <c r="A507" s="1" t="inlineStr">
         <is>
           <t>16091</t>
         </is>
@@ -18982,7 +18518,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="inlineStr">
+      <c r="A508" s="1" t="inlineStr">
         <is>
           <t>10150</t>
         </is>
@@ -19005,11 +18541,6 @@
       <c r="E508" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F508" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G508" t="n">
@@ -19020,7 +18551,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" t="inlineStr">
+      <c r="A509" s="1" t="inlineStr">
         <is>
           <t>16167</t>
         </is>
@@ -19058,7 +18589,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" t="inlineStr">
+      <c r="A510" s="1" t="inlineStr">
         <is>
           <t>16168</t>
         </is>
@@ -19081,11 +18612,6 @@
       <c r="E510" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F510" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G510" t="n">
@@ -19096,7 +18622,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" t="inlineStr">
+      <c r="A511" s="1" t="inlineStr">
         <is>
           <t>16181</t>
         </is>
@@ -19119,11 +18645,6 @@
       <c r="E511" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F511" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G511" t="n">
@@ -19134,7 +18655,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="inlineStr">
+      <c r="A512" s="1" t="inlineStr">
         <is>
           <t>16169</t>
         </is>
@@ -19157,11 +18678,6 @@
       <c r="E512" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F512" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G512" t="n">
@@ -19172,7 +18688,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" t="inlineStr">
+      <c r="A513" s="1" t="inlineStr">
         <is>
           <t>11731</t>
         </is>
@@ -19195,11 +18711,6 @@
       <c r="E513" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F513" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G513" t="n">
@@ -19210,7 +18721,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" t="inlineStr">
+      <c r="A514" s="1" t="inlineStr">
         <is>
           <t>16132</t>
         </is>
@@ -19243,7 +18754,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" t="inlineStr">
+      <c r="A515" s="1" t="inlineStr">
         <is>
           <t>16134</t>
         </is>
@@ -19266,11 +18777,6 @@
       <c r="E515" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F515" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G515" t="n">
@@ -19281,7 +18787,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" t="inlineStr">
+      <c r="A516" s="1" t="inlineStr">
         <is>
           <t>16165</t>
         </is>
@@ -19319,7 +18825,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" t="inlineStr">
+      <c r="A517" s="1" t="inlineStr">
         <is>
           <t>11347</t>
         </is>
@@ -19352,7 +18858,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" t="inlineStr">
+      <c r="A518" s="1" t="inlineStr">
         <is>
           <t>10928</t>
         </is>
@@ -19375,11 +18881,6 @@
       <c r="E518" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F518" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G518" t="n">
@@ -19390,7 +18891,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" t="inlineStr">
+      <c r="A519" s="1" t="inlineStr">
         <is>
           <t>1407</t>
         </is>
@@ -19428,7 +18929,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" t="inlineStr">
+      <c r="A520" s="1" t="inlineStr">
         <is>
           <t>16999</t>
         </is>
@@ -19466,7 +18967,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" t="inlineStr">
+      <c r="A521" s="1" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
@@ -19504,7 +19005,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" t="inlineStr">
+      <c r="A522" s="1" t="inlineStr">
         <is>
           <t>13959</t>
         </is>
@@ -19542,7 +19043,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" t="inlineStr">
+      <c r="A523" s="1" t="inlineStr">
         <is>
           <t>17000</t>
         </is>
@@ -19580,7 +19081,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" t="inlineStr">
+      <c r="A524" s="1" t="inlineStr">
         <is>
           <t>1081</t>
         </is>
@@ -19613,7 +19114,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" t="inlineStr">
+      <c r="A525" s="1" t="inlineStr">
         <is>
           <t>16477</t>
         </is>
@@ -19651,7 +19152,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" t="inlineStr">
+      <c r="A526" s="1" t="inlineStr">
         <is>
           <t>11594</t>
         </is>
@@ -19689,7 +19190,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" t="inlineStr">
+      <c r="A527" s="1" t="inlineStr">
         <is>
           <t>17003</t>
         </is>
@@ -19727,7 +19228,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" t="inlineStr">
+      <c r="A528" s="1" t="inlineStr">
         <is>
           <t>17002</t>
         </is>
@@ -19765,7 +19266,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" t="inlineStr">
+      <c r="A529" s="1" t="inlineStr">
         <is>
           <t>16476</t>
         </is>
@@ -19803,7 +19304,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" t="inlineStr">
+      <c r="A530" s="1" t="inlineStr">
         <is>
           <t>10848</t>
         </is>
@@ -19841,7 +19342,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" t="inlineStr">
+      <c r="A531" s="1" t="inlineStr">
         <is>
           <t>15798</t>
         </is>
@@ -19874,7 +19375,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" t="inlineStr">
+      <c r="A532" s="1" t="inlineStr">
         <is>
           <t>12356</t>
         </is>
@@ -19907,7 +19408,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" t="inlineStr">
+      <c r="A533" s="1" t="inlineStr">
         <is>
           <t>16075</t>
         </is>
@@ -19940,7 +19441,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" t="inlineStr">
+      <c r="A534" s="1" t="inlineStr">
         <is>
           <t>15799</t>
         </is>
@@ -19973,7 +19474,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" t="inlineStr">
+      <c r="A535" s="1" t="inlineStr">
         <is>
           <t>16254</t>
         </is>
@@ -20006,7 +19507,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" t="inlineStr">
+      <c r="A536" s="1" t="inlineStr">
         <is>
           <t>12342</t>
         </is>
@@ -20044,7 +19545,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" t="inlineStr">
+      <c r="A537" s="1" t="inlineStr">
         <is>
           <t>12389</t>
         </is>
@@ -20067,11 +19568,6 @@
       <c r="E537" t="inlineStr">
         <is>
           <t>140-160cm</t>
-        </is>
-      </c>
-      <c r="F537" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G537" t="n">
@@ -20082,7 +19578,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" t="inlineStr">
+      <c r="A538" s="1" t="inlineStr">
         <is>
           <t>1111</t>
         </is>
@@ -20105,11 +19601,6 @@
       <c r="E538" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F538" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G538" t="n">
@@ -20120,7 +19611,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" t="inlineStr">
+      <c r="A539" s="1" t="inlineStr">
         <is>
           <t>11075</t>
         </is>
@@ -20143,11 +19634,6 @@
       <c r="E539" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F539" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G539" t="n">
@@ -20158,7 +19644,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" t="inlineStr">
+      <c r="A540" s="1" t="inlineStr">
         <is>
           <t>14443</t>
         </is>
@@ -20196,7 +19682,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" t="inlineStr">
+      <c r="A541" s="1" t="inlineStr">
         <is>
           <t>11076</t>
         </is>
@@ -20234,7 +19720,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" t="inlineStr">
+      <c r="A542" s="1" t="inlineStr">
         <is>
           <t>14418</t>
         </is>
@@ -20272,7 +19758,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" t="inlineStr">
+      <c r="A543" s="1" t="inlineStr">
         <is>
           <t>16343</t>
         </is>
@@ -20305,7 +19791,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" t="inlineStr">
+      <c r="A544" s="1" t="inlineStr">
         <is>
           <t>16300</t>
         </is>
@@ -20338,7 +19824,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" t="inlineStr">
+      <c r="A545" s="1" t="inlineStr">
         <is>
           <t>11764</t>
         </is>
@@ -20371,7 +19857,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" t="inlineStr">
+      <c r="A546" s="1" t="inlineStr">
         <is>
           <t>16240</t>
         </is>
@@ -20409,7 +19895,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" t="inlineStr">
+      <c r="A547" s="1" t="inlineStr">
         <is>
           <t>17004</t>
         </is>
@@ -20447,7 +19933,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" t="inlineStr">
+      <c r="A548" s="1" t="inlineStr">
         <is>
           <t>17005</t>
         </is>
@@ -20485,7 +19971,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" t="inlineStr">
+      <c r="A549" s="1" t="inlineStr">
         <is>
           <t>15800</t>
         </is>
@@ -20523,7 +20009,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" t="inlineStr">
+      <c r="A550" s="1" t="inlineStr">
         <is>
           <t>15680</t>
         </is>
@@ -20561,7 +20047,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" t="inlineStr">
+      <c r="A551" s="1" t="inlineStr">
         <is>
           <t>1084</t>
         </is>
@@ -20584,11 +20070,6 @@
       <c r="E551" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F551" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G551" t="n">
@@ -20599,7 +20080,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" t="inlineStr">
+      <c r="A552" s="1" t="inlineStr">
         <is>
           <t>16236</t>
         </is>
@@ -20632,7 +20113,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" t="inlineStr">
+      <c r="A553" s="1" t="inlineStr">
         <is>
           <t>16422</t>
         </is>
@@ -20665,7 +20146,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" t="inlineStr">
+      <c r="A554" s="1" t="inlineStr">
         <is>
           <t>15659</t>
         </is>
@@ -20698,7 +20179,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" t="inlineStr">
+      <c r="A555" s="1" t="inlineStr">
         <is>
           <t>10855</t>
         </is>
@@ -20731,7 +20212,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" t="inlineStr">
+      <c r="A556" s="1" t="inlineStr">
         <is>
           <t>15705</t>
         </is>
@@ -20764,7 +20245,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" t="inlineStr">
+      <c r="A557" s="1" t="inlineStr">
         <is>
           <t>16213</t>
         </is>
@@ -20797,7 +20278,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" t="inlineStr">
+      <c r="A558" s="1" t="inlineStr">
         <is>
           <t>16247</t>
         </is>
@@ -20830,7 +20311,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" t="inlineStr">
+      <c r="A559" s="1" t="inlineStr">
         <is>
           <t>16312</t>
         </is>
@@ -20863,7 +20344,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" t="inlineStr">
+      <c r="A560" s="1" t="inlineStr">
         <is>
           <t>11805</t>
         </is>
@@ -20896,7 +20377,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" t="inlineStr">
+      <c r="A561" s="1" t="inlineStr">
         <is>
           <t>1430</t>
         </is>
@@ -20929,7 +20410,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" t="inlineStr">
+      <c r="A562" s="1" t="inlineStr">
         <is>
           <t>12516</t>
         </is>
@@ -20962,7 +20443,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" t="inlineStr">
+      <c r="A563" s="1" t="inlineStr">
         <is>
           <t>11625</t>
         </is>
@@ -20995,7 +20476,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" t="inlineStr">
+      <c r="A564" s="1" t="inlineStr">
         <is>
           <t>12564</t>
         </is>
@@ -21028,7 +20509,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" t="inlineStr">
+      <c r="A565" s="1" t="inlineStr">
         <is>
           <t>12565</t>
         </is>
@@ -21061,7 +20542,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" t="inlineStr">
+      <c r="A566" s="1" t="inlineStr">
         <is>
           <t>17241</t>
         </is>
@@ -21094,7 +20575,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" t="inlineStr">
+      <c r="A567" s="1" t="inlineStr">
         <is>
           <t>15801</t>
         </is>
@@ -21127,7 +20608,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" t="inlineStr">
+      <c r="A568" s="1" t="inlineStr">
         <is>
           <t>11857</t>
         </is>
@@ -21160,7 +20641,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" t="inlineStr">
+      <c r="A569" s="1" t="inlineStr">
         <is>
           <t>17354</t>
         </is>
@@ -21198,7 +20679,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" t="inlineStr">
+      <c r="A570" s="1" t="inlineStr">
         <is>
           <t>15625</t>
         </is>
@@ -21236,7 +20717,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" t="inlineStr">
+      <c r="A571" s="1" t="inlineStr">
         <is>
           <t>10750</t>
         </is>
@@ -21259,11 +20740,6 @@
       <c r="E571" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F571" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G571" t="n">
@@ -21274,7 +20750,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" t="inlineStr">
+      <c r="A572" s="1" t="inlineStr">
         <is>
           <t>15802</t>
         </is>
@@ -21307,7 +20783,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" t="inlineStr">
+      <c r="A573" s="1" t="inlineStr">
         <is>
           <t>16326</t>
         </is>
@@ -21340,7 +20816,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" t="inlineStr">
+      <c r="A574" s="1" t="inlineStr">
         <is>
           <t>17244</t>
         </is>
@@ -21373,7 +20849,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" t="inlineStr">
+      <c r="A575" s="1" t="inlineStr">
         <is>
           <t>11710</t>
         </is>
@@ -21406,7 +20882,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" t="inlineStr">
+      <c r="A576" s="1" t="inlineStr">
         <is>
           <t>11826</t>
         </is>
@@ -21439,7 +20915,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" t="inlineStr">
+      <c r="A577" s="1" t="inlineStr">
         <is>
           <t>17245</t>
         </is>
@@ -21462,11 +20938,6 @@
       <c r="E577" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F577" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G577" t="n">
@@ -21477,7 +20948,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" t="inlineStr">
+      <c r="A578" s="1" t="inlineStr">
         <is>
           <t>11858</t>
         </is>
@@ -21515,7 +20986,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" t="inlineStr">
+      <c r="A579" s="1" t="inlineStr">
         <is>
           <t>10173</t>
         </is>
@@ -21548,7 +21019,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" t="inlineStr">
+      <c r="A580" s="1" t="inlineStr">
         <is>
           <t>17246</t>
         </is>
@@ -21581,7 +21052,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" t="inlineStr">
+      <c r="A581" s="1" t="inlineStr">
         <is>
           <t>10753</t>
         </is>
@@ -21614,7 +21085,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" t="inlineStr">
+      <c r="A582" s="1" t="inlineStr">
         <is>
           <t>12542</t>
         </is>
@@ -21647,7 +21118,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" t="inlineStr">
+      <c r="A583" s="1" t="inlineStr">
         <is>
           <t>12525</t>
         </is>
@@ -21685,7 +21156,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" t="inlineStr">
+      <c r="A584" s="1" t="inlineStr">
         <is>
           <t>11091</t>
         </is>
@@ -21718,7 +21189,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" t="inlineStr">
+      <c r="A585" s="1" t="inlineStr">
         <is>
           <t>1458</t>
         </is>
@@ -21756,7 +21227,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" t="inlineStr">
+      <c r="A586" s="1" t="inlineStr">
         <is>
           <t>17008</t>
         </is>
@@ -21794,7 +21265,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" t="inlineStr">
+      <c r="A587" s="1" t="inlineStr">
         <is>
           <t>17006</t>
         </is>
@@ -21832,7 +21303,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" t="inlineStr">
+      <c r="A588" s="1" t="inlineStr">
         <is>
           <t>17007</t>
         </is>
@@ -21870,7 +21341,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" t="inlineStr">
+      <c r="A589" s="1" t="inlineStr">
         <is>
           <t>10756</t>
         </is>
@@ -21893,11 +21364,6 @@
       <c r="E589" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F589" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G589" t="n">
@@ -21908,7 +21374,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" t="inlineStr">
+      <c r="A590" s="1" t="inlineStr">
         <is>
           <t>16478</t>
         </is>
@@ -21946,7 +21412,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" t="inlineStr">
+      <c r="A591" s="1" t="inlineStr">
         <is>
           <t>11510</t>
         </is>
@@ -21984,7 +21450,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" t="inlineStr">
+      <c r="A592" s="1" t="inlineStr">
         <is>
           <t>12494</t>
         </is>
@@ -22022,7 +21488,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" t="inlineStr">
+      <c r="A593" s="1" t="inlineStr">
         <is>
           <t>17053</t>
         </is>
@@ -22060,7 +21526,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" t="inlineStr">
+      <c r="A594" s="1" t="inlineStr">
         <is>
           <t>17052</t>
         </is>
@@ -22098,7 +21564,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" t="inlineStr">
+      <c r="A595" s="1" t="inlineStr">
         <is>
           <t>16289</t>
         </is>
@@ -22131,7 +21597,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" t="inlineStr">
+      <c r="A596" s="1" t="inlineStr">
         <is>
           <t>17051</t>
         </is>
@@ -22169,7 +21635,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" t="inlineStr">
+      <c r="A597" s="1" t="inlineStr">
         <is>
           <t>15810</t>
         </is>
@@ -22207,7 +21673,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" t="inlineStr">
+      <c r="A598" s="1" t="inlineStr">
         <is>
           <t>11607</t>
         </is>
@@ -22245,7 +21711,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" t="inlineStr">
+      <c r="A599" s="1" t="inlineStr">
         <is>
           <t>16480</t>
         </is>
@@ -22283,7 +21749,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" t="inlineStr">
+      <c r="A600" s="1" t="inlineStr">
         <is>
           <t>16479</t>
         </is>
@@ -22321,7 +21787,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" t="inlineStr">
+      <c r="A601" s="1" t="inlineStr">
         <is>
           <t>17303</t>
         </is>
@@ -22344,11 +21810,6 @@
       <c r="E601" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F601" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G601" t="n">
@@ -22359,7 +21820,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" t="inlineStr">
+      <c r="A602" s="1" t="inlineStr">
         <is>
           <t>11851</t>
         </is>
@@ -22382,11 +21843,6 @@
       <c r="E602" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F602" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G602" t="n">
@@ -22397,7 +21853,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" t="inlineStr">
+      <c r="A603" s="1" t="inlineStr">
         <is>
           <t>16481</t>
         </is>
@@ -22435,7 +21891,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" t="inlineStr">
+      <c r="A604" s="1" t="inlineStr">
         <is>
           <t>12186</t>
         </is>
@@ -22473,7 +21929,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" t="inlineStr">
+      <c r="A605" s="1" t="inlineStr">
         <is>
           <t>16171</t>
         </is>
@@ -22511,7 +21967,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" t="inlineStr">
+      <c r="A606" s="1" t="inlineStr">
         <is>
           <t>16172</t>
         </is>
@@ -22549,7 +22005,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" t="inlineStr">
+      <c r="A607" s="1" t="inlineStr">
         <is>
           <t>17211</t>
         </is>
@@ -22572,11 +22028,6 @@
       <c r="E607" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F607" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G607" t="n">
@@ -22587,7 +22038,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" t="inlineStr">
+      <c r="A608" s="1" t="inlineStr">
         <is>
           <t>12584</t>
         </is>
@@ -22625,7 +22076,7 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" t="inlineStr">
+      <c r="A609" s="1" t="inlineStr">
         <is>
           <t>13966</t>
         </is>
@@ -22663,7 +22114,7 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" t="inlineStr">
+      <c r="A610" s="1" t="inlineStr">
         <is>
           <t>17014</t>
         </is>
@@ -22701,7 +22152,7 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" t="inlineStr">
+      <c r="A611" s="1" t="inlineStr">
         <is>
           <t>16044</t>
         </is>
@@ -22739,7 +22190,7 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" t="inlineStr">
+      <c r="A612" s="1" t="inlineStr">
         <is>
           <t>1496</t>
         </is>
@@ -22777,7 +22228,7 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" t="inlineStr">
+      <c r="A613" s="1" t="inlineStr">
         <is>
           <t>16426</t>
         </is>
@@ -22810,7 +22261,7 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" t="inlineStr">
+      <c r="A614" s="1" t="inlineStr">
         <is>
           <t>16425</t>
         </is>
@@ -22843,7 +22294,7 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" t="inlineStr">
+      <c r="A615" s="1" t="inlineStr">
         <is>
           <t>17358</t>
         </is>
@@ -22866,11 +22317,6 @@
       <c r="E615" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F615" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G615" t="n">
@@ -22881,7 +22327,7 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" t="inlineStr">
+      <c r="A616" s="1" t="inlineStr">
         <is>
           <t>11544</t>
         </is>
@@ -22919,7 +22365,7 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" t="inlineStr">
+      <c r="A617" s="1" t="inlineStr">
         <is>
           <t>16108</t>
         </is>
@@ -22942,11 +22388,6 @@
       <c r="E617" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F617" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G617" t="n">
@@ -22957,7 +22398,7 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" t="inlineStr">
+      <c r="A618" s="1" t="inlineStr">
         <is>
           <t>11514</t>
         </is>
@@ -22995,7 +22436,7 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" t="inlineStr">
+      <c r="A619" s="1" t="inlineStr">
         <is>
           <t>11582</t>
         </is>
@@ -23033,7 +22474,7 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" t="inlineStr">
+      <c r="A620" s="1" t="inlineStr">
         <is>
           <t>11875</t>
         </is>
@@ -23056,11 +22497,6 @@
       <c r="E620" t="inlineStr">
         <is>
           <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F620" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G620" t="n">
@@ -23071,7 +22507,7 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" t="inlineStr">
+      <c r="A621" s="1" t="inlineStr">
         <is>
           <t>15746</t>
         </is>
@@ -23109,7 +22545,7 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" t="inlineStr">
+      <c r="A622" s="1" t="inlineStr">
         <is>
           <t>14397</t>
         </is>
@@ -23147,7 +22583,7 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" t="inlineStr">
+      <c r="A623" s="1" t="inlineStr">
         <is>
           <t>10963</t>
         </is>
@@ -23170,11 +22606,6 @@
       <c r="E623" t="inlineStr">
         <is>
           <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F623" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G623" t="n">
@@ -23185,7 +22616,7 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" t="inlineStr">
+      <c r="A624" s="1" t="inlineStr">
         <is>
           <t>10643</t>
         </is>
@@ -23223,7 +22654,7 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" t="inlineStr">
+      <c r="A625" s="1" t="inlineStr">
         <is>
           <t>15812</t>
         </is>
@@ -23256,7 +22687,7 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" t="inlineStr">
+      <c r="A626" s="1" t="inlineStr">
         <is>
           <t>16140</t>
         </is>
@@ -23289,7 +22720,7 @@
       </c>
     </row>
     <row r="627">
-      <c r="A627" t="inlineStr">
+      <c r="A627" s="1" t="inlineStr">
         <is>
           <t>16174</t>
         </is>
@@ -23327,7 +22758,7 @@
       </c>
     </row>
     <row r="628">
-      <c r="A628" t="inlineStr">
+      <c r="A628" s="1" t="inlineStr">
         <is>
           <t>16173</t>
         </is>
@@ -23365,7 +22796,7 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" t="inlineStr">
+      <c r="A629" s="1" t="inlineStr">
         <is>
           <t>16276</t>
         </is>
@@ -23398,7 +22829,7 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" t="inlineStr">
+      <c r="A630" s="1" t="inlineStr">
         <is>
           <t>16175</t>
         </is>
@@ -23421,11 +22852,6 @@
       <c r="E630" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F630" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G630" t="n">
@@ -23436,7 +22862,7 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" t="inlineStr">
+      <c r="A631" s="1" t="inlineStr">
         <is>
           <t>16118</t>
         </is>
@@ -23474,7 +22900,7 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" t="inlineStr">
+      <c r="A632" s="1" t="inlineStr">
         <is>
           <t>11108</t>
         </is>
@@ -23512,7 +22938,7 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" t="inlineStr">
+      <c r="A633" s="1" t="inlineStr">
         <is>
           <t>16340</t>
         </is>
@@ -23550,7 +22976,7 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" t="inlineStr">
+      <c r="A634" s="1" t="inlineStr">
         <is>
           <t>17222</t>
         </is>
@@ -23588,7 +23014,7 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" t="inlineStr">
+      <c r="A635" s="1" t="inlineStr">
         <is>
           <t>17223</t>
         </is>
@@ -23626,7 +23052,7 @@
       </c>
     </row>
     <row r="636">
-      <c r="A636" t="inlineStr">
+      <c r="A636" s="1" t="inlineStr">
         <is>
           <t>17209</t>
         </is>
@@ -23649,11 +23075,6 @@
       <c r="E636" t="inlineStr">
         <is>
           <t>150-175cm</t>
-        </is>
-      </c>
-      <c r="F636" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G636" t="n">
@@ -23664,7 +23085,7 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" t="inlineStr">
+      <c r="A637" s="1" t="inlineStr">
         <is>
           <t>16079</t>
         </is>
@@ -23687,11 +23108,6 @@
       <c r="E637" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F637" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G637" t="n">
@@ -23702,7 +23118,7 @@
       </c>
     </row>
     <row r="638">
-      <c r="A638" t="inlineStr">
+      <c r="A638" s="1" t="inlineStr">
         <is>
           <t>16314</t>
         </is>
@@ -23740,7 +23156,7 @@
       </c>
     </row>
     <row r="639">
-      <c r="A639" t="inlineStr">
+      <c r="A639" s="1" t="inlineStr">
         <is>
           <t>17012</t>
         </is>
@@ -23778,7 +23194,7 @@
       </c>
     </row>
     <row r="640">
-      <c r="A640" t="inlineStr">
+      <c r="A640" s="1" t="inlineStr">
         <is>
           <t>15734</t>
         </is>
@@ -23816,7 +23232,7 @@
       </c>
     </row>
     <row r="641">
-      <c r="A641" t="inlineStr">
+      <c r="A641" s="1" t="inlineStr">
         <is>
           <t>14398</t>
         </is>
@@ -23854,7 +23270,7 @@
       </c>
     </row>
     <row r="642">
-      <c r="A642" t="inlineStr">
+      <c r="A642" s="1" t="inlineStr">
         <is>
           <t>16081</t>
         </is>
@@ -23887,7 +23303,7 @@
       </c>
     </row>
     <row r="643">
-      <c r="A643" t="inlineStr">
+      <c r="A643" s="1" t="inlineStr">
         <is>
           <t>12590</t>
         </is>
@@ -23925,7 +23341,7 @@
       </c>
     </row>
     <row r="644">
-      <c r="A644" t="inlineStr">
+      <c r="A644" s="1" t="inlineStr">
         <is>
           <t>16482</t>
         </is>
@@ -23963,7 +23379,7 @@
       </c>
     </row>
     <row r="645">
-      <c r="A645" t="inlineStr">
+      <c r="A645" s="1" t="inlineStr">
         <is>
           <t>11189</t>
         </is>
@@ -24001,7 +23417,7 @@
       </c>
     </row>
     <row r="646">
-      <c r="A646" t="inlineStr">
+      <c r="A646" s="1" t="inlineStr">
         <is>
           <t>12589</t>
         </is>
@@ -24039,7 +23455,7 @@
       </c>
     </row>
     <row r="647">
-      <c r="A647" t="inlineStr">
+      <c r="A647" s="1" t="inlineStr">
         <is>
           <t>17210</t>
         </is>
@@ -24062,11 +23478,6 @@
       <c r="E647" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F647" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G647" t="n">
@@ -24077,7 +23488,7 @@
       </c>
     </row>
     <row r="648">
-      <c r="A648" t="inlineStr">
+      <c r="A648" s="1" t="inlineStr">
         <is>
           <t>17347</t>
         </is>
@@ -24115,7 +23526,7 @@
       </c>
     </row>
     <row r="649">
-      <c r="A649" t="inlineStr">
+      <c r="A649" s="1" t="inlineStr">
         <is>
           <t>17011</t>
         </is>
@@ -24153,7 +23564,7 @@
       </c>
     </row>
     <row r="650">
-      <c r="A650" t="inlineStr">
+      <c r="A650" s="1" t="inlineStr">
         <is>
           <t>17010</t>
         </is>
@@ -24191,7 +23602,7 @@
       </c>
     </row>
     <row r="651">
-      <c r="A651" t="inlineStr">
+      <c r="A651" s="1" t="inlineStr">
         <is>
           <t>16242</t>
         </is>
@@ -24214,11 +23625,6 @@
       <c r="E651" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F651" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G651" t="n">
@@ -24229,7 +23635,7 @@
       </c>
     </row>
     <row r="652">
-      <c r="A652" t="inlineStr">
+      <c r="A652" s="1" t="inlineStr">
         <is>
           <t>16341</t>
         </is>
@@ -24267,7 +23673,7 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" t="inlineStr">
+      <c r="A653" s="1" t="inlineStr">
         <is>
           <t>12543</t>
         </is>
@@ -24305,7 +23711,7 @@
       </c>
     </row>
     <row r="654">
-      <c r="A654" t="inlineStr">
+      <c r="A654" s="1" t="inlineStr">
         <is>
           <t>17016</t>
         </is>
@@ -24343,7 +23749,7 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" t="inlineStr">
+      <c r="A655" s="1" t="inlineStr">
         <is>
           <t>17015</t>
         </is>
@@ -24381,7 +23787,7 @@
       </c>
     </row>
     <row r="656">
-      <c r="A656" t="inlineStr">
+      <c r="A656" s="1" t="inlineStr">
         <is>
           <t>13188</t>
         </is>
@@ -24419,7 +23825,7 @@
       </c>
     </row>
     <row r="657">
-      <c r="A657" t="inlineStr">
+      <c r="A657" s="1" t="inlineStr">
         <is>
           <t>16337</t>
         </is>
@@ -24457,7 +23863,7 @@
       </c>
     </row>
     <row r="658">
-      <c r="A658" t="inlineStr">
+      <c r="A658" s="1" t="inlineStr">
         <is>
           <t>15692</t>
         </is>
@@ -24495,7 +23901,7 @@
       </c>
     </row>
     <row r="659">
-      <c r="A659" t="inlineStr">
+      <c r="A659" s="1" t="inlineStr">
         <is>
           <t>11714</t>
         </is>
@@ -24533,7 +23939,7 @@
       </c>
     </row>
     <row r="660">
-      <c r="A660" t="inlineStr">
+      <c r="A660" s="1" t="inlineStr">
         <is>
           <t>11801</t>
         </is>
@@ -24566,7 +23972,7 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" t="inlineStr">
+      <c r="A661" s="1" t="inlineStr">
         <is>
           <t>17212</t>
         </is>
@@ -24589,11 +23995,6 @@
       <c r="E661" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F661" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G661" t="n">
@@ -24604,7 +24005,7 @@
       </c>
     </row>
     <row r="662">
-      <c r="A662" t="inlineStr">
+      <c r="A662" s="1" t="inlineStr">
         <is>
           <t>16046</t>
         </is>
@@ -24642,7 +24043,7 @@
       </c>
     </row>
     <row r="663">
-      <c r="A663" t="inlineStr">
+      <c r="A663" s="1" t="inlineStr">
         <is>
           <t>16484</t>
         </is>
@@ -24680,7 +24081,7 @@
       </c>
     </row>
     <row r="664">
-      <c r="A664" t="inlineStr">
+      <c r="A664" s="1" t="inlineStr">
         <is>
           <t>16483</t>
         </is>
@@ -24718,7 +24119,7 @@
       </c>
     </row>
     <row r="665">
-      <c r="A665" t="inlineStr">
+      <c r="A665" s="1" t="inlineStr">
         <is>
           <t>15648</t>
         </is>
@@ -24756,7 +24157,7 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" t="inlineStr">
+      <c r="A666" s="1" t="inlineStr">
         <is>
           <t>16334</t>
         </is>
@@ -24794,7 +24195,7 @@
       </c>
     </row>
     <row r="667">
-      <c r="A667" t="inlineStr">
+      <c r="A667" s="1" t="inlineStr">
         <is>
           <t>13968</t>
         </is>
@@ -24832,7 +24233,7 @@
       </c>
     </row>
     <row r="668">
-      <c r="A668" t="inlineStr">
+      <c r="A668" s="1" t="inlineStr">
         <is>
           <t>17017</t>
         </is>
@@ -24870,7 +24271,7 @@
       </c>
     </row>
     <row r="669">
-      <c r="A669" t="inlineStr">
+      <c r="A669" s="1" t="inlineStr">
         <is>
           <t>12396</t>
         </is>
@@ -24908,7 +24309,7 @@
       </c>
     </row>
     <row r="670">
-      <c r="A670" t="inlineStr">
+      <c r="A670" s="1" t="inlineStr">
         <is>
           <t>16176</t>
         </is>
@@ -24946,7 +24347,7 @@
       </c>
     </row>
     <row r="671">
-      <c r="A671" t="inlineStr">
+      <c r="A671" s="1" t="inlineStr">
         <is>
           <t>16179</t>
         </is>
@@ -24969,11 +24370,6 @@
       <c r="E671" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F671" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G671" t="n">
@@ -24984,7 +24380,7 @@
       </c>
     </row>
     <row r="672">
-      <c r="A672" t="inlineStr">
+      <c r="A672" s="1" t="inlineStr">
         <is>
           <t>16177</t>
         </is>
@@ -25022,7 +24418,7 @@
       </c>
     </row>
     <row r="673">
-      <c r="A673" t="inlineStr">
+      <c r="A673" s="1" t="inlineStr">
         <is>
           <t>16124</t>
         </is>
@@ -25060,7 +24456,7 @@
       </c>
     </row>
     <row r="674">
-      <c r="A674" t="inlineStr">
+      <c r="A674" s="1" t="inlineStr">
         <is>
           <t>13050</t>
         </is>
@@ -25083,11 +24479,6 @@
       <c r="E674" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F674" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G674" t="n">
@@ -25098,7 +24489,7 @@
       </c>
     </row>
     <row r="675">
-      <c r="A675" t="inlineStr">
+      <c r="A675" s="1" t="inlineStr">
         <is>
           <t>16126</t>
         </is>
@@ -25136,7 +24527,7 @@
       </c>
     </row>
     <row r="676">
-      <c r="A676" t="inlineStr">
+      <c r="A676" s="1" t="inlineStr">
         <is>
           <t>16148</t>
         </is>
@@ -25164,7 +24555,7 @@
       </c>
     </row>
     <row r="677">
-      <c r="A677" t="inlineStr">
+      <c r="A677" s="1" t="inlineStr">
         <is>
           <t>1645</t>
         </is>
@@ -25202,7 +24593,7 @@
       </c>
     </row>
     <row r="678">
-      <c r="A678" t="inlineStr">
+      <c r="A678" s="1" t="inlineStr">
         <is>
           <t>13972</t>
         </is>
@@ -25240,7 +24631,7 @@
       </c>
     </row>
     <row r="679">
-      <c r="A679" t="inlineStr">
+      <c r="A679" s="1" t="inlineStr">
         <is>
           <t>17020</t>
         </is>
@@ -25278,7 +24669,7 @@
       </c>
     </row>
     <row r="680">
-      <c r="A680" t="inlineStr">
+      <c r="A680" s="1" t="inlineStr">
         <is>
           <t>17019</t>
         </is>
@@ -25316,7 +24707,7 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" t="inlineStr">
+      <c r="A681" s="1" t="inlineStr">
         <is>
           <t>17018</t>
         </is>
@@ -25354,7 +24745,7 @@
       </c>
     </row>
     <row r="682">
-      <c r="A682" t="inlineStr">
+      <c r="A682" s="1" t="inlineStr">
         <is>
           <t>16047</t>
         </is>
@@ -25392,7 +24783,7 @@
       </c>
     </row>
     <row r="683">
-      <c r="A683" t="inlineStr">
+      <c r="A683" s="1" t="inlineStr">
         <is>
           <t>11852</t>
         </is>
@@ -25425,7 +24816,7 @@
       </c>
     </row>
     <row r="684">
-      <c r="A684" t="inlineStr">
+      <c r="A684" s="1" t="inlineStr">
         <is>
           <t>16083</t>
         </is>
@@ -25458,7 +24849,7 @@
       </c>
     </row>
     <row r="685">
-      <c r="A685" t="inlineStr">
+      <c r="A685" s="1" t="inlineStr">
         <is>
           <t>17022</t>
         </is>
@@ -25496,7 +24887,7 @@
       </c>
     </row>
     <row r="686">
-      <c r="A686" t="inlineStr">
+      <c r="A686" s="1" t="inlineStr">
         <is>
           <t>17021</t>
         </is>
@@ -25534,7 +24925,7 @@
       </c>
     </row>
     <row r="687">
-      <c r="A687" t="inlineStr">
+      <c r="A687" s="1" t="inlineStr">
         <is>
           <t>16048</t>
         </is>
@@ -25557,11 +24948,6 @@
       <c r="E687" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F687" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G687" t="n">
@@ -25572,7 +24958,7 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" t="inlineStr">
+      <c r="A688" s="1" t="inlineStr">
         <is>
           <t>12397</t>
         </is>
@@ -25595,11 +24981,6 @@
       <c r="E688" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F688" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G688" t="n">
@@ -25610,7 +24991,7 @@
       </c>
     </row>
     <row r="689">
-      <c r="A689" t="inlineStr">
+      <c r="A689" s="1" t="inlineStr">
         <is>
           <t>16335</t>
         </is>
@@ -25648,7 +25029,7 @@
       </c>
     </row>
     <row r="690">
-      <c r="A690" t="inlineStr">
+      <c r="A690" s="1" t="inlineStr">
         <is>
           <t>12418</t>
         </is>
@@ -25686,7 +25067,7 @@
       </c>
     </row>
     <row r="691">
-      <c r="A691" t="inlineStr">
+      <c r="A691" s="1" t="inlineStr">
         <is>
           <t>13991</t>
         </is>
@@ -25724,7 +25105,7 @@
       </c>
     </row>
     <row r="692">
-      <c r="A692" t="inlineStr">
+      <c r="A692" s="1" t="inlineStr">
         <is>
           <t>12420</t>
         </is>
@@ -25762,7 +25143,7 @@
       </c>
     </row>
     <row r="693">
-      <c r="A693" t="inlineStr">
+      <c r="A693" s="1" t="inlineStr">
         <is>
           <t>16342</t>
         </is>
@@ -25800,7 +25181,7 @@
       </c>
     </row>
     <row r="694">
-      <c r="A694" t="inlineStr">
+      <c r="A694" s="1" t="inlineStr">
         <is>
           <t>16316</t>
         </is>
@@ -25838,7 +25219,7 @@
       </c>
     </row>
     <row r="695">
-      <c r="A695" t="inlineStr">
+      <c r="A695" s="1" t="inlineStr">
         <is>
           <t>11673</t>
         </is>
@@ -25861,11 +25242,6 @@
       <c r="E695" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F695" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G695" t="n">
@@ -25876,7 +25252,7 @@
       </c>
     </row>
     <row r="696">
-      <c r="A696" t="inlineStr">
+      <c r="A696" s="1" t="inlineStr">
         <is>
           <t>12398</t>
         </is>
@@ -25914,7 +25290,7 @@
       </c>
     </row>
     <row r="697">
-      <c r="A697" t="inlineStr">
+      <c r="A697" s="1" t="inlineStr">
         <is>
           <t>11536</t>
         </is>
@@ -25952,7 +25328,7 @@
       </c>
     </row>
     <row r="698">
-      <c r="A698" t="inlineStr">
+      <c r="A698" s="1" t="inlineStr">
         <is>
           <t>11537</t>
         </is>
@@ -25990,7 +25366,7 @@
       </c>
     </row>
     <row r="699">
-      <c r="A699" t="inlineStr">
+      <c r="A699" s="1" t="inlineStr">
         <is>
           <t>13268</t>
         </is>
@@ -26028,7 +25404,7 @@
       </c>
     </row>
     <row r="700">
-      <c r="A700" t="inlineStr">
+      <c r="A700" s="1" t="inlineStr">
         <is>
           <t>10216</t>
         </is>
@@ -26051,11 +25427,6 @@
       <c r="E700" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F700" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G700" t="n">
@@ -26066,7 +25437,7 @@
       </c>
     </row>
     <row r="701">
-      <c r="A701" t="inlineStr">
+      <c r="A701" s="1" t="inlineStr">
         <is>
           <t>14413</t>
         </is>
@@ -26104,7 +25475,7 @@
       </c>
     </row>
     <row r="702">
-      <c r="A702" t="inlineStr">
+      <c r="A702" s="1" t="inlineStr">
         <is>
           <t>11675</t>
         </is>
@@ -26137,7 +25508,7 @@
       </c>
     </row>
     <row r="703">
-      <c r="A703" t="inlineStr">
+      <c r="A703" s="1" t="inlineStr">
         <is>
           <t>1525</t>
         </is>
@@ -26170,7 +25541,7 @@
       </c>
     </row>
     <row r="704">
-      <c r="A704" t="inlineStr">
+      <c r="A704" s="1" t="inlineStr">
         <is>
           <t>17213</t>
         </is>
@@ -26203,7 +25574,7 @@
       </c>
     </row>
     <row r="705">
-      <c r="A705" t="inlineStr">
+      <c r="A705" s="1" t="inlineStr">
         <is>
           <t>12540</t>
         </is>
@@ -26226,11 +25597,6 @@
       <c r="E705" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F705" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G705" t="n">
@@ -26241,7 +25607,7 @@
       </c>
     </row>
     <row r="706">
-      <c r="A706" t="inlineStr">
+      <c r="A706" s="1" t="inlineStr">
         <is>
           <t>16485</t>
         </is>
@@ -26279,7 +25645,7 @@
       </c>
     </row>
     <row r="707">
-      <c r="A707" t="inlineStr">
+      <c r="A707" s="1" t="inlineStr">
         <is>
           <t>17024</t>
         </is>
@@ -26317,7 +25683,7 @@
       </c>
     </row>
     <row r="708">
-      <c r="A708" t="inlineStr">
+      <c r="A708" s="1" t="inlineStr">
         <is>
           <t>17214</t>
         </is>
@@ -26355,7 +25721,7 @@
       </c>
     </row>
     <row r="709">
-      <c r="A709" t="inlineStr">
+      <c r="A709" s="1" t="inlineStr">
         <is>
           <t>16301</t>
         </is>
@@ -26378,11 +25744,6 @@
       <c r="E709" t="inlineStr">
         <is>
           <t>120-140cm</t>
-        </is>
-      </c>
-      <c r="F709" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G709" t="n">
@@ -26393,7 +25754,7 @@
       </c>
     </row>
     <row r="710">
-      <c r="A710" t="inlineStr">
+      <c r="A710" s="1" t="inlineStr">
         <is>
           <t>11679</t>
         </is>
@@ -26416,11 +25777,6 @@
       <c r="E710" t="inlineStr">
         <is>
           <t>120-150cm</t>
-        </is>
-      </c>
-      <c r="F710" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G710" t="n">
@@ -26431,7 +25787,7 @@
       </c>
     </row>
     <row r="711">
-      <c r="A711" t="inlineStr">
+      <c r="A711" s="1" t="inlineStr">
         <is>
           <t>17247</t>
         </is>
@@ -26469,7 +25825,7 @@
       </c>
     </row>
     <row r="712">
-      <c r="A712" t="inlineStr">
+      <c r="A712" s="1" t="inlineStr">
         <is>
           <t>17025</t>
         </is>
@@ -26507,7 +25863,7 @@
       </c>
     </row>
     <row r="713">
-      <c r="A713" t="inlineStr">
+      <c r="A713" s="1" t="inlineStr">
         <is>
           <t>17026</t>
         </is>
@@ -26545,7 +25901,7 @@
       </c>
     </row>
     <row r="714">
-      <c r="A714" t="inlineStr">
+      <c r="A714" s="1" t="inlineStr">
         <is>
           <t>16051</t>
         </is>
@@ -26583,7 +25939,7 @@
       </c>
     </row>
     <row r="715">
-      <c r="A715" t="inlineStr">
+      <c r="A715" s="1" t="inlineStr">
         <is>
           <t>14408</t>
         </is>
@@ -26621,7 +25977,7 @@
       </c>
     </row>
     <row r="716">
-      <c r="A716" t="inlineStr">
+      <c r="A716" s="1" t="inlineStr">
         <is>
           <t>11550</t>
         </is>
@@ -26659,7 +26015,7 @@
       </c>
     </row>
     <row r="717">
-      <c r="A717" t="inlineStr">
+      <c r="A717" s="1" t="inlineStr">
         <is>
           <t>11270</t>
         </is>
@@ -26682,11 +26038,6 @@
       <c r="E717" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F717" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G717" t="n">
@@ -26697,7 +26048,7 @@
       </c>
     </row>
     <row r="718">
-      <c r="A718" t="inlineStr">
+      <c r="A718" s="1" t="inlineStr">
         <is>
           <t>10723</t>
         </is>
@@ -26720,11 +26071,6 @@
       <c r="E718" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F718" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G718" t="n">
@@ -26735,7 +26081,7 @@
       </c>
     </row>
     <row r="719">
-      <c r="A719" t="inlineStr">
+      <c r="A719" s="1" t="inlineStr">
         <is>
           <t>16486</t>
         </is>
@@ -26773,7 +26119,7 @@
       </c>
     </row>
     <row r="720">
-      <c r="A720" t="inlineStr">
+      <c r="A720" s="1" t="inlineStr">
         <is>
           <t>16297</t>
         </is>
@@ -26796,11 +26142,6 @@
       <c r="E720" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F720" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G720" t="n">
@@ -26811,7 +26152,7 @@
       </c>
     </row>
     <row r="721">
-      <c r="A721" t="inlineStr">
+      <c r="A721" s="1" t="inlineStr">
         <is>
           <t>15645</t>
         </is>
@@ -26849,7 +26190,7 @@
       </c>
     </row>
     <row r="722">
-      <c r="A722" t="inlineStr">
+      <c r="A722" s="1" t="inlineStr">
         <is>
           <t>1537</t>
         </is>
@@ -26882,7 +26223,7 @@
       </c>
     </row>
     <row r="723">
-      <c r="A723" t="inlineStr">
+      <c r="A723" s="1" t="inlineStr">
         <is>
           <t>16054</t>
         </is>
@@ -26915,7 +26256,7 @@
       </c>
     </row>
     <row r="724">
-      <c r="A724" t="inlineStr">
+      <c r="A724" s="1" t="inlineStr">
         <is>
           <t>17365</t>
         </is>
@@ -26948,7 +26289,7 @@
       </c>
     </row>
     <row r="725">
-      <c r="A725" t="inlineStr">
+      <c r="A725" s="1" t="inlineStr">
         <is>
           <t>10874</t>
         </is>
@@ -26971,11 +26312,6 @@
       <c r="E725" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F725" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G725" t="n">
@@ -26986,7 +26322,7 @@
       </c>
     </row>
     <row r="726">
-      <c r="A726" t="inlineStr">
+      <c r="A726" s="1" t="inlineStr">
         <is>
           <t>13976</t>
         </is>
@@ -27024,7 +26360,7 @@
       </c>
     </row>
     <row r="727">
-      <c r="A727" t="inlineStr">
+      <c r="A727" s="1" t="inlineStr">
         <is>
           <t>17028</t>
         </is>
@@ -27062,7 +26398,7 @@
       </c>
     </row>
     <row r="728">
-      <c r="A728" t="inlineStr">
+      <c r="A728" s="1" t="inlineStr">
         <is>
           <t>17029</t>
         </is>
@@ -27100,7 +26436,7 @@
       </c>
     </row>
     <row r="729">
-      <c r="A729" t="inlineStr">
+      <c r="A729" s="1" t="inlineStr">
         <is>
           <t>13978</t>
         </is>
@@ -27138,7 +26474,7 @@
       </c>
     </row>
     <row r="730">
-      <c r="A730" t="inlineStr">
+      <c r="A730" s="1" t="inlineStr">
         <is>
           <t>15699</t>
         </is>
@@ -27161,11 +26497,6 @@
       <c r="E730" t="inlineStr">
         <is>
           <t>100 -125cm</t>
-        </is>
-      </c>
-      <c r="F730" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G730" t="n">
@@ -27176,7 +26507,7 @@
       </c>
     </row>
     <row r="731">
-      <c r="A731" t="inlineStr">
+      <c r="A731" s="1" t="inlineStr">
         <is>
           <t>11638</t>
         </is>
@@ -27214,7 +26545,7 @@
       </c>
     </row>
     <row r="732">
-      <c r="A732" t="inlineStr">
+      <c r="A732" s="1" t="inlineStr">
         <is>
           <t>10912</t>
         </is>
@@ -27237,11 +26568,6 @@
       <c r="E732" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F732" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G732" t="n">
@@ -27252,7 +26578,7 @@
       </c>
     </row>
     <row r="733">
-      <c r="A733" t="inlineStr">
+      <c r="A733" s="1" t="inlineStr">
         <is>
           <t>15716</t>
         </is>
@@ -27290,7 +26616,7 @@
       </c>
     </row>
     <row r="734">
-      <c r="A734" t="inlineStr">
+      <c r="A734" s="1" t="inlineStr">
         <is>
           <t>15706</t>
         </is>
@@ -27328,7 +26654,7 @@
       </c>
     </row>
     <row r="735">
-      <c r="A735" t="inlineStr">
+      <c r="A735" s="1" t="inlineStr">
         <is>
           <t>17032</t>
         </is>
@@ -27366,7 +26692,7 @@
       </c>
     </row>
     <row r="736">
-      <c r="A736" t="inlineStr">
+      <c r="A736" s="1" t="inlineStr">
         <is>
           <t>17031</t>
         </is>
@@ -27404,7 +26730,7 @@
       </c>
     </row>
     <row r="737">
-      <c r="A737" t="inlineStr">
+      <c r="A737" s="1" t="inlineStr">
         <is>
           <t>17030</t>
         </is>
@@ -27442,7 +26768,7 @@
       </c>
     </row>
     <row r="738">
-      <c r="A738" t="inlineStr">
+      <c r="A738" s="1" t="inlineStr">
         <is>
           <t>10907</t>
         </is>
@@ -27480,7 +26806,7 @@
       </c>
     </row>
     <row r="739">
-      <c r="A739" t="inlineStr">
+      <c r="A739" s="1" t="inlineStr">
         <is>
           <t>10866</t>
         </is>
@@ -27503,11 +26829,6 @@
       <c r="E739" t="inlineStr">
         <is>
           <t>250- 300cm</t>
-        </is>
-      </c>
-      <c r="F739" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G739" t="n">
@@ -27518,7 +26839,7 @@
       </c>
     </row>
     <row r="740">
-      <c r="A740" t="inlineStr">
+      <c r="A740" s="1" t="inlineStr">
         <is>
           <t>17034</t>
         </is>
@@ -27556,7 +26877,7 @@
       </c>
     </row>
     <row r="741">
-      <c r="A741" t="inlineStr">
+      <c r="A741" s="1" t="inlineStr">
         <is>
           <t>17357</t>
         </is>
@@ -27594,7 +26915,7 @@
       </c>
     </row>
     <row r="742">
-      <c r="A742" t="inlineStr">
+      <c r="A742" s="1" t="inlineStr">
         <is>
           <t>1547</t>
         </is>
@@ -27617,11 +26938,6 @@
       <c r="E742" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F742" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G742" t="n">
@@ -27632,7 +26948,7 @@
       </c>
     </row>
     <row r="743">
-      <c r="A743" t="inlineStr">
+      <c r="A743" s="1" t="inlineStr">
         <is>
           <t>12557</t>
         </is>
@@ -27670,7 +26986,7 @@
       </c>
     </row>
     <row r="744">
-      <c r="A744" t="inlineStr">
+      <c r="A744" s="1" t="inlineStr">
         <is>
           <t>16487</t>
         </is>
@@ -27708,7 +27024,7 @@
       </c>
     </row>
     <row r="745">
-      <c r="A745" t="inlineStr">
+      <c r="A745" s="1" t="inlineStr">
         <is>
           <t>13269</t>
         </is>
@@ -27746,7 +27062,7 @@
       </c>
     </row>
     <row r="746">
-      <c r="A746" t="inlineStr">
+      <c r="A746" s="1" t="inlineStr">
         <is>
           <t>1089</t>
         </is>
@@ -27769,11 +27085,6 @@
       <c r="E746" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F746" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G746" t="n">
@@ -27784,7 +27095,7 @@
       </c>
     </row>
     <row r="747">
-      <c r="A747" t="inlineStr">
+      <c r="A747" s="1" t="inlineStr">
         <is>
           <t>13271</t>
         </is>
@@ -27817,7 +27128,7 @@
       </c>
     </row>
     <row r="748">
-      <c r="A748" t="inlineStr">
+      <c r="A748" s="1" t="inlineStr">
         <is>
           <t>17037</t>
         </is>
@@ -27855,7 +27166,7 @@
       </c>
     </row>
     <row r="749">
-      <c r="A749" t="inlineStr">
+      <c r="A749" s="1" t="inlineStr">
         <is>
           <t>16488</t>
         </is>
@@ -27893,7 +27204,7 @@
       </c>
     </row>
     <row r="750">
-      <c r="A750" t="inlineStr">
+      <c r="A750" s="1" t="inlineStr">
         <is>
           <t>16055</t>
         </is>
@@ -27926,7 +27237,7 @@
       </c>
     </row>
     <row r="751">
-      <c r="A751" t="inlineStr">
+      <c r="A751" s="1" t="inlineStr">
         <is>
           <t>12526</t>
         </is>
@@ -27959,7 +27270,7 @@
       </c>
     </row>
     <row r="752">
-      <c r="A752" t="inlineStr">
+      <c r="A752" s="1" t="inlineStr">
         <is>
           <t>11170</t>
         </is>
@@ -27992,7 +27303,7 @@
       </c>
     </row>
     <row r="753">
-      <c r="A753" t="inlineStr">
+      <c r="A753" s="1" t="inlineStr">
         <is>
           <t>17248</t>
         </is>
@@ -28025,7 +27336,7 @@
       </c>
     </row>
     <row r="754">
-      <c r="A754" t="inlineStr">
+      <c r="A754" s="1" t="inlineStr">
         <is>
           <t>17350</t>
         </is>
@@ -28058,7 +27369,7 @@
       </c>
     </row>
     <row r="755">
-      <c r="A755" t="inlineStr">
+      <c r="A755" s="1" t="inlineStr">
         <is>
           <t>12412</t>
         </is>
@@ -28096,7 +27407,7 @@
       </c>
     </row>
     <row r="756">
-      <c r="A756" t="inlineStr">
+      <c r="A756" s="1" t="inlineStr">
         <is>
           <t>11645</t>
         </is>
@@ -28119,11 +27430,6 @@
       <c r="E756" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F756" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G756" t="n">
@@ -28134,7 +27440,7 @@
       </c>
     </row>
     <row r="757">
-      <c r="A757" t="inlineStr">
+      <c r="A757" s="1" t="inlineStr">
         <is>
           <t>13195</t>
         </is>
@@ -28172,7 +27478,7 @@
       </c>
     </row>
     <row r="758">
-      <c r="A758" t="inlineStr">
+      <c r="A758" s="1" t="inlineStr">
         <is>
           <t>10899</t>
         </is>
@@ -28210,7 +27516,7 @@
       </c>
     </row>
     <row r="759">
-      <c r="A759" t="inlineStr">
+      <c r="A759" s="1" t="inlineStr">
         <is>
           <t>16281</t>
         </is>
@@ -28248,7 +27554,7 @@
       </c>
     </row>
     <row r="760">
-      <c r="A760" t="inlineStr">
+      <c r="A760" s="1" t="inlineStr">
         <is>
           <t>16056</t>
         </is>
@@ -28271,11 +27577,6 @@
       <c r="E760" t="inlineStr">
         <is>
           <t>140-160cm</t>
-        </is>
-      </c>
-      <c r="F760" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G760" t="n">
@@ -28286,7 +27587,7 @@
       </c>
     </row>
     <row r="761">
-      <c r="A761" t="inlineStr">
+      <c r="A761" s="1" t="inlineStr">
         <is>
           <t>12527</t>
         </is>
@@ -28309,11 +27610,6 @@
       <c r="E761" t="inlineStr">
         <is>
           <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F761" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G761" t="n">
@@ -28324,7 +27620,7 @@
       </c>
     </row>
     <row r="762">
-      <c r="A762" t="inlineStr">
+      <c r="A762" s="1" t="inlineStr">
         <is>
           <t>15639</t>
         </is>
@@ -28362,7 +27658,7 @@
       </c>
     </row>
     <row r="763">
-      <c r="A763" t="inlineStr">
+      <c r="A763" s="1" t="inlineStr">
         <is>
           <t>16271</t>
         </is>
@@ -28385,11 +27681,6 @@
       <c r="E763" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F763" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G763" t="n">
@@ -28400,7 +27691,7 @@
       </c>
     </row>
     <row r="764">
-      <c r="A764" t="inlineStr">
+      <c r="A764" s="1" t="inlineStr">
         <is>
           <t>11702</t>
         </is>
@@ -28438,7 +27729,7 @@
       </c>
     </row>
     <row r="765">
-      <c r="A765" t="inlineStr">
+      <c r="A765" s="1" t="inlineStr">
         <is>
           <t>11003</t>
         </is>
@@ -28476,7 +27767,7 @@
       </c>
     </row>
     <row r="766">
-      <c r="A766" t="inlineStr">
+      <c r="A766" s="1" t="inlineStr">
         <is>
           <t>17047</t>
         </is>
@@ -28514,7 +27805,7 @@
       </c>
     </row>
     <row r="767">
-      <c r="A767" t="inlineStr">
+      <c r="A767" s="1" t="inlineStr">
         <is>
           <t>11001</t>
         </is>
@@ -28552,7 +27843,7 @@
       </c>
     </row>
     <row r="768">
-      <c r="A768" t="inlineStr">
+      <c r="A768" s="1" t="inlineStr">
         <is>
           <t>11640</t>
         </is>
@@ -28575,11 +27866,6 @@
       <c r="E768" t="inlineStr">
         <is>
           <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F768" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G768" t="n">
@@ -28590,7 +27876,7 @@
       </c>
     </row>
     <row r="769">
-      <c r="A769" t="inlineStr">
+      <c r="A769" s="1" t="inlineStr">
         <is>
           <t>16057</t>
         </is>
@@ -28623,7 +27909,7 @@
       </c>
     </row>
     <row r="770">
-      <c r="A770" t="inlineStr">
+      <c r="A770" s="1" t="inlineStr">
         <is>
           <t>12609</t>
         </is>
@@ -28656,7 +27942,7 @@
       </c>
     </row>
     <row r="771">
-      <c r="A771" t="inlineStr">
+      <c r="A771" s="1" t="inlineStr">
         <is>
           <t>15713</t>
         </is>
@@ -28689,7 +27975,7 @@
       </c>
     </row>
     <row r="772">
-      <c r="A772" t="inlineStr">
+      <c r="A772" s="1" t="inlineStr">
         <is>
           <t>12305</t>
         </is>
@@ -28722,7 +28008,7 @@
       </c>
     </row>
     <row r="773">
-      <c r="A773" t="inlineStr">
+      <c r="A773" s="1" t="inlineStr">
         <is>
           <t>10230</t>
         </is>
@@ -28755,7 +28041,7 @@
       </c>
     </row>
     <row r="774">
-      <c r="A774" t="inlineStr">
+      <c r="A774" s="1" t="inlineStr">
         <is>
           <t>15623</t>
         </is>
@@ -28788,7 +28074,7 @@
       </c>
     </row>
     <row r="775">
-      <c r="A775" t="inlineStr">
+      <c r="A775" s="1" t="inlineStr">
         <is>
           <t>17249</t>
         </is>
@@ -28821,7 +28107,7 @@
       </c>
     </row>
     <row r="776">
-      <c r="A776" t="inlineStr">
+      <c r="A776" s="1" t="inlineStr">
         <is>
           <t>16238</t>
         </is>
@@ -28854,7 +28140,7 @@
       </c>
     </row>
     <row r="777">
-      <c r="A777" t="inlineStr">
+      <c r="A777" s="1" t="inlineStr">
         <is>
           <t>16215</t>
         </is>
@@ -28887,7 +28173,7 @@
       </c>
     </row>
     <row r="778">
-      <c r="A778" t="inlineStr">
+      <c r="A778" s="1" t="inlineStr">
         <is>
           <t>16493</t>
         </is>
@@ -28925,7 +28211,7 @@
       </c>
     </row>
     <row r="779">
-      <c r="A779" t="inlineStr">
+      <c r="A779" s="1" t="inlineStr">
         <is>
           <t>16492</t>
         </is>
@@ -28963,7 +28249,7 @@
       </c>
     </row>
     <row r="780">
-      <c r="A780" t="inlineStr">
+      <c r="A780" s="1" t="inlineStr">
         <is>
           <t>16491</t>
         </is>
@@ -29001,7 +28287,7 @@
       </c>
     </row>
     <row r="781">
-      <c r="A781" t="inlineStr">
+      <c r="A781" s="1" t="inlineStr">
         <is>
           <t>15653</t>
         </is>
@@ -29039,7 +28325,7 @@
       </c>
     </row>
     <row r="782">
-      <c r="A782" t="inlineStr">
+      <c r="A782" s="1" t="inlineStr">
         <is>
           <t>16495</t>
         </is>
@@ -29077,7 +28363,7 @@
       </c>
     </row>
     <row r="783">
-      <c r="A783" t="inlineStr">
+      <c r="A783" s="1" t="inlineStr">
         <is>
           <t>15741</t>
         </is>
@@ -29115,7 +28401,7 @@
       </c>
     </row>
     <row r="784">
-      <c r="A784" t="inlineStr">
+      <c r="A784" s="1" t="inlineStr">
         <is>
           <t>17216</t>
         </is>
@@ -29138,11 +28424,6 @@
       <c r="E784" t="inlineStr">
         <is>
           <t>30-40cm</t>
-        </is>
-      </c>
-      <c r="F784" t="inlineStr">
-        <is>
-          <t>.0</t>
         </is>
       </c>
       <c r="G784" t="n">
@@ -29153,7 +28434,7 @@
       </c>
     </row>
     <row r="785">
-      <c r="A785" t="inlineStr">
+      <c r="A785" s="1" t="inlineStr">
         <is>
           <t>13272</t>
         </is>
@@ -29186,7 +28467,7 @@
       </c>
     </row>
     <row r="786">
-      <c r="A786" t="inlineStr">
+      <c r="A786" s="1" t="inlineStr">
         <is>
           <t>15651</t>
         </is>
@@ -29224,7 +28505,7 @@
       </c>
     </row>
     <row r="787">
-      <c r="A787" t="inlineStr">
+      <c r="A787" s="1" t="inlineStr">
         <is>
           <t>16490</t>
         </is>
@@ -29262,7 +28543,7 @@
       </c>
     </row>
     <row r="788">
-      <c r="A788" t="inlineStr">
+      <c r="A788" s="1" t="inlineStr">
         <is>
           <t>16489</t>
         </is>
@@ -29300,7 +28581,7 @@
       </c>
     </row>
     <row r="789">
-      <c r="A789" t="inlineStr">
+      <c r="A789" s="1" t="inlineStr">
         <is>
           <t>13273</t>
         </is>
@@ -29323,11 +28604,6 @@
       <c r="E789" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F789" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G789" t="n">
@@ -29338,7 +28614,7 @@
       </c>
     </row>
     <row r="790">
-      <c r="A790" t="inlineStr">
+      <c r="A790" s="1" t="inlineStr">
         <is>
           <t>15652</t>
         </is>
@@ -29376,7 +28652,7 @@
       </c>
     </row>
     <row r="791">
-      <c r="A791" t="inlineStr">
+      <c r="A791" s="1" t="inlineStr">
         <is>
           <t>16494</t>
         </is>
@@ -29414,7 +28690,7 @@
       </c>
     </row>
     <row r="792">
-      <c r="A792" t="inlineStr">
+      <c r="A792" s="1" t="inlineStr">
         <is>
           <t>17039</t>
         </is>
@@ -29452,7 +28728,7 @@
       </c>
     </row>
     <row r="793">
-      <c r="A793" t="inlineStr">
+      <c r="A793" s="1" t="inlineStr">
         <is>
           <t>17038</t>
         </is>
@@ -29490,7 +28766,7 @@
       </c>
     </row>
     <row r="794">
-      <c r="A794" t="inlineStr">
+      <c r="A794" s="1" t="inlineStr">
         <is>
           <t>11598</t>
         </is>
@@ -29528,7 +28804,7 @@
       </c>
     </row>
     <row r="795">
-      <c r="A795" t="inlineStr">
+      <c r="A795" s="1" t="inlineStr">
         <is>
           <t>16060</t>
         </is>
@@ -29561,7 +28837,7 @@
       </c>
     </row>
     <row r="796">
-      <c r="A796" t="inlineStr">
+      <c r="A796" s="1" t="inlineStr">
         <is>
           <t>17231</t>
         </is>
@@ -29594,7 +28870,7 @@
       </c>
     </row>
     <row r="797">
-      <c r="A797" t="inlineStr">
+      <c r="A797" s="1" t="inlineStr">
         <is>
           <t>12587</t>
         </is>
@@ -29627,7 +28903,7 @@
       </c>
     </row>
     <row r="798">
-      <c r="A798" t="inlineStr">
+      <c r="A798" s="1" t="inlineStr">
         <is>
           <t>16497</t>
         </is>
@@ -29665,7 +28941,7 @@
       </c>
     </row>
     <row r="799">
-      <c r="A799" t="inlineStr">
+      <c r="A799" s="1" t="inlineStr">
         <is>
           <t>16496</t>
         </is>
@@ -29703,7 +28979,7 @@
       </c>
     </row>
     <row r="800">
-      <c r="A800" t="inlineStr">
+      <c r="A800" s="1" t="inlineStr">
         <is>
           <t>11708</t>
         </is>
@@ -29726,11 +29002,6 @@
       <c r="E800" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F800" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G800" t="n">
@@ -29741,7 +29012,7 @@
       </c>
     </row>
     <row r="801">
-      <c r="A801" t="inlineStr">
+      <c r="A801" s="1" t="inlineStr">
         <is>
           <t>16498</t>
         </is>
@@ -29779,7 +29050,7 @@
       </c>
     </row>
     <row r="802">
-      <c r="A802" t="inlineStr">
+      <c r="A802" s="1" t="inlineStr">
         <is>
           <t>12195</t>
         </is>
@@ -29817,7 +29088,7 @@
       </c>
     </row>
     <row r="803">
-      <c r="A803" t="inlineStr">
+      <c r="A803" s="1" t="inlineStr">
         <is>
           <t>15704</t>
         </is>
@@ -29850,7 +29121,7 @@
       </c>
     </row>
     <row r="804">
-      <c r="A804" t="inlineStr">
+      <c r="A804" s="1" t="inlineStr">
         <is>
           <t>11280</t>
         </is>
@@ -29873,11 +29144,6 @@
       <c r="E804" t="inlineStr">
         <is>
           <t>200-225cm</t>
-        </is>
-      </c>
-      <c r="F804" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G804" t="n">
@@ -29888,7 +29154,7 @@
       </c>
     </row>
     <row r="805">
-      <c r="A805" t="inlineStr">
+      <c r="A805" s="1" t="inlineStr">
         <is>
           <t>17040</t>
         </is>
@@ -29926,7 +29192,7 @@
       </c>
     </row>
     <row r="806">
-      <c r="A806" t="inlineStr">
+      <c r="A806" s="1" t="inlineStr">
         <is>
           <t>17217</t>
         </is>
@@ -29949,11 +29215,6 @@
       <c r="E806" t="inlineStr">
         <is>
           <t>30-50cm</t>
-        </is>
-      </c>
-      <c r="F806" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G806" t="n">
@@ -29964,7 +29225,7 @@
       </c>
     </row>
     <row r="807">
-      <c r="A807" t="inlineStr">
+      <c r="A807" s="1" t="inlineStr">
         <is>
           <t>1586</t>
         </is>
@@ -30002,7 +29263,7 @@
       </c>
     </row>
     <row r="808">
-      <c r="A808" t="inlineStr">
+      <c r="A808" s="1" t="inlineStr">
         <is>
           <t>13274</t>
         </is>
@@ -30040,7 +29301,7 @@
       </c>
     </row>
     <row r="809">
-      <c r="A809" t="inlineStr">
+      <c r="A809" s="1" t="inlineStr">
         <is>
           <t>11046</t>
         </is>
@@ -30078,7 +29339,7 @@
       </c>
     </row>
     <row r="810">
-      <c r="A810" t="inlineStr">
+      <c r="A810" s="1" t="inlineStr">
         <is>
           <t>11282</t>
         </is>
@@ -30111,7 +29372,7 @@
       </c>
     </row>
     <row r="811">
-      <c r="A811" t="inlineStr">
+      <c r="A811" s="1" t="inlineStr">
         <is>
           <t>11156</t>
         </is>
@@ -30144,7 +29405,7 @@
       </c>
     </row>
     <row r="812">
-      <c r="A812" t="inlineStr">
+      <c r="A812" s="1" t="inlineStr">
         <is>
           <t>16421</t>
         </is>
@@ -30177,7 +29438,7 @@
       </c>
     </row>
     <row r="813">
-      <c r="A813" t="inlineStr">
+      <c r="A813" s="1" t="inlineStr">
         <is>
           <t>1592</t>
         </is>
@@ -30210,7 +29471,7 @@
       </c>
     </row>
     <row r="814">
-      <c r="A814" t="inlineStr">
+      <c r="A814" s="1" t="inlineStr">
         <is>
           <t>16233</t>
         </is>
@@ -30243,7 +29504,7 @@
       </c>
     </row>
     <row r="815">
-      <c r="A815" t="inlineStr">
+      <c r="A815" s="1" t="inlineStr">
         <is>
           <t>16062</t>
         </is>
@@ -30276,7 +29537,7 @@
       </c>
     </row>
     <row r="816">
-      <c r="A816" t="inlineStr">
+      <c r="A816" s="1" t="inlineStr">
         <is>
           <t>1144</t>
         </is>
@@ -30309,7 +29570,7 @@
       </c>
     </row>
     <row r="817">
-      <c r="A817" t="inlineStr">
+      <c r="A817" s="1" t="inlineStr">
         <is>
           <t>16323</t>
         </is>
@@ -30347,7 +29608,7 @@
       </c>
     </row>
     <row r="818">
-      <c r="A818" t="inlineStr">
+      <c r="A818" s="1" t="inlineStr">
         <is>
           <t>1145</t>
         </is>
@@ -30370,11 +29631,6 @@
       <c r="E818" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F818" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G818" t="n">
@@ -30385,7 +29641,7 @@
       </c>
     </row>
     <row r="819">
-      <c r="A819" t="inlineStr">
+      <c r="A819" s="1" t="inlineStr">
         <is>
           <t>12603</t>
         </is>
@@ -30418,7 +29674,7 @@
       </c>
     </row>
     <row r="820">
-      <c r="A820" t="inlineStr">
+      <c r="A820" s="1" t="inlineStr">
         <is>
           <t>16298</t>
         </is>
@@ -30451,7 +29707,7 @@
       </c>
     </row>
     <row r="821">
-      <c r="A821" t="inlineStr">
+      <c r="A821" s="1" t="inlineStr">
         <is>
           <t>10862</t>
         </is>
@@ -30484,7 +29740,7 @@
       </c>
     </row>
     <row r="822">
-      <c r="A822" t="inlineStr">
+      <c r="A822" s="1" t="inlineStr">
         <is>
           <t>16332</t>
         </is>
@@ -30517,7 +29773,7 @@
       </c>
     </row>
     <row r="823">
-      <c r="A823" t="inlineStr">
+      <c r="A823" s="1" t="inlineStr">
         <is>
           <t>16251</t>
         </is>
@@ -30550,7 +29806,7 @@
       </c>
     </row>
     <row r="824">
-      <c r="A824" t="inlineStr">
+      <c r="A824" s="1" t="inlineStr">
         <is>
           <t>15742</t>
         </is>
@@ -30588,7 +29844,7 @@
       </c>
     </row>
     <row r="825">
-      <c r="A825" t="inlineStr">
+      <c r="A825" s="1" t="inlineStr">
         <is>
           <t>11634</t>
         </is>
@@ -30626,7 +29882,7 @@
       </c>
     </row>
     <row r="826">
-      <c r="A826" t="inlineStr">
+      <c r="A826" s="1" t="inlineStr">
         <is>
           <t>17044</t>
         </is>
@@ -30664,7 +29920,7 @@
       </c>
     </row>
     <row r="827">
-      <c r="A827" t="inlineStr">
+      <c r="A827" s="1" t="inlineStr">
         <is>
           <t>17043</t>
         </is>
@@ -30702,7 +29958,7 @@
       </c>
     </row>
     <row r="828">
-      <c r="A828" t="inlineStr">
+      <c r="A828" s="1" t="inlineStr">
         <is>
           <t>11526</t>
         </is>
@@ -30740,7 +29996,7 @@
       </c>
     </row>
     <row r="829">
-      <c r="A829" t="inlineStr">
+      <c r="A829" s="1" t="inlineStr">
         <is>
           <t>16286</t>
         </is>
@@ -30763,11 +30019,6 @@
       <c r="E829" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F829" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G829" t="n">
@@ -30778,7 +30029,7 @@
       </c>
     </row>
     <row r="830">
-      <c r="A830" t="inlineStr">
+      <c r="A830" s="1" t="inlineStr">
         <is>
           <t>17218</t>
         </is>
@@ -30816,7 +30067,7 @@
       </c>
     </row>
     <row r="831">
-      <c r="A831" t="inlineStr">
+      <c r="A831" s="1" t="inlineStr">
         <is>
           <t>16085</t>
         </is>
@@ -30839,11 +30090,6 @@
       <c r="E831" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F831" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G831" t="n">
@@ -30854,7 +30100,7 @@
       </c>
     </row>
     <row r="832">
-      <c r="A832" t="inlineStr">
+      <c r="A832" s="1" t="inlineStr">
         <is>
           <t>16499</t>
         </is>
@@ -30892,7 +30138,7 @@
       </c>
     </row>
     <row r="833">
-      <c r="A833" t="inlineStr">
+      <c r="A833" s="1" t="inlineStr">
         <is>
           <t>16270</t>
         </is>
@@ -30930,7 +30176,7 @@
       </c>
     </row>
     <row r="834">
-      <c r="A834" t="inlineStr">
+      <c r="A834" s="1" t="inlineStr">
         <is>
           <t>10713</t>
         </is>
@@ -30968,7 +30214,7 @@
       </c>
     </row>
     <row r="835">
-      <c r="A835" t="inlineStr">
+      <c r="A835" s="1" t="inlineStr">
         <is>
           <t>1603</t>
         </is>
@@ -31006,7 +30252,7 @@
       </c>
     </row>
     <row r="836">
-      <c r="A836" t="inlineStr">
+      <c r="A836" s="1" t="inlineStr">
         <is>
           <t>16287</t>
         </is>
@@ -31029,11 +30275,6 @@
       <c r="E836" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F836" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G836" t="n">
@@ -31044,7 +30285,7 @@
       </c>
     </row>
     <row r="837">
-      <c r="A837" t="inlineStr">
+      <c r="A837" s="1" t="inlineStr">
         <is>
           <t>13194</t>
         </is>
@@ -31082,7 +30323,7 @@
       </c>
     </row>
     <row r="838">
-      <c r="A838" t="inlineStr">
+      <c r="A838" s="1" t="inlineStr">
         <is>
           <t>12404</t>
         </is>
@@ -31105,11 +30346,6 @@
       <c r="E838" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F838" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G838" t="n">
@@ -31120,7 +30356,7 @@
       </c>
     </row>
     <row r="839">
-      <c r="A839" t="inlineStr">
+      <c r="A839" s="1" t="inlineStr">
         <is>
           <t>11008</t>
         </is>
@@ -31158,7 +30394,7 @@
       </c>
     </row>
     <row r="840">
-      <c r="A840" t="inlineStr">
+      <c r="A840" s="1" t="inlineStr">
         <is>
           <t>17220</t>
         </is>
@@ -31196,7 +30432,7 @@
       </c>
     </row>
     <row r="841">
-      <c r="A841" t="inlineStr">
+      <c r="A841" s="1" t="inlineStr">
         <is>
           <t>13275</t>
         </is>
@@ -31219,11 +30455,6 @@
       <c r="E841" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F841" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G841" t="n">
@@ -31234,7 +30465,7 @@
       </c>
     </row>
     <row r="842">
-      <c r="A842" t="inlineStr">
+      <c r="A842" s="1" t="inlineStr">
         <is>
           <t>16284</t>
         </is>
@@ -31272,7 +30503,7 @@
       </c>
     </row>
     <row r="843">
-      <c r="A843" t="inlineStr">
+      <c r="A843" s="1" t="inlineStr">
         <is>
           <t>13994</t>
         </is>
@@ -31310,7 +30541,7 @@
       </c>
     </row>
     <row r="844">
-      <c r="A844" t="inlineStr">
+      <c r="A844" s="1" t="inlineStr">
         <is>
           <t>11169</t>
         </is>
@@ -31348,7 +30579,7 @@
       </c>
     </row>
     <row r="845">
-      <c r="A845" t="inlineStr">
+      <c r="A845" s="1" t="inlineStr">
         <is>
           <t>13995</t>
         </is>
@@ -31386,7 +30617,7 @@
       </c>
     </row>
     <row r="846">
-      <c r="A846" t="inlineStr">
+      <c r="A846" s="1" t="inlineStr">
         <is>
           <t>10895</t>
         </is>
@@ -31424,7 +30655,7 @@
       </c>
     </row>
     <row r="847">
-      <c r="A847" t="inlineStr">
+      <c r="A847" s="1" t="inlineStr">
         <is>
           <t>10894</t>
         </is>
@@ -31447,11 +30678,6 @@
       <c r="E847" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F847" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G847" t="n">
@@ -31462,7 +30688,7 @@
       </c>
     </row>
     <row r="848">
-      <c r="A848" t="inlineStr">
+      <c r="A848" s="1" t="inlineStr">
         <is>
           <t>16331</t>
         </is>
@@ -31495,7 +30721,7 @@
       </c>
     </row>
     <row r="849">
-      <c r="A849" t="inlineStr">
+      <c r="A849" s="1" t="inlineStr">
         <is>
           <t>11779</t>
         </is>
@@ -31528,7 +30754,7 @@
       </c>
     </row>
     <row r="850">
-      <c r="A850" t="inlineStr">
+      <c r="A850" s="1" t="inlineStr">
         <is>
           <t>16318</t>
         </is>
@@ -31561,7 +30787,7 @@
       </c>
     </row>
     <row r="851">
-      <c r="A851" t="inlineStr">
+      <c r="A851" s="1" t="inlineStr">
         <is>
           <t>14423</t>
         </is>
@@ -31599,7 +30825,7 @@
       </c>
     </row>
     <row r="852">
-      <c r="A852" t="inlineStr">
+      <c r="A852" s="1" t="inlineStr">
         <is>
           <t>11601</t>
         </is>
@@ -31637,7 +30863,7 @@
       </c>
     </row>
     <row r="853">
-      <c r="A853" t="inlineStr">
+      <c r="A853" s="1" t="inlineStr">
         <is>
           <t>11034</t>
         </is>
@@ -31675,7 +30901,7 @@
       </c>
     </row>
     <row r="854">
-      <c r="A854" t="inlineStr">
+      <c r="A854" s="1" t="inlineStr">
         <is>
           <t>17361</t>
         </is>
@@ -31708,7 +30934,7 @@
       </c>
     </row>
     <row r="855">
-      <c r="A855" t="inlineStr">
+      <c r="A855" s="1" t="inlineStr">
         <is>
           <t>12562</t>
         </is>
@@ -31741,7 +30967,7 @@
       </c>
     </row>
     <row r="856">
-      <c r="A856" t="inlineStr">
+      <c r="A856" s="1" t="inlineStr">
         <is>
           <t>1615</t>
         </is>
@@ -31779,7 +31005,7 @@
       </c>
     </row>
     <row r="857">
-      <c r="A857" t="inlineStr">
+      <c r="A857" s="1" t="inlineStr">
         <is>
           <t>11709</t>
         </is>
@@ -31817,7 +31043,7 @@
       </c>
     </row>
     <row r="858">
-      <c r="A858" t="inlineStr">
+      <c r="A858" s="1" t="inlineStr">
         <is>
           <t>11168</t>
         </is>

--- a/files/availability-list-2026.xlsx
+++ b/files/availability-list-2026.xlsx
@@ -148,6 +148,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -498,7 +501,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abies Alba</t>
+          <t>Abies alba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -531,7 +534,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abies Concolor</t>
+          <t>Abies concolor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -564,7 +567,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abies Concolor</t>
+          <t>Abies concolor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -597,7 +600,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Abies Fraseri</t>
+          <t>Abies fraseri</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -630,7 +633,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Abies Grandis</t>
+          <t>Abies grandis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -663,7 +666,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abies Grandis</t>
+          <t>Abies grandis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -696,7 +699,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Abies Grandis</t>
+          <t>Abies grandis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -729,7 +732,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abies Koreana</t>
+          <t>Abies koreana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,7 +765,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Abies Koreana</t>
+          <t>Abies koreana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -795,7 +798,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abies Koreana</t>
+          <t>Abies koreana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -828,7 +831,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Abies Koreana</t>
+          <t>Abies koreana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -861,7 +864,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abies Lasiocarpa</t>
+          <t>Abies lasiocarpa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -894,7 +897,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abies Nobilis</t>
+          <t>Abies nobilis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -927,7 +930,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abies Nordmanniana</t>
+          <t>Abies nordmanniana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -960,7 +963,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abies Nordmanniana</t>
+          <t>Abies nordmanniana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -993,7 +996,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abies Nordmanniana</t>
+          <t>Abies nordmanniana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1026,7 +1029,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abies Pinsapo</t>
+          <t>Abies pinsapo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1059,7 +1062,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abies Pinsapo</t>
+          <t>Abies pinsapo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1092,7 +1095,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Acacia Dealbata</t>
+          <t>Acacia dealbata</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1125,7 +1128,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Acacia Melanoxylon</t>
+          <t>Acacia melanoxylon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1229,7 +1232,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Acer Buergerianum</t>
+          <t>Acer buergerianum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1267,7 +1270,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Acer Buergerianum</t>
+          <t>Acer buergerianum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1300,7 +1303,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Acer Campestre</t>
+          <t>Acer campestre</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1338,7 +1341,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Acer Campestre</t>
+          <t>Acer campestre</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1376,7 +1379,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Acer Campestre</t>
+          <t>Acer campestre</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1414,7 +1417,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Acer Campestre</t>
+          <t>Acer campestre</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1430,11 +1433,6 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1452,7 +1450,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Acer Campestre</t>
+          <t>Acer campestre</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1485,7 +1483,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Acer Campestre ‘Elsrijk’</t>
+          <t>Acer campestre</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1523,7 +1521,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Acer Campestre 'Queen Elizabeth'</t>
+          <t>Acer campestre 'Queen Elizabeth'</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1561,7 +1559,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Acer Campestre 'Queen Elizabeth'</t>
+          <t>Acer campestre 'Queen Elizabeth'</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1599,7 +1597,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Acer Campestre 'Red Shine'</t>
+          <t>Acer campestre 'Red Shine'</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1632,7 +1630,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Acer Campestre 'Red Shine'</t>
+          <t>Acer campestre 'Red Shine'</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1648,11 +1646,6 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>250-300cm</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1670,7 +1663,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Acer Campestre 'Red Shine'</t>
+          <t>Acer campestre 'Red Shine'</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1708,7 +1701,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Acer Cappadocicum 'Aureum'</t>
+          <t>Acer cappadocicum 'Aureum'</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1741,7 +1734,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Acer Cappadocicum 'Aureum'</t>
+          <t>Acer cappadocicum 'Aureum'</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1779,7 +1772,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Acer Cappadocicum 'Rubrum'</t>
+          <t>Acer cappadocicum 'Rubrum'</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1812,7 +1805,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Acer Carpinifolium</t>
+          <t>Acer carpinifolium</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1845,7 +1838,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Acer Davidii</t>
+          <t>Acer davidii</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1878,7 +1871,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Acer Davidii</t>
+          <t>Acer davidii</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1916,7 +1909,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Acer Davidii</t>
+          <t>Acer davidii</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1954,7 +1947,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Acer Davidii</t>
+          <t>Acer davidii</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1992,7 +1985,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Acer Davidii</t>
+          <t>Acer davidii</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2030,7 +2023,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Acer Freemanii 'Armstrong'</t>
+          <t>Acer freemanii 'Armstrong'</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2068,7 +2061,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Acer Freemanii 'Armstrong'</t>
+          <t>Acer freemanii 'Armstrong'</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2106,7 +2099,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Acer Freemanii 'Autumn Blaze' ('Jeffersred')</t>
+          <t>Acer freemanii 'Autumn Blaze'</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2122,11 +2115,6 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>140-160cm</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2144,7 +2132,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Acer Freemanii 'Autumn Blaze' ('Jeffersred')</t>
+          <t>Acer freemanii 'Autumn Blaze'</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2160,11 +2148,6 @@
       <c r="E50" t="inlineStr">
         <is>
           <t>150-200 cm</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2182,7 +2165,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Acer Freemanii 'Autumn Blaze' ('Jeffersred')</t>
+          <t>Acer freemanii 'Autumn Blaze'</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2198,11 +2181,6 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>250-300cm</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2220,7 +2198,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Acer Freemanii 'Autumn Blaze' ('Jeffersred')</t>
+          <t>Acer freemanii 'Autumn Blaze'</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2258,7 +2236,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Acer Freemanii 'Autumn Blaze' ('Jeffersred')</t>
+          <t>Acer freemanii 'Autumn Blaze'</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2296,7 +2274,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Acer Freemanii 'Autumn Blaze' ('Jeffersred')</t>
+          <t>Acer freemanii 'Autumn Blaze'</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2334,7 +2312,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Acer Freemanii 'Autumn Blaze' ('Jeffersred')</t>
+          <t>Acer freemanii 'Autumn Blaze'</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2372,7 +2350,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Acer Freemanii 'Autumn Blaze' ('Jeffersred')</t>
+          <t>Acer freemanii 'Autumn Blaze'</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2410,7 +2388,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Acer Freemanii 'Autumn Blaze' ('Jeffersred')</t>
+          <t>Acer freemanii 'Autumn Blaze'</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2426,11 +2404,6 @@
       <c r="E57" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>'0</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2448,7 +2421,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Acer Freemanii 'Celebration'</t>
+          <t>Acer freemanii 'Celebration'</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2486,7 +2459,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Acer Freemanii 'Celebration'</t>
+          <t>Acer freemanii 'Celebration'</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2519,7 +2492,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Acer Ginnala</t>
+          <t>Acer ginnala</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2552,7 +2525,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Acer Ginnala</t>
+          <t>Acer ginnala</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2590,7 +2563,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Acer Griseum</t>
+          <t>Acer griseum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2606,11 +2579,6 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -2628,7 +2596,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Acer Griseum</t>
+          <t>Acer griseum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2661,7 +2629,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Acer Griseum</t>
+          <t>Acer griseum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2677,11 +2645,6 @@
       <c r="E64" t="inlineStr">
         <is>
           <t>60-80cm</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -2699,7 +2662,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Acer Monspessulanum</t>
+          <t>Acer monspessulanum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2732,7 +2695,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Acer Monspessulanum</t>
+          <t>Acer monspessulanum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2770,7 +2733,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Acer Negundo 'Flamingo'</t>
+          <t>Acer negundo 'Flamingo'</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2803,7 +2766,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Acer Negundo 'Flamingo'</t>
+          <t>Acer negundo 'Flamingo'</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2841,7 +2804,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Acer Negundo 'Flamingo'</t>
+          <t>Acer negundo 'Flamingo'</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2874,7 +2837,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Acer Palmatum 'Aureum'</t>
+          <t>Acer palmatum 'Aureum'</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2907,7 +2870,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Acer Palmatum ‘Bloodgood’</t>
+          <t>Acer palmatum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2940,7 +2903,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Acer Palmatum 'Crimson Queen'</t>
+          <t>Acer palmatum 'Crimson Queen'</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2973,7 +2936,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Acer Palmatum ‘Fireglow’</t>
+          <t>Acer palmatum</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3006,7 +2969,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Acer Palmatum 'Skeeter's Broom'</t>
+          <t>Acer palmatum 'Skeeter'</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3039,7 +3002,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Acer Plat.</t>
+          <t>Acer plat.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3055,11 +3018,6 @@
       <c r="E75" t="inlineStr">
         <is>
           <t>250 -300cm</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -3077,7 +3035,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Acer Plat.</t>
+          <t>Acer plat.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3115,7 +3073,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Acer Plat.</t>
+          <t>Acer plat.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3153,7 +3111,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Acer Plat.</t>
+          <t>Acer plat.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3191,7 +3149,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Acer Plat.</t>
+          <t>Acer plat.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3229,7 +3187,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Acer Plat.</t>
+          <t>Acer plat.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3267,7 +3225,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Acer Plat. ‘Columnare’</t>
+          <t>Acer plat.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3305,7 +3263,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Acer Plat. ‘Columnare’</t>
+          <t>Acer plat.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3343,7 +3301,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Crimson King'</t>
+          <t>Acer plat. 'Crimson King'</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3359,11 +3317,6 @@
       <c r="E83" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -3381,7 +3334,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Crimson King'</t>
+          <t>Acer plat. 'Crimson King'</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3419,7 +3372,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Crimson Sentry'</t>
+          <t>Acer plat. 'Crimson Sentry'</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3452,7 +3405,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Crimson Sentry'</t>
+          <t>Acer plat. 'Crimson Sentry'</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3490,7 +3443,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Crimson Sentry'</t>
+          <t>Acer plat. 'Crimson Sentry'</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3528,7 +3481,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Drummondii'</t>
+          <t>Acer plat. 'Drummondii'</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3561,7 +3514,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Drummondii'</t>
+          <t>Acer plat. 'Drummondii'</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3599,7 +3552,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Drummondii'</t>
+          <t>Acer plat. 'Drummondii'</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3637,7 +3590,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Emerald Queen'</t>
+          <t>Acer plat. 'Emerald Queen'</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3670,7 +3623,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Emerald Queen'</t>
+          <t>Acer plat. 'Emerald Queen'</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3703,7 +3656,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Lorbergii'</t>
+          <t>Acer plat. 'Lorbergii'</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3741,7 +3694,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Lorbergii'</t>
+          <t>Acer plat. 'Lorbergii'</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3779,7 +3732,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Princeton Gold'</t>
+          <t>Acer plat. 'Princeton Gold'</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3817,7 +3770,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Royal Red'</t>
+          <t>Acer plat. 'Royal Red'</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3833,11 +3786,6 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>20-30cm</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -3855,7 +3803,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Royal Red'</t>
+          <t>Acer plat. 'Royal Red'</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3888,7 +3836,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Acer Plat. 'Royal Red'</t>
+          <t>Acer plat. 'Royal Red'</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3926,7 +3874,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Acer Pseudoplatanus</t>
+          <t>Acer pseudoplatanus</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3959,7 +3907,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Acer Pseudoplatanus</t>
+          <t>Acer pseudoplatanus</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3997,7 +3945,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Acer Pseudoplatanus</t>
+          <t>Acer pseudoplatanus</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4035,7 +3983,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Acer Pseudoplatanus</t>
+          <t>Acer pseudoplatanus</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4073,7 +4021,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Acer Pseudoplatanus</t>
+          <t>Acer pseudoplatanus</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4111,7 +4059,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Acer Pseudoplatanus</t>
+          <t>Acer pseudoplatanus</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4149,7 +4097,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Acer Pseudoplatanus ‘Leopoldii’</t>
+          <t>Acer pseudoplatanus</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4165,11 +4113,6 @@
       <c r="E105" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -4187,7 +4130,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Acer Pseudoplatanus ‘Leopoldii’</t>
+          <t>Acer pseudoplatanus</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4220,7 +4163,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Acer Pseudoplatanus 'Spaethii'</t>
+          <t>Acer pseudoplatanus 'Spaethii'</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4258,7 +4201,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Acer Pseudoplatanus 'Spaethii'</t>
+          <t>Acer pseudoplatanus 'Spaethii'</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4296,7 +4239,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Acer Pseudoplatanus 'Spaethii'</t>
+          <t>Acer pseudoplatanus 'Spaethii'</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4334,7 +4277,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Acer Pseudoplatanus 'Spaethii'</t>
+          <t>Acer pseudoplatanus 'Spaethii'</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4372,7 +4315,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Acer Rubrum</t>
+          <t>Acer rubrum</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4405,7 +4348,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Acer Rubrum</t>
+          <t>Acer rubrum</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4443,7 +4386,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Acer Rubrum</t>
+          <t>Acer rubrum</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4481,7 +4424,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Acer Rubrum</t>
+          <t>Acer rubrum</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4519,7 +4462,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Acer Rubrum 'Fairview Flame'</t>
+          <t>Acer rubrum 'Fairview Flame'</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4557,7 +4500,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Acer Rubrum 'Fairview Flame'</t>
+          <t>Acer rubrum 'Fairview Flame'</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4595,7 +4538,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Acer Rubrum 'Fairview Flame'</t>
+          <t>Acer rubrum 'Fairview Flame'</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4633,7 +4576,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Acer Rubrum 'October Glory'</t>
+          <t>Acer rubrum 'October Glory'</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4649,11 +4592,6 @@
       <c r="E118" t="inlineStr">
         <is>
           <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -4671,7 +4609,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Acer Rubrum 'October Glory'</t>
+          <t>Acer rubrum 'October Glory'</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4704,7 +4642,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Acer Rubrum 'October Glory'</t>
+          <t>Acer rubrum 'October Glory'</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4742,7 +4680,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Acer Rubrum 'October Glory'</t>
+          <t>Acer rubrum 'October Glory'</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4780,7 +4718,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Acer Rubrum 'October Glory'</t>
+          <t>Acer rubrum 'October Glory'</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4796,11 +4734,6 @@
       <c r="E122" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -4818,7 +4751,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Acer Rubrum 'Red Sunset'</t>
+          <t>Acer rubrum 'Red Sunset'</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4856,7 +4789,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Acer Rubrum 'Red Sunset'</t>
+          <t>Acer rubrum 'Red Sunset'</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4894,7 +4827,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Acer Rubrum 'Red Sunset'</t>
+          <t>Acer rubrum 'Red Sunset'</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4932,7 +4865,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Acer Rubrum 'Sun Valley'</t>
+          <t>Acer rubrum 'Sun Valley'</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4970,7 +4903,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Acer Rubrum 'Sun Valley'</t>
+          <t>Acer rubrum 'Sun Valley'</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5008,7 +4941,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Acer Saccharinum 'Born's Gracious'</t>
+          <t>Acer saccharinum 'Born'</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5046,7 +4979,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Acer Saccharinum 'Born's Gracious'</t>
+          <t>Acer saccharinum 'Born'</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5084,7 +5017,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Acer Saccharinum Pyramidale</t>
+          <t>Acer saccharinum</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5100,11 +5033,6 @@
       <c r="E130" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -5122,7 +5050,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Acer Saccharinum Pyramidale</t>
+          <t>Acer saccharinum</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5160,7 +5088,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Acer Saccharinum Pyramidale</t>
+          <t>Acer saccharinum</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5198,7 +5126,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Acer Saccharinum Pyramidale</t>
+          <t>Acer saccharinum</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5236,7 +5164,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Acer Saccharinum Pyramidale</t>
+          <t>Acer saccharinum</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5274,7 +5202,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Acer Saccharinum Pyramidale</t>
+          <t>Acer saccharinum</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5312,7 +5240,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Acer Saccharinum Pyramidale</t>
+          <t>Acer saccharinum</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5350,7 +5278,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Aesculus Hippocastanum</t>
+          <t>Aesculus hippocastanum</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5388,7 +5316,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Aesculus Hippocastanum</t>
+          <t>Aesculus hippocastanum</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5404,11 +5332,6 @@
       <c r="E138" t="inlineStr">
         <is>
           <t>200-225cm</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -5426,7 +5349,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Aesculus Hippocastanum</t>
+          <t>Aesculus hippocastanum</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5459,7 +5382,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Aesculus Hippocastanum 'Laciniata'</t>
+          <t>Aesculus hippocastanum 'Laciniata'</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5492,7 +5415,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Aesculus Indica</t>
+          <t>Aesculus indica</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5525,7 +5448,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Aesculus X Carnea 'Briotii'</t>
+          <t>Aesculus x 'Briotii'</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5558,7 +5481,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Albizia Julibrissin</t>
+          <t>Albizia julibrissin</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5591,7 +5514,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Alnus Cordata</t>
+          <t>Alnus cordata</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5624,7 +5547,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Alnus Cordata</t>
+          <t>Alnus cordata</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5662,7 +5585,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Alnus Cordata</t>
+          <t>Alnus cordata</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5700,7 +5623,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Alnus Cordata</t>
+          <t>Alnus cordata</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5738,7 +5661,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Alnus Glutinosa</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5776,7 +5699,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Alnus Glutinosa</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5814,7 +5737,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Alnus Glutinosa 'Aurea'</t>
+          <t>Alnus glutinosa 'Aurea'</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5852,7 +5775,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Alnus Glutinosa ‘Imperialis’</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5885,7 +5808,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Alnus Glutinosa ‘Imperialis’</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5923,7 +5846,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Alnus Glutinosa ‘Imperialis’</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5961,7 +5884,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Alnus Glutinosa ‘Imperialis’</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5999,7 +5922,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Alnus Glutinosa ‘Imperialis’</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6037,7 +5960,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Alnus Glutinosa ‘Imperialis’</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6075,7 +5998,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Alnus Glutinosa 'Laciniata'</t>
+          <t>Alnus glutinosa 'Laciniata'</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6108,7 +6031,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Alnus Glutinosa 'Laciniata'</t>
+          <t>Alnus glutinosa 'Laciniata'</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6146,7 +6069,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Alnus Glutinosa 'Laciniata'</t>
+          <t>Alnus glutinosa 'Laciniata'</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6184,7 +6107,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Alnus Glutinosa 'Laciniata'</t>
+          <t>Alnus glutinosa 'Laciniata'</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6222,7 +6145,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Alnus Incana 'Aurea'</t>
+          <t>Alnus incana 'Aurea'</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6255,7 +6178,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Alnus X Spaethii</t>
+          <t>Alnus x</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6288,7 +6211,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Alnus X Spaethii</t>
+          <t>Alnus x</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6430,7 +6353,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Amelanchier Alnifolia 'Obelisk'</t>
+          <t>Amelanchier alnifolia 'Obelisk'</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6463,7 +6386,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Amelanchier Alnifolia 'Obelisk'</t>
+          <t>Amelanchier alnifolia 'Obelisk'</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6496,7 +6419,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Amelanchier Canadensis</t>
+          <t>Amelanchier canadensis</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6529,7 +6452,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Amelanchier Canadensis 'Prince William'</t>
+          <t>Amelanchier canadensis 'Prince William'</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6562,7 +6485,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Amelanchier Lamarckii</t>
+          <t>Amelanchier lamarckii</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6595,7 +6518,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Amelanchier Lamarckii</t>
+          <t>Amelanchier lamarckii</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6611,11 +6534,6 @@
       <c r="E172" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -6633,7 +6551,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Amelanchier Lamarckii</t>
+          <t>Amelanchier lamarckii</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6666,7 +6584,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Amelanchier Lamarckii</t>
+          <t>Amelanchier lamarckii</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6704,7 +6622,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Amelanchier Lamarckii</t>
+          <t>Amelanchier lamarckii</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6737,7 +6655,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Amelanchier Lamarckii</t>
+          <t>Amelanchier lamarckii</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6775,7 +6693,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Amelanchier Lamarckii</t>
+          <t>Amelanchier lamarckii</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6813,7 +6731,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Amelanchier Lamarckii</t>
+          <t>Amelanchier lamarckii</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6851,7 +6769,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Amelanchier Lamarckii</t>
+          <t>Amelanchier lamarckii</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6889,7 +6807,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Aralia Elata</t>
+          <t>Aralia elata</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6922,7 +6840,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Aralia Elata</t>
+          <t>Aralia elata</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6955,7 +6873,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Aralia Elata</t>
+          <t>Aralia elata</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6988,7 +6906,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Araucaria Araucana</t>
+          <t>Araucaria araucana</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7021,7 +6939,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Arbutus Unedo</t>
+          <t>Arbutus unedo</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7059,7 +6977,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Arbutus Unedo</t>
+          <t>Arbutus unedo</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7075,11 +6993,6 @@
       <c r="E185" t="inlineStr">
         <is>
           <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -7097,7 +7010,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Bamboo Pseudosasa 'Japonica'</t>
+          <t>Bamboo pseudosasa 'Japonica'</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7130,7 +7043,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Betula Albosinensis 'Fascination'</t>
+          <t>Betula albosinensis 'Fascination'</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7168,7 +7081,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Betula Albosinensis 'Fascination'</t>
+          <t>Betula albosinensis 'Fascination'</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7206,7 +7119,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Betula Albosinensis 'Fascination'</t>
+          <t>Betula albosinensis 'Fascination'</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7244,7 +7157,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Betula Albosinensis 'Fascination'</t>
+          <t>Betula albosinensis 'Fascination'</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7282,7 +7195,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Betula Albosinensis Septentrionalis</t>
+          <t>Betula albosinensis</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7320,7 +7233,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Betula Ermanii</t>
+          <t>Betula ermanii</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7353,7 +7266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Betula Ermanii</t>
+          <t>Betula ermanii</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7386,7 +7299,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Betula Nigra</t>
+          <t>Betula nigra</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7424,7 +7337,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Betula Nigra</t>
+          <t>Betula nigra</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7462,7 +7375,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Betula Nigra</t>
+          <t>Betula nigra</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7500,7 +7413,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Betula Nigra</t>
+          <t>Betula nigra</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7516,11 +7429,6 @@
       <c r="E197" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -7538,7 +7446,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Betula Papyrifera</t>
+          <t>Betula papyrifera</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7571,7 +7479,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Betula Papyrifera</t>
+          <t>Betula papyrifera</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7604,7 +7512,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Betula Papyrifera</t>
+          <t>Betula papyrifera</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7642,7 +7550,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Betula Pendula</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7658,11 +7566,6 @@
       <c r="E201" t="inlineStr">
         <is>
           <t>150-175cm</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -7680,7 +7583,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Betula Pendula</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7713,7 +7616,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Betula Pendula</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7751,7 +7654,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Betula Pendula</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7789,7 +7692,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Betula Pendula</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7827,7 +7730,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Betula Pendula</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7865,7 +7768,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Betula Pendula</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7903,7 +7806,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Betula Pendula</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7941,7 +7844,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Betula Pendula</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7979,7 +7882,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Betula Pendula</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -8017,7 +7920,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Betula Pendula</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -8050,7 +7953,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Betula Pendula</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8088,7 +7991,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Betula Pendula</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8126,7 +8029,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Betula Pendula</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -8159,7 +8062,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Betula Pendula 'Fastigiata Joes'</t>
+          <t>Betula pendula 'Fastigiata Joes'</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8197,7 +8100,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Betula Pendula 'Fastigiata Joes'</t>
+          <t>Betula pendula 'Fastigiata Joes'</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -8230,7 +8133,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Betula Pendula 'Fastigiata'</t>
+          <t>Betula pendula 'Fastigiata'</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8263,7 +8166,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Betula Pendula 'Fastigiata'</t>
+          <t>Betula pendula 'Fastigiata'</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8296,7 +8199,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Betula Pendula ‘Tristis’</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8312,11 +8215,6 @@
       <c r="E219" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -8334,7 +8232,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Betula Pendula ‘Tristis’</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8367,7 +8265,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Betula Pendula ‘Tristis’</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8405,7 +8303,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Betula Pendula ‘Tristis’</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8443,7 +8341,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Betula Pendula 'Youngii'</t>
+          <t>Betula pendula 'Youngii'</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8459,11 +8357,6 @@
       <c r="E223" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -8481,7 +8374,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Betula Pendula 'Youngii'</t>
+          <t>Betula pendula 'Youngii'</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8497,11 +8390,6 @@
       <c r="E224" t="inlineStr">
         <is>
           <t>150-175cm</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -8519,7 +8407,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Betula Pendula 'Youngii'</t>
+          <t>Betula pendula 'Youngii'</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8552,7 +8440,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Betula Pubescens</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8568,11 +8456,6 @@
       <c r="E226" t="inlineStr">
         <is>
           <t>120-140cm</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -8590,7 +8473,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Betula Pubescens</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8628,7 +8511,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Betula Pubescens</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8661,7 +8544,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Betula Pubescens</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8699,7 +8582,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Betula Pubescens</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8737,7 +8620,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Betula Pubescens</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8775,7 +8658,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Betula Pubescens</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8813,7 +8696,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Betula Utilis 'Doorenbos'</t>
+          <t>Betula utilis 'Doorenbos'</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8846,7 +8729,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Betula Utilis 'Doorenbos'</t>
+          <t>Betula utilis 'Doorenbos'</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8862,11 +8745,6 @@
       <c r="E234" t="inlineStr">
         <is>
           <t>150-175cm</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -8884,7 +8762,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Betula Utilis 'Doorenbos'</t>
+          <t>Betula utilis 'Doorenbos'</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8917,7 +8795,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Betula Utilis 'Doorenbos'</t>
+          <t>Betula utilis 'Doorenbos'</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8950,7 +8828,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Betula Utilis 'Edinburgh'</t>
+          <t>Betula utilis 'Edinburgh'</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8983,7 +8861,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Betula Utilis 'Edinburgh'</t>
+          <t>Betula utilis 'Edinburgh'</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -9021,7 +8899,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Betula Utilis 'Edinburgh'</t>
+          <t>Betula utilis 'Edinburgh'</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9059,7 +8937,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Betula Utilis 'Edinburgh'</t>
+          <t>Betula utilis 'Edinburgh'</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -9097,7 +8975,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Betula Utilis 'Nepalese Orange'</t>
+          <t>Betula utilis 'Nepalese Orange'</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -9130,7 +9008,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Betula Utilis Jacquemontii</t>
+          <t>Betula utilis</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9163,7 +9041,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Betula Utilis Jacquemontii</t>
+          <t>Betula utilis</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9196,7 +9074,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Betula Utilis Jacquemontii</t>
+          <t>Betula utilis</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9234,7 +9112,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Fastigiata'</t>
+          <t>Carpinus bet. 'Fastigiata'</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -9250,11 +9128,6 @@
       <c r="E245" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -9272,7 +9145,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Fastigiata'</t>
+          <t>Carpinus bet. 'Fastigiata'</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9305,7 +9178,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Fastigiata'</t>
+          <t>Carpinus bet. 'Fastigiata'</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9338,7 +9211,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Fastigiata'</t>
+          <t>Carpinus bet. 'Fastigiata'</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9376,7 +9249,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Fastigiata'</t>
+          <t>Carpinus bet. 'Fastigiata'</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9414,7 +9287,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Frans Fontaine'</t>
+          <t>Carpinus bet. 'Frans Fontaine'</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9430,11 +9303,6 @@
       <c r="E250" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -9452,7 +9320,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Frans Fontaine'</t>
+          <t>Carpinus bet. 'Frans Fontaine'</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9485,7 +9353,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Frans Fontaine'</t>
+          <t>Carpinus bet. 'Frans Fontaine'</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9501,11 +9369,6 @@
       <c r="E252" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -9523,7 +9386,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Frans Fontaine'</t>
+          <t>Carpinus bet. 'Frans Fontaine'</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9561,7 +9424,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Frans Fontaine'</t>
+          <t>Carpinus bet. 'Frans Fontaine'</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9599,7 +9462,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Frans Fontaine'</t>
+          <t>Carpinus bet. 'Frans Fontaine'</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9637,7 +9500,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Lucas'</t>
+          <t>Carpinus bet. 'Lucas'</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9670,7 +9533,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Lucas'</t>
+          <t>Carpinus bet. 'Lucas'</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9703,7 +9566,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Lucas'</t>
+          <t>Carpinus bet. 'Lucas'</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9741,7 +9604,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Lucas'</t>
+          <t>Carpinus bet. 'Lucas'</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9757,11 +9620,6 @@
       <c r="E259" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -9779,7 +9637,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Quercifolia'</t>
+          <t>Carpinus bet. 'Quercifolia'</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9817,7 +9675,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Quercifolia'</t>
+          <t>Carpinus bet. 'Quercifolia'</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9855,7 +9713,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Quercifolia'</t>
+          <t>Carpinus bet. 'Quercifolia'</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9893,7 +9751,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Rockhampton Red'</t>
+          <t>Carpinus bet. 'Rockhampton Red'</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9909,11 +9767,6 @@
       <c r="E263" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -9931,7 +9784,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Rockhampton Red'</t>
+          <t>Carpinus bet. 'Rockhampton Red'</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9969,7 +9822,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Carpinus Bet. 'Rockhampton Red'</t>
+          <t>Carpinus bet. 'Rockhampton Red'</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -10002,7 +9855,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Carpinus Betulus</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -10040,7 +9893,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Carpinus Betulus</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -10078,7 +9931,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Carpinus Betulus</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -10111,7 +9964,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Carpinus Betulus</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -10149,7 +10002,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Carpinus Betulus</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -10187,7 +10040,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Carpinus Betulus</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -10225,7 +10078,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Carpinus Betulus</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -10263,7 +10116,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Carpinus Betulus</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -10301,7 +10154,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Carpinus Japonica</t>
+          <t>Carpinus japonica</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -10334,7 +10187,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Carpinus Japonica</t>
+          <t>Carpinus japonica</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10367,7 +10220,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Carya Illinoinensis</t>
+          <t>Carya illinoinensis</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10400,7 +10253,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Carya Ovata</t>
+          <t>Carya ovata</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10433,7 +10286,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Castanea Sativa</t>
+          <t>Castanea sativa</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10449,11 +10302,6 @@
       <c r="E278" t="inlineStr">
         <is>
           <t>120-150cm</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -10471,7 +10319,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Castanea Sativa</t>
+          <t>Castanea sativa</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10509,7 +10357,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Catalpa Bignonioides</t>
+          <t>Catalpa bignonioides</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10542,7 +10390,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Catalpa Bignonioides</t>
+          <t>Catalpa bignonioides</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10580,7 +10428,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Catalpa Bignonioides</t>
+          <t>Catalpa bignonioides</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10613,7 +10461,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Catalpa Bignonioides</t>
+          <t>Catalpa bignonioides</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10651,7 +10499,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Catalpa Bignonioides</t>
+          <t>Catalpa bignonioides</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10689,7 +10537,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Catalpa Bignonioides</t>
+          <t>Catalpa bignonioides</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10727,7 +10575,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Catalpa Bignonioides</t>
+          <t>Catalpa bignonioides</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10765,7 +10613,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Catalpa Bignonioides 'Aurea'</t>
+          <t>Catalpa bignonioides 'Aurea'</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10798,7 +10646,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Cedrus Atlantica</t>
+          <t>Cedrus atlantica</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10831,7 +10679,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Cedrus Atlantica</t>
+          <t>Cedrus atlantica</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10869,7 +10717,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Cedrus Atlantica</t>
+          <t>Cedrus atlantica</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10885,11 +10733,6 @@
       <c r="E290" t="inlineStr">
         <is>
           <t>40-60cm</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -10907,7 +10750,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Cedrus Atlantica ‘Glauca’</t>
+          <t>Cedrus atlantica</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10923,11 +10766,6 @@
       <c r="E291" t="inlineStr">
         <is>
           <t>60-90cm</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -10945,7 +10783,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Cedrus Deodara</t>
+          <t>Cedrus deodara</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10978,7 +10816,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Cedrus Deodara</t>
+          <t>Cedrus deodara</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -11011,7 +10849,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Cedrus Libani</t>
+          <t>Cedrus libani</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -11027,11 +10865,6 @@
       <c r="E294" t="inlineStr">
         <is>
           <t>60-90cm</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -11049,7 +10882,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Celtis Sinensis</t>
+          <t>Celtis sinensis</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -11082,7 +10915,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Cercidiphyllum Japonicum</t>
+          <t>Cercidiphyllum japonicum</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -11120,7 +10953,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Cercidiphyllum Japonicum</t>
+          <t>Cercidiphyllum japonicum</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -11158,7 +10991,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Cercidiphyllum Japonicum</t>
+          <t>Cercidiphyllum japonicum</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -11191,7 +11024,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Cercidiphyllum Japonicum</t>
+          <t>Cercidiphyllum japonicum</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -11207,11 +11040,6 @@
       <c r="E299" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -11229,7 +11057,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Chamaecyparis L. ‘Columnaris’</t>
+          <t>Chamaecyparis l.</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -11262,7 +11090,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Chamaecyparis Lawonsonia</t>
+          <t>Chamaecyparis lawonsonia</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -11278,11 +11106,6 @@
       <c r="E301" t="inlineStr">
         <is>
           <t>140-160cm</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -11300,7 +11123,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Chitalpa Tashkentensis 'Pink Dawn'</t>
+          <t>Chitalpa tashkentensis 'Pink Dawn'</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -11333,7 +11156,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Chitalpa Tashkentensis 'Pink Dawn'</t>
+          <t>Chitalpa tashkentensis 'Pink Dawn'</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11366,7 +11189,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Cladrastis Kentukea</t>
+          <t>Cladrastis kentukea</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11399,7 +11222,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Cladrastis Kentukea</t>
+          <t>Cladrastis kentukea</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11432,7 +11255,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Cordyline Australis</t>
+          <t>Cordyline australis</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11465,7 +11288,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Cornus Controversa</t>
+          <t>Cornus controversa</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11503,7 +11326,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Cornus Controversa 'Variegata'</t>
+          <t>Cornus controversa 'Variegata'</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11536,7 +11359,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Cornus Florida</t>
+          <t>Cornus florida</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11569,7 +11392,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Cornus Florida 'Cherokee Chief'</t>
+          <t>Cornus florida 'Cherokee Chief'</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -11602,7 +11425,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Cornus Kousa 'China Girl'</t>
+          <t>Cornus kousa 'China Girl'</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -11635,7 +11458,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Cornus Kousa 'China Girl'</t>
+          <t>Cornus kousa 'China Girl'</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -11668,7 +11491,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Cornus Kousa ‘Milky Way’</t>
+          <t>Cornus kousa</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11701,7 +11524,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Cornus Kousa 'Satomi'</t>
+          <t>Cornus kousa 'Satomi'</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11734,7 +11557,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Cornus Kousa 'White Giant'</t>
+          <t>Cornus kousa 'White Giant'</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -11767,7 +11590,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Cornus Kousa Chinensis</t>
+          <t>Cornus kousa</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -11800,7 +11623,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Cornus Kousa Chinensis</t>
+          <t>Cornus kousa</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -11833,7 +11656,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Cornus Mas</t>
+          <t>Cornus mas</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -11866,7 +11689,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Cornus Mas</t>
+          <t>Cornus mas</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -11899,7 +11722,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Cornus Mas</t>
+          <t>Cornus mas</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -11932,7 +11755,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Cornus Mas</t>
+          <t>Cornus mas</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -11970,7 +11793,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Cornus Wilsoniana</t>
+          <t>Cornus wilsoniana</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -12003,7 +11826,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Corylus Avellana</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -12036,7 +11859,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Corylus Avellana</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -12069,7 +11892,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Corylus Avellana 'Contorta'</t>
+          <t>Corylus avellana 'Contorta'</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -12102,7 +11925,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Corylus Colurna</t>
+          <t>Corylus colurna</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -12140,7 +11963,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Corylus Colurna</t>
+          <t>Corylus colurna</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -12178,7 +12001,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Cotoneaster Watereri 'Cornubia'</t>
+          <t>Cotoneaster watereri 'Cornubia'</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -12211,7 +12034,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Cotoneaster Watereri 'Cornubia'</t>
+          <t>Cotoneaster watereri 'Cornubia'</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -12244,7 +12067,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Cotoneaster Watereri 'Cornubia'</t>
+          <t>Cotoneaster watereri 'Cornubia'</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -12277,7 +12100,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Cotoneaster Watereri 'Cornubia'</t>
+          <t>Cotoneaster watereri 'Cornubia'</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -12315,7 +12138,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Crataegus ‘Paul’S Scarlet’</t>
+          <t>Crataegus ‘paul’s</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -12348,7 +12171,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Crataegus Laevigata 'Crimson Cloud'</t>
+          <t>Crataegus laevigata 'Crimson Cloud'</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -12386,7 +12209,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Crataegus Laevigata 'Rosea Flore Pleno'</t>
+          <t>Crataegus laevigata 'Rosea Flore Pleno'</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -12402,11 +12225,6 @@
       <c r="E334" t="inlineStr">
         <is>
           <t>120-140cm</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -12424,7 +12242,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Crataegus Laevigata 'Rosea Flore Pleno'</t>
+          <t>Crataegus laevigata 'Rosea Flore Pleno'</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -12440,11 +12258,6 @@
       <c r="E335" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -12462,7 +12275,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Crataegus Laevigata 'Rosea Flore Pleno'</t>
+          <t>Crataegus laevigata 'Rosea Flore Pleno'</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -12500,7 +12313,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Crataegus Laevigata 'Rosea Flore Pleno'</t>
+          <t>Crataegus laevigata 'Rosea Flore Pleno'</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -12533,7 +12346,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Crataegus Monogyna</t>
+          <t>Crataegus monogyna</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -12566,7 +12379,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Crataegus Mordenensis 'Toba'</t>
+          <t>Crataegus mordenensis 'Toba'</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -12599,7 +12412,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Crataegus Mordenensis 'Toba'</t>
+          <t>Crataegus mordenensis 'Toba'</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -12637,7 +12450,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Crataegus Mordenensis 'Toba'</t>
+          <t>Crataegus mordenensis 'Toba'</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -12675,7 +12488,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Crateagus Monogyna ‘Stricta’</t>
+          <t>Crateagus monogyna</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -12713,7 +12526,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Cupressus Macrocarpa</t>
+          <t>Cupressus macrocarpa</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -12746,7 +12559,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Cupressus Macrocarpa</t>
+          <t>Cupressus macrocarpa</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -12779,7 +12592,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Cupressus Sempervirens 'Stricta'</t>
+          <t>Cupressus sempervirens 'Stricta'</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -12812,7 +12625,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Cydonia Oblonga 'Vranja'</t>
+          <t>Cydonia oblonga 'Vranja'</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -12828,11 +12641,6 @@
       <c r="E346" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -12850,7 +12658,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Davidia Involucrata</t>
+          <t>Davidia involucrata</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -12883,7 +12691,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Davidia Involucrata</t>
+          <t>Davidia involucrata</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -12899,11 +12707,6 @@
       <c r="E348" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G348" t="n">
@@ -12921,7 +12724,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Elaeagnus × Ebbingei</t>
+          <t>Elaeagnus ×</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -12959,7 +12762,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Elaeagnus × Ebbingei</t>
+          <t>Elaeagnus ×</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -12992,7 +12795,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Eucalyptus Dalrympleana</t>
+          <t>Eucalyptus dalrympleana</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -13025,7 +12828,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Eucalyptus Gunnii</t>
+          <t>Eucalyptus gunnii</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -13058,7 +12861,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Eucalyptus Gunnii 'France Bleu'</t>
+          <t>Eucalyptus gunnii 'France Bleu'</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -13091,7 +12894,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Eucalyptus Moorei</t>
+          <t>Eucalyptus moorei</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -13124,7 +12927,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Eucalyptus Perriniana</t>
+          <t>Eucalyptus perriniana</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -13157,7 +12960,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Euonymus Europaeus 'Red Cascade'</t>
+          <t>Euonymus europaeus 'Red Cascade'</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -13190,7 +12993,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Fagus Syl. 'Asplenifolia'</t>
+          <t>Fagus syl. 'Asplenifolia'</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -13223,7 +13026,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Fagus Syl. 'Atropunicea'</t>
+          <t>Fagus syl. 'Atropunicea'</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -13256,7 +13059,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Fagus Syl. 'Dawyck Gold'</t>
+          <t>Fagus syl. 'Dawyck Gold'</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -13294,7 +13097,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Fagus Syl. 'Dawyck Gold'</t>
+          <t>Fagus syl. 'Dawyck Gold'</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -13327,7 +13130,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Fagus Syl. 'Dawyck Green'</t>
+          <t>Fagus syl. 'Dawyck Green'</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -13360,7 +13163,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Fagus Syl. 'Dawyck Green'</t>
+          <t>Fagus syl. 'Dawyck Green'</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -13398,7 +13201,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Fagus Syl. 'Dawyck Green'</t>
+          <t>Fagus syl. 'Dawyck Green'</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -13414,11 +13217,6 @@
       <c r="E363" t="inlineStr">
         <is>
           <t>60-90cm</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G363" t="n">
@@ -13436,7 +13234,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Fagus Syl. 'Dawyck Green'</t>
+          <t>Fagus syl. 'Dawyck Green'</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -13474,7 +13272,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Fagus Syl. 'Dawyck Purple'</t>
+          <t>Fagus syl. 'Dawyck Purple'</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -13507,7 +13305,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Fagus Syl. 'Dawyck Purple'</t>
+          <t>Fagus syl. 'Dawyck Purple'</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -13545,7 +13343,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Fagus Syl. 'Dawyck Purple'</t>
+          <t>Fagus syl. 'Dawyck Purple'</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -13578,7 +13376,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Fagus Syl. 'Dawyck Purple'</t>
+          <t>Fagus syl. 'Dawyck Purple'</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -13611,7 +13409,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Fagus Syl. ‘Purpurea Pendula’</t>
+          <t>Fagus syl.</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -13644,7 +13442,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Fagus Syl. 'Rohan Obelisk'</t>
+          <t>Fagus syl. 'Rohan Obelisk'</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -13682,7 +13480,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Fagus Sylvatica</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -13715,7 +13513,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Fagus Sylvatica</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -13753,7 +13551,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Fagus Sylvatica</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -13791,7 +13589,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Fagus Sylvatica</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -13824,7 +13622,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Fargesia Robusta Formidable</t>
+          <t>Fargesia robusta</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -13923,7 +13721,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Fraxinus Angustifolia ‘Raywood’/ Claret Ash</t>
+          <t>Fraxinus angustifolia</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -13951,7 +13749,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Fraxinus Ornus 'Louisa Lady'</t>
+          <t>Fraxinus ornus 'Louisa Lady'</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -13989,7 +13787,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Fraxinus Ornus 'Louisa Lady'</t>
+          <t>Fraxinus ornus 'Louisa Lady'</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -14027,7 +13825,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Gift Card</t>
+          <t>Gift card</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -14057,7 +13855,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Ginkgo Biloba</t>
+          <t>Ginkgo biloba</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -14090,7 +13888,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Ginkgo Biloba</t>
+          <t>Ginkgo biloba</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -14123,7 +13921,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Ginkgo Biloba</t>
+          <t>Ginkgo biloba</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -14161,7 +13959,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Ginkgo Biloba</t>
+          <t>Ginkgo biloba</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -14177,11 +13975,6 @@
       <c r="E385" t="inlineStr">
         <is>
           <t>40-60cm</t>
-        </is>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G385" t="n">
@@ -14199,7 +13992,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Ginkgo Biloba</t>
+          <t>Ginkgo biloba</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -14232,7 +14025,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Ginkgo Biloba ‘Blagon’</t>
+          <t>Ginkgo biloba</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -14265,7 +14058,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Ginkgo Biloba 'Brivingtetun'</t>
+          <t>Ginkgo biloba 'Brivingtetun'</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -14298,7 +14091,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Ginkgo Biloba 'Menhir'</t>
+          <t>Ginkgo biloba 'Menhir'</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -14331,7 +14124,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Ginkgo Biloba 'Princeton Sentry'</t>
+          <t>Ginkgo biloba 'Princeton Sentry'</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -14364,7 +14157,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Ginkgo Biloba 'Princeton Sentry'</t>
+          <t>Ginkgo biloba 'Princeton Sentry'</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -14397,7 +14190,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Gleditsia Triacanthos 'Sunburst'</t>
+          <t>Gleditsia triacanthos 'Sunburst'</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -14435,7 +14228,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Gleditsia Triacanthos 'Sunburst'</t>
+          <t>Gleditsia triacanthos 'Sunburst'</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -14451,11 +14244,6 @@
       <c r="E393" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G393" t="n">
@@ -14473,7 +14261,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Halesia Carolina</t>
+          <t>Halesia carolina</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -14506,7 +14294,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Halesia Carolina</t>
+          <t>Halesia carolina</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -14539,7 +14327,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Halesia Carolina</t>
+          <t>Halesia carolina</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -14555,11 +14343,6 @@
       <c r="E396" t="inlineStr">
         <is>
           <t>40-60cm</t>
-        </is>
-      </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G396" t="n">
@@ -14577,7 +14360,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Hamamelis × Intermedia 'Diane'</t>
+          <t>Hamamelis × 'Diane'</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -14610,7 +14393,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Heptacodium Miconioides</t>
+          <t>Heptacodium miconioides</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -14643,7 +14426,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Heptacodium Miconioides</t>
+          <t>Heptacodium miconioides</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -14681,7 +14464,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Heptacodium Miconioides</t>
+          <t>Heptacodium miconioides</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -14697,11 +14480,6 @@
       <c r="E400" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G400" t="n">
@@ -14719,7 +14497,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Hibiscus Syriacus 'Hamabo'</t>
+          <t>Hibiscus syriacus 'Hamabo'</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -14770,11 +14548,6 @@
           <t>225-250cm</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>0.</t>
-        </is>
-      </c>
       <c r="G402" t="n">
         <v>90</v>
       </c>
@@ -14823,7 +14596,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Ilex Aquifolium ‘Alaska’</t>
+          <t>Ilex aquifolium</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -14856,7 +14629,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Ilex Aquifolium ‘Alaska’</t>
+          <t>Ilex aquifolium</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -14889,7 +14662,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Juglans Nigra</t>
+          <t>Juglans nigra</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -14905,11 +14678,6 @@
       <c r="E406" t="inlineStr">
         <is>
           <t>100-125 cm</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G406" t="n">
@@ -14927,7 +14695,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Juglans Nigra</t>
+          <t>Juglans nigra</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -14965,7 +14733,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Juglans Nigra</t>
+          <t>Juglans nigra</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -15003,7 +14771,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Juglans Nigra</t>
+          <t>Juglans nigra</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -15041,7 +14809,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Juglans Regia</t>
+          <t>Juglans regia</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -15074,7 +14842,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Juglans Regia</t>
+          <t>Juglans regia</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -15107,7 +14875,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Juglans Regia</t>
+          <t>Juglans regia</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -15145,7 +14913,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Juniperus Scopulorum 'Blue Arrow'</t>
+          <t>Juniperus scopulorum 'Blue Arrow'</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -15178,7 +14946,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Juniperus Scopulorum 'Blue Arrow'</t>
+          <t>Juniperus scopulorum 'Blue Arrow'</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -15211,7 +14979,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Juniperus Scopulorum 'Blue Arrow'</t>
+          <t>Juniperus scopulorum 'Blue Arrow'</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -15244,7 +15012,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Juniperus Scopulorum 'Skyrocket'</t>
+          <t>Juniperus scopulorum 'Skyrocket'</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -15282,7 +15050,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Koelreuteria Paniculata</t>
+          <t>Koelreuteria paniculata</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -15315,7 +15083,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Koelreuteria Paniculata</t>
+          <t>Koelreuteria paniculata</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -15353,7 +15121,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Koelreuteria Paniculata</t>
+          <t>Koelreuteria paniculata</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -15386,7 +15154,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Koelreuteria Paniculata</t>
+          <t>Koelreuteria paniculata</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -15424,7 +15192,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Laburnum X Watereri 'Vossii'</t>
+          <t>Laburnum x 'Vossii'</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -15457,7 +15225,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Larix Decidua</t>
+          <t>Larix decidua</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -15490,7 +15258,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Larix Kaempferi</t>
+          <t>Larix kaempferi</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -15523,7 +15291,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Larix Kaempferi</t>
+          <t>Larix kaempferi</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -15556,7 +15324,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Larix Kaempferi</t>
+          <t>Larix kaempferi</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -15589,7 +15357,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Laurus Nobilis</t>
+          <t>Laurus nobilis</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -15622,7 +15390,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Laurus Nobilis</t>
+          <t>Laurus nobilis</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -15655,7 +15423,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Liquidambar Styraciflua</t>
+          <t>Liquidambar styraciflua</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -15693,7 +15461,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Liquidambar Styraciflua</t>
+          <t>Liquidambar styraciflua</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -15731,7 +15499,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Liquidambar Styraciflua</t>
+          <t>Liquidambar styraciflua</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -15769,7 +15537,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Liquidambar Styraciflua</t>
+          <t>Liquidambar styraciflua</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -15807,7 +15575,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Liquidambar Styraciflua 'Lane Roberts'</t>
+          <t>Liquidambar styraciflua 'Lane Roberts'</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -15840,7 +15608,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Liquidambar Styraciflua 'Slender Silhouette'</t>
+          <t>Liquidambar styraciflua 'Slender Silhouette'</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -15873,7 +15641,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Liquidambar Styraciflua 'Slender Silhouette'</t>
+          <t>Liquidambar styraciflua 'Slender Silhouette'</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -15911,7 +15679,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Liquidambar Styraciflua 'Slender Silhouette'</t>
+          <t>Liquidambar styraciflua 'Slender Silhouette'</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -15949,7 +15717,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Liquidambar Styraciflua 'Slender Silhouette'</t>
+          <t>Liquidambar styraciflua 'Slender Silhouette'</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -15965,11 +15733,6 @@
       <c r="E436" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G436" t="n">
@@ -15987,7 +15750,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Liquidambar Styraciflua 'Worplesdon'</t>
+          <t>Liquidambar styraciflua 'Worplesdon'</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -16003,11 +15766,6 @@
       <c r="E437" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G437" t="n">
@@ -16025,7 +15783,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Liquidambar Styraciflua 'Worplesdon'</t>
+          <t>Liquidambar styraciflua 'Worplesdon'</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -16063,7 +15821,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Liquidambar Styraciflua 'Worplesdon'</t>
+          <t>Liquidambar styraciflua 'Worplesdon'</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -16101,7 +15859,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Liquidambar Styraciflua 'Worplesdon'</t>
+          <t>Liquidambar styraciflua 'Worplesdon'</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -16139,7 +15897,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Liquidambar Styraciflua 'Worplesdon'</t>
+          <t>Liquidambar styraciflua 'Worplesdon'</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -16177,7 +15935,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Liriodendron Tulipifera</t>
+          <t>Liriodendron tulipifera</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -16193,11 +15951,6 @@
       <c r="E442" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G442" t="n">
@@ -16215,7 +15968,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Liriodendron Tulipifera</t>
+          <t>Liriodendron tulipifera</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -16248,7 +16001,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Liriodendron Tulipifera</t>
+          <t>Liriodendron tulipifera</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -16281,7 +16034,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Liriodendron Tulipifera</t>
+          <t>Liriodendron tulipifera</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -16319,7 +16072,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Liriodendron Tulipifera</t>
+          <t>Liriodendron tulipifera</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -16357,7 +16110,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Liriodendron Tulipifera 'Aureomarginatum'</t>
+          <t>Liriodendron tulipifera 'Aureomarginatum'</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -16390,7 +16143,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Liriodendron Tulipifera 'Aureomarginatum'</t>
+          <t>Liriodendron tulipifera 'Aureomarginatum'</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -16406,11 +16159,6 @@
       <c r="E448" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F448" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G448" t="n">
@@ -16428,7 +16176,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Liriodendron Tulipifera 'Fastigiatum'/ Columnar Tulip Tree</t>
+          <t>Liriodendron tulipifera 'Fastigiatum'</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -16456,7 +16204,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Magnolia ‘Galaxy’</t>
+          <t>Magnolia ‘galaxy’</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -16494,7 +16242,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Magnolia ‘Galaxy’</t>
+          <t>Magnolia ‘galaxy’</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -16532,7 +16280,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Magnolia ‘Galaxy’</t>
+          <t>Magnolia ‘galaxy’</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -16570,7 +16318,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Magnolia ‘Galaxy’</t>
+          <t>Magnolia ‘galaxy’</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -16608,7 +16356,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Magnolia ‘Galaxy’</t>
+          <t>Magnolia ‘galaxy’</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -16740,7 +16488,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Magnolia Grandiflora</t>
+          <t>Magnolia grandiflora</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -16773,7 +16521,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Magnolia Kobus</t>
+          <t>Magnolia kobus</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -16806,7 +16554,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Magnolia Stellata</t>
+          <t>Magnolia stellata</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -16839,7 +16587,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Magnolia Stellata</t>
+          <t>Magnolia stellata</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -16872,7 +16620,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Magnolia X Loebneri 'Leonard Messel'</t>
+          <t>Magnolia x 'Leonard Messel'</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -17531,7 +17279,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Malus ‘Prairie Fire’</t>
+          <t>Malus ‘prairie</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -17564,7 +17312,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Malus ‘Prairie Fire’</t>
+          <t>Malus ‘prairie</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -17871,11 +17619,6 @@
           <t>125-150cm</t>
         </is>
       </c>
-      <c r="F489" t="inlineStr">
-        <is>
-          <t>'0</t>
-        </is>
-      </c>
       <c r="G489" t="n">
         <v>31.5</v>
       </c>
@@ -17909,11 +17652,6 @@
           <t>175-200cm</t>
         </is>
       </c>
-      <c r="F490" t="inlineStr">
-        <is>
-          <t>0'</t>
-        </is>
-      </c>
       <c r="G490" t="n">
         <v>45</v>
       </c>
@@ -18000,7 +17738,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Malus Baccata ‘Columnaris Red’</t>
+          <t>Malus baccata</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -18033,7 +17771,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Beauty Of Bath'</t>
+          <t>Malus domestica 'Beauty Of Bath'</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -18066,7 +17804,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Beauty Of Bath'</t>
+          <t>Malus domestica 'Beauty Of Bath'</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -18104,7 +17842,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Bramley's Seedling'</t>
+          <t>Malus domestica 'Bramley'</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -18120,11 +17858,6 @@
       <c r="E496" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F496" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G496" t="n">
@@ -18142,7 +17875,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Charles Ross'</t>
+          <t>Malus domestica 'Charles Ross'</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -18175,7 +17908,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Cox's Orange Pippin'</t>
+          <t>Malus domestica 'Cox'</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -18191,11 +17924,6 @@
       <c r="E498" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F498" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G498" t="n">
@@ -18213,7 +17941,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Ellison's Orange'</t>
+          <t>Malus domestica 'Ellison'</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -18246,7 +17974,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Elstar'</t>
+          <t>Malus domestica 'Elstar'</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -18262,11 +17990,6 @@
       <c r="E500" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F500" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G500" t="n">
@@ -18284,7 +18007,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Elstar'</t>
+          <t>Malus domestica 'Elstar'</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -18317,7 +18040,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Greensleeves'</t>
+          <t>Malus domestica 'Greensleeves'</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -18350,7 +18073,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Howgate Wonder'</t>
+          <t>Malus domestica 'Howgate Wonder'</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -18383,7 +18106,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Howgate Wonder'</t>
+          <t>Malus domestica 'Howgate Wonder'</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -18416,7 +18139,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Malus Domestica 'James Grieve'</t>
+          <t>Malus domestica 'James Grieve'</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -18449,7 +18172,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Jonagold'</t>
+          <t>Malus domestica 'Jonagold'</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -18465,11 +18188,6 @@
       <c r="E506" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F506" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G506" t="n">
@@ -18487,7 +18205,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Laxton's Superb'</t>
+          <t>Malus domestica 'Laxton'</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -18503,11 +18221,6 @@
       <c r="E507" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F507" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G507" t="n">
@@ -18525,7 +18238,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Laxton's Superb'</t>
+          <t>Malus domestica 'Laxton'</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -18558,7 +18271,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Red Devil'</t>
+          <t>Malus domestica 'Red Devil'</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -18574,11 +18287,6 @@
       <c r="E509" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F509" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G509" t="n">
@@ -18596,7 +18304,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Rode Jonathan'</t>
+          <t>Malus domestica 'Rode Jonathan'</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -18629,7 +18337,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Scrumptious'</t>
+          <t>Malus domestica 'Scrumptious'</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -18662,7 +18370,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Spartan'</t>
+          <t>Malus domestica 'Spartan'</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -18695,7 +18403,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Spartan'</t>
+          <t>Malus domestica 'Spartan'</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -18728,7 +18436,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Summerred'</t>
+          <t>Malus domestica 'Summerred'</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -18761,7 +18469,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Malus Domestica 'Worcester Pearmain'</t>
+          <t>Malus domestica 'Worcester Pearmain'</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -18794,7 +18502,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Malus Domestica Katja</t>
+          <t>Malus domestica</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -18810,11 +18518,6 @@
       <c r="E516" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F516" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G516" t="n">
@@ -18832,7 +18535,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Malus Sylvestris</t>
+          <t>Malus sylvestris</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -18865,7 +18568,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Malus Trilobata</t>
+          <t>Malus trilobata</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -18898,7 +18601,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Malus Trilobata</t>
+          <t>Malus trilobata</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -18936,7 +18639,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Malus Trilobata</t>
+          <t>Malus trilobata</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -18974,7 +18677,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Malus Trilobata</t>
+          <t>Malus trilobata</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -19012,7 +18715,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Malus Trilobata</t>
+          <t>Malus trilobata</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -19050,7 +18753,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Malus Trilobata</t>
+          <t>Malus trilobata</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -19088,7 +18791,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Mespilus Germanica</t>
+          <t>Mespilus germanica</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -19121,7 +18824,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Metasequoia Glytostroboides</t>
+          <t>Metasequoia glytostroboides</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -19159,7 +18862,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Metasequoia Glytostroboides</t>
+          <t>Metasequoia glytostroboides</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -19197,7 +18900,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Metasequoia Glytostroboides</t>
+          <t>Metasequoia glytostroboides</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -19235,7 +18938,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Metasequoia Glytostroboides</t>
+          <t>Metasequoia glytostroboides</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -19273,7 +18976,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Metasequoia Glytostroboides</t>
+          <t>Metasequoia glytostroboides</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -19311,7 +19014,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Metasequoia Glytostroboides</t>
+          <t>Metasequoia glytostroboides</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -19349,7 +19052,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Morus Alba</t>
+          <t>Morus alba</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -19382,7 +19085,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Morus Alba</t>
+          <t>Morus alba</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -19415,7 +19118,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Morus Alba ‘Fruitless’ Syn. Kagayamae</t>
+          <t>Morus alba</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -19448,7 +19151,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Morus Nigra</t>
+          <t>Morus nigra</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -19481,7 +19184,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Nothofagus Antarctica</t>
+          <t>Nothofagus antarctica</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -19514,7 +19217,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Nyssa Sylvatica</t>
+          <t>Nyssa sylvatica</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -19530,11 +19233,6 @@
       <c r="E536" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F536" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G536" t="n">
@@ -19552,7 +19250,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Nyssa Sylvatica</t>
+          <t>Nyssa sylvatica</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -19585,7 +19283,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Nyssa Sylvatica</t>
+          <t>Nyssa sylvatica</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -19618,7 +19316,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Ostrya Carpinifolia</t>
+          <t>Ostrya carpinifolia</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -19651,7 +19349,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Ostrya Carpinifolia</t>
+          <t>Ostrya carpinifolia</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -19689,7 +19387,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Ostrya Carpinifolia</t>
+          <t>Ostrya carpinifolia</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -19727,7 +19425,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Parrotia Persica</t>
+          <t>Parrotia persica</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -19765,7 +19463,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Parrotia Persica</t>
+          <t>Parrotia persica</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -19798,7 +19496,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Parrotia Persica 'Persian Spire'</t>
+          <t>Parrotia persica 'Persian Spire'</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -19831,7 +19529,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Parrotia Persica 'Persian Spire'</t>
+          <t>Parrotia persica 'Persian Spire'</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -19864,7 +19562,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Parrotia Persica 'Vanessa'</t>
+          <t>Parrotia persica 'Vanessa'</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -19880,11 +19578,6 @@
       <c r="E546" t="inlineStr">
         <is>
           <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F546" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G546" t="n">
@@ -19902,7 +19595,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Parrotia Persica 'Vanessa'</t>
+          <t>Parrotia persica 'Vanessa'</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -19940,7 +19633,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Parrotia Persica 'Vanessa'</t>
+          <t>Parrotia persica 'Vanessa'</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -19978,7 +19671,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Parrotia Persica 'Vanessa'</t>
+          <t>Parrotia persica 'Vanessa'</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -19994,11 +19687,6 @@
       <c r="E549" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F549" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G549" t="n">
@@ -20016,7 +19704,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Paulownia Tomentosa</t>
+          <t>Paulownia tomentosa</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -20054,7 +19742,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Paulownia Tomentosa</t>
+          <t>Paulownia tomentosa</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -20087,7 +19775,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Phellodendron Amurense</t>
+          <t>Phellodendron amurense</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -20120,7 +19808,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Picea Abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -20153,7 +19841,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Picea Abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -20186,7 +19874,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Picea Abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -20219,7 +19907,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Picea Glauca Var. Albertiana 'Conica'</t>
+          <t>Picea glauca 'Conica'</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -20252,7 +19940,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Picea Omorika</t>
+          <t>Picea omorika</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -20285,7 +19973,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Picea Pungens Glauca</t>
+          <t>Picea pungens</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -20318,7 +20006,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Picea Sitchensis</t>
+          <t>Picea sitchensis</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -20351,7 +20039,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Pinus Armandii</t>
+          <t>Pinus armandii</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -20384,7 +20072,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Pinus Contorta</t>
+          <t>Pinus contorta</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -20417,7 +20105,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Pinus Halepensis</t>
+          <t>Pinus halepensis</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -20450,7 +20138,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Pinus Mugo Mughus</t>
+          <t>Pinus mugo</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -20483,7 +20171,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Pinus Mugo Subsp. Uncinata</t>
+          <t>Pinus mugo</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -20516,7 +20204,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Pinus Mugo Subsp. Uncinata</t>
+          <t>Pinus mugo</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -20549,7 +20237,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Pinus Nigra</t>
+          <t>Pinus nigra</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -20582,7 +20270,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Pinus Nigra</t>
+          <t>Pinus nigra</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -20615,7 +20303,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Pinus Nigra</t>
+          <t>Pinus nigra</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -20648,7 +20336,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Pinus Nigra Laricio</t>
+          <t>Pinus nigra</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -20686,7 +20374,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Pinus Pinaster</t>
+          <t>Pinus pinaster</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -20724,7 +20412,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Pinus Pinaster</t>
+          <t>Pinus pinaster</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -20757,7 +20445,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Pinus Pinea</t>
+          <t>Pinus pinea</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -20790,7 +20478,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Pinus Ponderosa</t>
+          <t>Pinus ponderosa</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -20823,7 +20511,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Pinus Strobus</t>
+          <t>Pinus strobus</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -20856,7 +20544,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Pinus Strobus</t>
+          <t>Pinus strobus</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -20889,7 +20577,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Pinus Strobus</t>
+          <t>Pinus strobus</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -20922,7 +20610,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Pinus Sylvestris</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -20955,7 +20643,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Pinus Sylvestris</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -20971,11 +20659,6 @@
       <c r="E578" t="inlineStr">
         <is>
           <t>40-60cm</t>
-        </is>
-      </c>
-      <c r="F578" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G578" t="n">
@@ -20993,7 +20676,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Pinus Tabuliformis</t>
+          <t>Pinus tabuliformis</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -21026,7 +20709,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Pinus Tabuliformis</t>
+          <t>Pinus tabuliformis</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -21059,7 +20742,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Pinus Wallichiana</t>
+          <t>Pinus wallichiana</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -21092,7 +20775,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Pinus Wallichiana</t>
+          <t>Pinus wallichiana</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -21125,7 +20808,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Platanus Orientalis</t>
+          <t>Platanus orientalis</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -21141,11 +20824,6 @@
       <c r="E583" t="inlineStr">
         <is>
           <t>120-150cm</t>
-        </is>
-      </c>
-      <c r="F583" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G583" t="n">
@@ -21163,7 +20841,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Platanus Orientalis</t>
+          <t>Platanus orientalis</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -21196,7 +20874,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Platanus Orientalis</t>
+          <t>Platanus orientalis</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -21234,7 +20912,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Platanus Orientalis</t>
+          <t>Platanus orientalis</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -21272,7 +20950,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Platanus Orientalis</t>
+          <t>Platanus orientalis</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -21310,7 +20988,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Platanus Orientalis</t>
+          <t>Platanus orientalis</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -21348,7 +21026,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Platanus X Hispanica</t>
+          <t>Platanus x</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -21381,7 +21059,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Platanus X Hispanica</t>
+          <t>Platanus x</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -21419,7 +21097,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Platanus X Hispanica</t>
+          <t>Platanus x</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -21457,7 +21135,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Platanus X Hispanica</t>
+          <t>Platanus x</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -21495,7 +21173,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Platanus X Hispanica ‘Pyramidalis’</t>
+          <t>Platanus x</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -21533,7 +21211,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Platanus X Hispanica ‘Pyramidalis’</t>
+          <t>Platanus x</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -21571,7 +21249,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Populus Alba</t>
+          <t>Populus alba</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -21604,7 +21282,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Populus Tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -21642,7 +21320,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Populus Tremula ‘Erecta’</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -21658,11 +21336,6 @@
       <c r="E597" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F597" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G597" t="n">
@@ -21680,7 +21353,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Populus Tremula ‘Erecta’</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -21718,7 +21391,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Populus Tremula ‘Erecta’</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -21756,7 +21429,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Populus Tremula ‘Erecta’</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -21794,7 +21467,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Populus Tremula ‘Erecta’</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -21954,11 +21627,6 @@
           <t>150-200cm</t>
         </is>
       </c>
-      <c r="F605" t="inlineStr">
-        <is>
-          <t>0.</t>
-        </is>
-      </c>
       <c r="G605" t="n">
         <v>37.5</v>
       </c>
@@ -21992,11 +21660,6 @@
           <t>150-200cm</t>
         </is>
       </c>
-      <c r="F606" t="inlineStr">
-        <is>
-          <t>0.</t>
-        </is>
-      </c>
       <c r="G606" t="n">
         <v>37.5</v>
       </c>
@@ -22177,11 +21840,6 @@
           <t>60-90cm</t>
         </is>
       </c>
-      <c r="F611" t="inlineStr">
-        <is>
-          <t>0.</t>
-        </is>
-      </c>
       <c r="G611" t="n">
         <v>25.5</v>
       </c>
@@ -22235,7 +21893,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Prunus Armeniaca 'Bredase'</t>
+          <t>Prunus armeniaca 'Bredase'</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -22268,7 +21926,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Prunus Armeniaca 'Hongaarse'</t>
+          <t>Prunus armeniaca 'Hongaarse'</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -22301,7 +21959,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Prunus Avium</t>
+          <t>Prunus avium</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -22334,7 +21992,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Prunus Avium</t>
+          <t>Prunus avium</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -22372,7 +22030,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Prunus Avium 'Plena'</t>
+          <t>Prunus avium 'Plena'</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -22405,7 +22063,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Prunus Avium 'Plena'</t>
+          <t>Prunus avium 'Plena'</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -22443,7 +22101,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Prunus Avium 'Plena'</t>
+          <t>Prunus avium 'Plena'</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -22481,7 +22139,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Prunus Cer. 'Crimson Pointe'</t>
+          <t>Prunus cer. 'Crimson Pointe'</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -22514,7 +22172,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Prunus Cer. 'Crimson Pointe'</t>
+          <t>Prunus cer. 'Crimson Pointe'</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -22552,7 +22210,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Prunus Cerasifera 'Nigra'</t>
+          <t>Prunus cerasifera 'Nigra'</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -22568,11 +22226,6 @@
       <c r="E622" t="inlineStr">
         <is>
           <t>175-200 cm</t>
-        </is>
-      </c>
-      <c r="F622" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G622" t="n">
@@ -22590,7 +22243,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Prunus Cerasifera 'Nigra'</t>
+          <t>Prunus cerasifera 'Nigra'</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -22623,7 +22276,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Prunus Cerasifera 'Nigra'</t>
+          <t>Prunus cerasifera 'Nigra'</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -22661,7 +22314,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Prunus Cerasifera 'Pissardii'</t>
+          <t>Prunus cerasifera 'Pissardii'</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -22694,7 +22347,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Prunus D. 'Merryweather Damson'</t>
+          <t>Prunus d. 'Merryweather Damson'</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -22727,7 +22380,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Prunus Domestica 'Czar'</t>
+          <t>Prunus domestica 'Czar'</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -22743,11 +22396,6 @@
       <c r="E627" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F627" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G627" t="n">
@@ -22765,7 +22413,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Prunus Domestica 'Opal'</t>
+          <t>Prunus domestica 'Opal'</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -22781,11 +22429,6 @@
       <c r="E628" t="inlineStr">
         <is>
           <t>12Ltr</t>
-        </is>
-      </c>
-      <c r="F628" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G628" t="n">
@@ -22803,7 +22446,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Prunus Domestica 'Reine Claude D'oullins'</t>
+          <t>Prunus domestica 'Reine Claude D'</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -22836,7 +22479,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Prunus Domestica 'Victoria'</t>
+          <t>Prunus domestica 'Victoria'</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -22869,7 +22512,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Prunus Domestica 'Victoria'</t>
+          <t>Prunus domestica 'Victoria'</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -22907,7 +22550,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Prunus Domestica 'Victoria'</t>
+          <t>Prunus domestica 'Victoria'</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -22945,7 +22588,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Prunus Hybrid 'Shogetsu'</t>
+          <t>Prunus hybrid 'Shogetsu'</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -22983,7 +22626,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Prunus L. ‘Etna’</t>
+          <t>Prunus l.</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -23021,7 +22664,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Prunus L. ‘Etna’</t>
+          <t>Prunus l.</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -23059,7 +22702,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Prunus L. 'Novita'</t>
+          <t>Prunus l. 'Novita'</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -23092,7 +22735,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Prunus Padus 'Canada Red'</t>
+          <t>Prunus padus 'Canada Red'</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -23125,7 +22768,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Prunus Padus 'Canada Red'</t>
+          <t>Prunus padus 'Canada Red'</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -23163,7 +22806,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Prunus Padus 'Canada Red'</t>
+          <t>Prunus padus 'Canada Red'</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -23201,7 +22844,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Prunus Padus 'Canada Red'</t>
+          <t>Prunus padus 'Canada Red'</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -23239,7 +22882,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Prunus Padus ‘Colorata’</t>
+          <t>Prunus padus</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -23277,7 +22920,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Prunus Ser. 'Royal Burgundy'</t>
+          <t>Prunus ser. 'Royal Burgundy'</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -23310,7 +22953,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Prunus Serr. 'Fugenzo'</t>
+          <t>Prunus serr. 'Fugenzo'</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -23348,7 +22991,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Prunus Serr. 'Fugenzo'</t>
+          <t>Prunus serr. 'Fugenzo'</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -23386,7 +23029,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Prunus Serrula 'Tibetica'</t>
+          <t>Prunus serrula 'Tibetica'</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -23424,7 +23067,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Prunus Serrulata ‘Kanzan’</t>
+          <t>Prunus serrulata</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -23440,11 +23083,6 @@
       <c r="E646" t="inlineStr">
         <is>
           <t>200-250 cm</t>
-        </is>
-      </c>
-      <c r="F646" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G646" t="n">
@@ -23462,7 +23100,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Prunus Serrulata ‘Kanzan’</t>
+          <t>Prunus serrulata</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -23495,7 +23133,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Prunus Serrulata ‘Kanzan’</t>
+          <t>Prunus serrulata</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -23533,7 +23171,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Prunus Serrulata ‘Kanzan’</t>
+          <t>Prunus serrulata</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -23571,7 +23209,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Prunus Serrulata ‘Kanzan’</t>
+          <t>Prunus serrulata</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -23609,7 +23247,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Prunus Serrulata ‘Kanzan’</t>
+          <t>Prunus serrulata</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -23642,7 +23280,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Prunus Serrulata 'Shimidsu' (Miyako)</t>
+          <t>Prunus serrulata 'Shimidsu'</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -23680,7 +23318,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Prunus Serrulata ‘Tai Haku’</t>
+          <t>Prunus serrulata</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -23696,11 +23334,6 @@
       <c r="E653" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F653" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G653" t="n">
@@ -23718,7 +23351,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Prunus X Subhirtella 'Autumnalis'</t>
+          <t>Prunus x 'Autumnalis'</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -23756,7 +23389,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Prunus X Subhirtella 'Autumnalis'</t>
+          <t>Prunus x 'Autumnalis'</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -23794,7 +23427,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Prunus X Subhirtella 'Autumnalis'</t>
+          <t>Prunus x 'Autumnalis'</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -23832,7 +23465,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Pterocarya Fraxinifolia</t>
+          <t>Pterocarya fraxinifolia</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -23870,7 +23503,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Pterocarya Fraxinifolia</t>
+          <t>Pterocarya fraxinifolia</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -23886,11 +23519,6 @@
       <c r="E658" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F658" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G658" t="n">
@@ -23908,7 +23536,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Pterocarya Fraxinifolia</t>
+          <t>Pterocarya fraxinifolia</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -23946,7 +23574,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Pyrus Calleryana</t>
+          <t>Pyrus calleryana</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -23979,7 +23607,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Pyrus Calleryana 'Chanticleer'</t>
+          <t>Pyrus calleryana 'Chanticleer'</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -24012,7 +23640,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Pyrus Calleryana 'Chanticleer'</t>
+          <t>Pyrus calleryana 'Chanticleer'</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -24028,11 +23656,6 @@
       <c r="E662" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F662" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G662" t="n">
@@ -24050,7 +23673,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Pyrus Calleryana 'Chanticleer'</t>
+          <t>Pyrus calleryana 'Chanticleer'</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -24088,7 +23711,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Pyrus Calleryana 'Chanticleer'</t>
+          <t>Pyrus calleryana 'Chanticleer'</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -24126,7 +23749,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Pyrus Calleryana 'Chanticleer'</t>
+          <t>Pyrus calleryana 'Chanticleer'</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -24164,7 +23787,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Pyrus Calleryana 'Chanticleer'</t>
+          <t>Pyrus calleryana 'Chanticleer'</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -24202,7 +23825,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Pyrus Calleryana 'Chanticleer'</t>
+          <t>Pyrus calleryana 'Chanticleer'</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -24240,7 +23863,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Pyrus Calleryana 'Chanticleer'</t>
+          <t>Pyrus calleryana 'Chanticleer'</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -24278,7 +23901,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Pyrus Calleryana 'Chanticleer'</t>
+          <t>Pyrus calleryana 'Chanticleer'</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -24294,11 +23917,6 @@
       <c r="E669" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F669" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G669" t="n">
@@ -24316,7 +23934,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Pyrus Communis ‘Beurre Hardy’</t>
+          <t>Pyrus communis</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -24332,11 +23950,6 @@
       <c r="E670" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F670" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G670" t="n">
@@ -24354,7 +23967,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Pyrus Communis ‘Concorde’</t>
+          <t>Pyrus communis</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -24387,7 +24000,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Pyrus Communis 'Conference'</t>
+          <t>Pyrus communis 'Conference'</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -24403,11 +24016,6 @@
       <c r="E672" t="inlineStr">
         <is>
           <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F672" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G672" t="n">
@@ -24425,7 +24033,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Pyrus Communis 'Conference'</t>
+          <t>Pyrus communis 'Conference'</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -24463,7 +24071,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Pyrus Communis 'Conference'</t>
+          <t>Pyrus communis 'Conference'</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -24496,7 +24104,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Pyrus Communis 'Williams'</t>
+          <t>Pyrus communis 'Williams'</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -24534,7 +24142,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Pyrus Domestica 'Doyenne Du Comice'/ Comice Pear</t>
+          <t>Pyrus domestica 'Doyenne Du Comice'</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -24562,7 +24170,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Pyrus Salicifolia ‘Pendula’</t>
+          <t>Pyrus salicifolia</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -24600,7 +24208,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Quercus Acutissima</t>
+          <t>Quercus acutissima</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -24638,7 +24246,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Quercus Acutissima</t>
+          <t>Quercus acutissima</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -24676,7 +24284,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Quercus Acutissima</t>
+          <t>Quercus acutissima</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -24714,7 +24322,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Quercus Acutissima</t>
+          <t>Quercus acutissima</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -24752,7 +24360,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Quercus Acutissima</t>
+          <t>Quercus acutissima</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -24768,11 +24376,6 @@
       <c r="E682" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F682" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G682" t="n">
@@ -24790,7 +24393,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Quercus Bicolor</t>
+          <t>Quercus bicolor</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -24823,7 +24426,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Quercus Buckleyi</t>
+          <t>Quercus buckleyi</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -24856,7 +24459,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Quercus Castaneifolia 'Green Spire'</t>
+          <t>Quercus castaneifolia 'Green Spire'</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -24894,7 +24497,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Quercus Castaneifolia 'Green Spire'</t>
+          <t>Quercus castaneifolia 'Green Spire'</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -24932,7 +24535,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Quercus Castaneifolia 'Green Spire'</t>
+          <t>Quercus castaneifolia 'Green Spire'</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -24965,7 +24568,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Quercus Cerris</t>
+          <t>Quercus cerris</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -24998,7 +24601,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Quercus Cerris</t>
+          <t>Quercus cerris</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -25036,7 +24639,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Quercus Cerris</t>
+          <t>Quercus cerris</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -25074,7 +24677,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Quercus Cerris</t>
+          <t>Quercus cerris</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -25112,7 +24715,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Quercus Cerris</t>
+          <t>Quercus cerris</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -25150,7 +24753,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Quercus Cerris</t>
+          <t>Quercus cerris</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -25188,7 +24791,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Quercus Coccinea</t>
+          <t>Quercus coccinea</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -25204,11 +24807,6 @@
       <c r="E694" t="inlineStr">
         <is>
           <t>300-350cm</t>
-        </is>
-      </c>
-      <c r="F694" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G694" t="n">
@@ -25226,7 +24824,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Quercus Falcata 'Pagodifolia'</t>
+          <t>Quercus falcata 'Pagodifolia'</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -25259,7 +24857,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Quercus Ilex</t>
+          <t>Quercus ilex</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -25275,11 +24873,6 @@
       <c r="E696" t="inlineStr">
         <is>
           <t>120-140cm</t>
-        </is>
-      </c>
-      <c r="F696" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G696" t="n">
@@ -25297,7 +24890,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Quercus Ilex</t>
+          <t>Quercus ilex</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -25335,7 +24928,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Quercus Ilex</t>
+          <t>Quercus ilex</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -25373,7 +24966,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Quercus Ilex</t>
+          <t>Quercus ilex</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -25389,11 +24982,6 @@
       <c r="E699" t="inlineStr">
         <is>
           <t>30-50cm</t>
-        </is>
-      </c>
-      <c r="F699" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G699" t="n">
@@ -25411,7 +24999,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Quercus Imbricaria</t>
+          <t>Quercus imbricaria</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -25444,7 +25032,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Quercus Imbricaria</t>
+          <t>Quercus imbricaria</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -25482,7 +25070,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Quercus Macrocarpa</t>
+          <t>Quercus macrocarpa</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -25515,7 +25103,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Quercus Myrsinifolia</t>
+          <t>Quercus myrsinifolia</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -25548,7 +25136,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Quercus Myrsinifolia</t>
+          <t>Quercus myrsinifolia</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -25581,7 +25169,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Quercus Nigra</t>
+          <t>Quercus nigra</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -25614,7 +25202,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Quercus Nigra</t>
+          <t>Quercus nigra</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -25652,7 +25240,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Quercus Nigra</t>
+          <t>Quercus nigra</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -25690,7 +25278,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Quercus Nigra</t>
+          <t>Quercus nigra</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -25706,11 +25294,6 @@
       <c r="E708" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F708" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G708" t="n">
@@ -25728,7 +25311,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Quercus Palustris</t>
+          <t>Quercus palustris</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -25761,7 +25344,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Quercus Palustris</t>
+          <t>Quercus palustris</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -25794,7 +25377,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Quercus Palustris</t>
+          <t>Quercus palustris</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -25832,7 +25415,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Quercus Palustris</t>
+          <t>Quercus palustris</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -25870,7 +25453,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Quercus Palustris</t>
+          <t>Quercus palustris</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -25908,7 +25491,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Quercus Palustris 'Green Pillar'</t>
+          <t>Quercus palustris 'Green Pillar'</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -25924,11 +25507,6 @@
       <c r="E714" t="inlineStr">
         <is>
           <t>120-150cm</t>
-        </is>
-      </c>
-      <c r="F714" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G714" t="n">
@@ -25946,7 +25524,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Quercus Palustris 'Green Pillar'</t>
+          <t>Quercus palustris 'Green Pillar'</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -25962,11 +25540,6 @@
       <c r="E715" t="inlineStr">
         <is>
           <t>150-175cm</t>
-        </is>
-      </c>
-      <c r="F715" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G715" t="n">
@@ -25984,7 +25557,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Quercus Palustris 'Green Pillar'</t>
+          <t>Quercus palustris 'Green Pillar'</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -26022,7 +25595,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Quercus Palustris 'Green Pillar'</t>
+          <t>Quercus palustris 'Green Pillar'</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -26055,7 +25628,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Quercus Petraea</t>
+          <t>Quercus petraea</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -26088,7 +25661,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Quercus Petraea</t>
+          <t>Quercus petraea</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -26126,7 +25699,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Quercus Petraea</t>
+          <t>Quercus petraea</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -26159,7 +25732,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Quercus Phellos</t>
+          <t>Quercus phellos</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -26197,7 +25770,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Quercus Phillyreoides</t>
+          <t>Quercus phillyreoides</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -26230,7 +25803,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Quercus Phillyreoides</t>
+          <t>Quercus phillyreoides</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -26263,7 +25836,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Quercus Phillyreoides</t>
+          <t>Quercus phillyreoides</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -26296,7 +25869,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Quercus Pubescens</t>
+          <t>Quercus pubescens</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -26329,7 +25902,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Quercus Pubescens</t>
+          <t>Quercus pubescens</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -26367,7 +25940,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Quercus Pubescens</t>
+          <t>Quercus pubescens</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -26405,7 +25978,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Quercus Pubescens</t>
+          <t>Quercus pubescens</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -26443,7 +26016,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Quercus Pyrenaica</t>
+          <t>Quercus pyrenaica</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -26481,7 +26054,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Quercus Robur</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -26514,7 +26087,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Quercus Robur</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -26552,7 +26125,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Quercus Robur</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -26585,7 +26158,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Quercus Robur</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -26623,7 +26196,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Quercus Robur</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -26639,11 +26212,6 @@
       <c r="E734" t="inlineStr">
         <is>
           <t>30-50cm</t>
-        </is>
-      </c>
-      <c r="F734" t="inlineStr">
-        <is>
-          <t>'0</t>
         </is>
       </c>
       <c r="G734" t="n">
@@ -26661,7 +26229,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Quercus Robur</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -26699,7 +26267,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Quercus Robur</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -26737,7 +26305,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Quercus Robur</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -26775,7 +26343,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Quercus Robur</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -26813,7 +26381,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Quercus Robur 'Fastigiata Koster'</t>
+          <t>Quercus robur 'Fastigiata Koster'</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -26846,7 +26414,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Quercus Robur 'Fastigiata Koster'</t>
+          <t>Quercus robur 'Fastigiata Koster'</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -26884,7 +26452,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Quercus Rubra</t>
+          <t>Quercus rubra</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -26900,11 +26468,6 @@
       <c r="E741" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F741" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G741" t="n">
@@ -26922,7 +26485,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Quercus Rubra</t>
+          <t>Quercus rubra</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -26955,7 +26518,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Quercus Rubra</t>
+          <t>Quercus rubra</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -26993,7 +26556,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Quercus Rubra</t>
+          <t>Quercus rubra</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -27031,7 +26594,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Quercus Rubra</t>
+          <t>Quercus rubra</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -27047,11 +26610,6 @@
       <c r="E745" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F745" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G745" t="n">
@@ -27069,7 +26627,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Quercus Suber</t>
+          <t>Quercus suber</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -27102,7 +26660,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Quercus Texana</t>
+          <t>Quercus texana</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -27135,7 +26693,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Quercus Turneri 'Pseudoturneri'</t>
+          <t>Quercus turneri 'Pseudoturneri'</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -27173,7 +26731,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Quercus X Hispanica 'Wageningen'</t>
+          <t>Quercus x 'Wageningen'</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -27211,7 +26769,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Rhus Typhina</t>
+          <t>Rhus typhina</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -27244,7 +26802,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Rhus Typhina</t>
+          <t>Rhus typhina</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -27277,7 +26835,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Rhus Typhina</t>
+          <t>Rhus typhina</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -27310,7 +26868,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Rhus Typhina</t>
+          <t>Rhus typhina</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -27343,7 +26901,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Rhus Typhina</t>
+          <t>Rhus typhina</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -27376,7 +26934,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Rhus Typhina Laciniata</t>
+          <t>Rhus typhina</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -27414,7 +26972,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Rhus Typhina Laciniata</t>
+          <t>Rhus typhina</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -27523,7 +27081,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Robinia Pseudoacacia 'Frisia'</t>
+          <t>Robinia pseudoacacia 'Frisia'</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -27539,11 +27097,6 @@
       <c r="E759" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F759" t="inlineStr">
-        <is>
-          <t>0'</t>
         </is>
       </c>
       <c r="G759" t="n">
@@ -27561,7 +27114,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>Robinia Pseudoacacia 'Frisia'</t>
+          <t>Robinia pseudoacacia 'Frisia'</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -27594,7 +27147,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Robinia Pseudoacacia 'Frisia'</t>
+          <t>Robinia pseudoacacia 'Frisia'</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -27627,7 +27180,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Robinia Pseudoacacia 'Frisia'</t>
+          <t>Robinia pseudoacacia 'Frisia'</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -27643,11 +27196,6 @@
       <c r="E762" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F762" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G762" t="n">
@@ -27665,7 +27213,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Salix Alba 'Tristis'</t>
+          <t>Salix alba 'Tristis'</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -27698,7 +27246,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Salix Alba 'Tristis'</t>
+          <t>Salix alba 'Tristis'</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -27736,7 +27284,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Salix Alba 'Tristis'</t>
+          <t>Salix alba 'Tristis'</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -27774,7 +27322,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Salix Alba 'Tristis'</t>
+          <t>Salix alba 'Tristis'</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -27812,7 +27360,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Salix Alba 'Tristis'</t>
+          <t>Salix alba 'Tristis'</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -27850,7 +27398,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Salix Babylonica 'Tortuosa'</t>
+          <t>Salix babylonica 'Tortuosa'</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -27883,7 +27431,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Salix Caprea 'Pendula'</t>
+          <t>Salix caprea 'Pendula'</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -27916,7 +27464,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Salix Caprea 'Pendula'</t>
+          <t>Salix caprea 'Pendula'</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -27949,7 +27497,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Salix Cinerea</t>
+          <t>Salix cinerea</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -27982,7 +27530,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Salix Integra 'Hakuro-Nishiki'</t>
+          <t>Salix integra 'Hakuro-nishiki'</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -28015,7 +27563,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Sambucus Nigra</t>
+          <t>Sambucus nigra</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -28048,7 +27596,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>Sequoia Sempervirens</t>
+          <t>Sequoia sempervirens</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -28081,7 +27629,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Sequoia Sempervirens</t>
+          <t>Sequoia sempervirens</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -28114,7 +27662,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>Sequoia Sempervirens</t>
+          <t>Sequoia sempervirens</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -28147,7 +27695,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Sophora Japonica</t>
+          <t>Sophora japonica</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -28180,7 +27728,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>Sorbus  'Golden Wonder'</t>
+          <t>Sorbus 'Golden Wonder'</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -28218,7 +27766,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Sorbus  'Golden Wonder'</t>
+          <t>Sorbus 'Golden Wonder'</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -28256,7 +27804,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Sorbus  'Golden Wonder'</t>
+          <t>Sorbus 'Golden Wonder'</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -28312,11 +27860,6 @@
           <t>150-200cm</t>
         </is>
       </c>
-      <c r="F781" t="inlineStr">
-        <is>
-          <t>0.</t>
-        </is>
-      </c>
       <c r="G781" t="n">
         <v>45</v>
       </c>
@@ -28388,11 +27931,6 @@
           <t>175 -200cm</t>
         </is>
       </c>
-      <c r="F783" t="inlineStr">
-        <is>
-          <t>0.</t>
-        </is>
-      </c>
       <c r="G783" t="n">
         <v>55</v>
       </c>
@@ -28441,7 +27979,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Sorbus Aria 'Lutescens'</t>
+          <t>Sorbus aria 'Lutescens'</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -28474,7 +28012,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>Sorbus Aria 'Magnifica'</t>
+          <t>Sorbus aria 'Magnifica'</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -28512,7 +28050,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>Sorbus Aria 'Magnifica'</t>
+          <t>Sorbus aria 'Magnifica'</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -28550,7 +28088,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>Sorbus Aria 'Magnifica'</t>
+          <t>Sorbus aria 'Magnifica'</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -28588,7 +28126,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>Sorbus Aria 'Magnifica'</t>
+          <t>Sorbus aria 'Magnifica'</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -28621,7 +28159,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>Sorbus Aucuparia</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -28637,11 +28175,6 @@
       <c r="E790" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F790" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G790" t="n">
@@ -28659,7 +28192,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>Sorbus Aucuparia</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -28697,7 +28230,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>Sorbus Aucuparia</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -28735,7 +28268,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Sorbus Aucuparia</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -28773,7 +28306,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>Sorbus Aucuparia</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -28811,7 +28344,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>Sorbus Aucuparia 'Autumn Spire'</t>
+          <t>Sorbus aucuparia 'Autumn Spire'</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -28844,7 +28377,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>Sorbus Aucuparia 'Fastigiata'</t>
+          <t>Sorbus aucuparia 'Fastigiata'</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -28877,7 +28410,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>Sorbus Aucuparia 'Sheerwater Seedling'</t>
+          <t>Sorbus aucuparia 'Sheerwater Seedling'</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -28910,7 +28443,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Sorbus Hupehensis 'Pink Pagoda'</t>
+          <t>Sorbus hupehensis 'Pink Pagoda'</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -28948,7 +28481,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Sorbus Hupehensis 'Pink Pagoda'</t>
+          <t>Sorbus hupehensis 'Pink Pagoda'</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -28986,7 +28519,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>Sorbus Intermedia</t>
+          <t>Sorbus intermedia</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -29019,7 +28552,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Sorbus Intermedia</t>
+          <t>Sorbus intermedia</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -29057,7 +28590,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>Sorbus Intermedia</t>
+          <t>Sorbus intermedia</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -29095,7 +28628,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Sorbus Pseudovilmorinii</t>
+          <t>Sorbus pseudovilmorinii</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -29128,7 +28661,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Sorbus Thur. 'Fastigiata'</t>
+          <t>Sorbus thur. 'Fastigiata'</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -29161,7 +28694,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Sorbus Thur. 'Fastigiata'</t>
+          <t>Sorbus thur. 'Fastigiata'</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -29199,7 +28732,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Sorbus Torminalis</t>
+          <t>Sorbus torminalis</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -29232,7 +28765,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Sorbus Torminalis</t>
+          <t>Sorbus torminalis</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -29270,7 +28803,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Sorbus Torminalis</t>
+          <t>Sorbus torminalis</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -29286,11 +28819,6 @@
       <c r="E808" t="inlineStr">
         <is>
           <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F808" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G808" t="n">
@@ -29308,7 +28836,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Sorbus Vilmorinii</t>
+          <t>Sorbus vilmorinii</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -29346,7 +28874,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Stewartia Pseudocamellia</t>
+          <t>Stewartia pseudocamellia</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -29379,7 +28907,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Syringa Vulgaris 'Madame Lemoine'</t>
+          <t>Syringa vulgaris 'Madame Lemoine'</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -29412,7 +28940,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>Taxodium Distichum</t>
+          <t>Taxodium distichum</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -29445,7 +28973,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Taxus Baccata</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -29478,7 +29006,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>Taxus Baccata</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -29511,7 +29039,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Taxus Baccata 'Fastigiata Robusta'</t>
+          <t>Taxus baccata 'Fastigiata Robusta'</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -29544,7 +29072,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>Taxus Baccata Fastigiata Aurea</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -29577,7 +29105,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Tetradium Daniellii</t>
+          <t>Tetradium daniellii</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -29593,11 +29121,6 @@
       <c r="E817" t="inlineStr">
         <is>
           <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F817" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G817" t="n">
@@ -29615,7 +29138,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Tetradium Daniellii</t>
+          <t>Tetradium daniellii</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -29648,7 +29171,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Thuja Occidentalis 'Smaragd'</t>
+          <t>Thuja occidentalis 'Smaragd'</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -29681,7 +29204,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Thuja Occidentalis 'Smaragd'</t>
+          <t>Thuja occidentalis 'Smaragd'</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -29714,7 +29237,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Thuja Occidentalis 'Smaragd'</t>
+          <t>Thuja occidentalis 'Smaragd'</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -29747,7 +29270,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>Thuja Plicata 'Atrovirens'</t>
+          <t>Thuja plicata 'Atrovirens'</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -29780,7 +29303,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Thujopsis Dolabrata</t>
+          <t>Thujopsis dolabrata</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -29813,7 +29336,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Tilia Americana 'American Sentry'</t>
+          <t>Tilia americana 'American Sentry'</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -29851,7 +29374,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Tilia Cordata</t>
+          <t>Tilia cordata</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -29889,7 +29412,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Tilia Cordata</t>
+          <t>Tilia cordata</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -29927,7 +29450,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Tilia Cordata</t>
+          <t>Tilia cordata</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -29965,7 +29488,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Tilia Cordata</t>
+          <t>Tilia cordata</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -30003,7 +29526,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Tilia Cordata</t>
+          <t>Tilia cordata</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -30036,7 +29559,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>Tilia Cordata 'Greenspire '</t>
+          <t>Tilia cordata 'Greenspire'</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -30052,11 +29575,6 @@
       <c r="E830" t="inlineStr">
         <is>
           <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F830" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G830" t="n">
@@ -30074,7 +29592,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Tilia Cordata 'Greenspire '</t>
+          <t>Tilia cordata 'Greenspire'</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -30107,7 +29625,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Tilia Cordata 'Greenspire '</t>
+          <t>Tilia cordata 'Greenspire'</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -30145,7 +29663,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Tilia Cordata 'Winter Orange'</t>
+          <t>Tilia cordata 'Winter Orange'</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -30161,11 +29679,6 @@
       <c r="E833" t="inlineStr">
         <is>
           <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F833" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G833" t="n">
@@ -30183,7 +29696,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>Tilia Cordata 'Winter Orange'</t>
+          <t>Tilia cordata 'Winter Orange'</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
@@ -30221,7 +29734,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Tilia Henryana</t>
+          <t>Tilia henryana</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -30259,7 +29772,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>Tilia Platyphyllos</t>
+          <t>Tilia platyphyllos</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -30292,7 +29805,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Tilia Platyphyllos 'Rubra'</t>
+          <t>Tilia platyphyllos 'Rubra'</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -30330,7 +29843,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Tilia X Euchlora</t>
+          <t>Tilia x</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -30363,7 +29876,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Tilia X Europaea 'Pallida'</t>
+          <t>Tilia x 'Pallida'</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -30401,7 +29914,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Tilia X Europaea 'Pallida'</t>
+          <t>Tilia x 'Pallida'</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -30417,11 +29930,6 @@
       <c r="E840" t="inlineStr">
         <is>
           <t>100-125 cm</t>
-        </is>
-      </c>
-      <c r="F840" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G840" t="n">
@@ -30439,7 +29947,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Tilia X Europaea 'Pallida'</t>
+          <t>Tilia x 'Pallida'</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -30472,7 +29980,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Tilia X Europaea 'Pallida'</t>
+          <t>Tilia x 'Pallida'</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -30510,7 +30018,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Tilia X Mongolica 'Harvest Gold'</t>
+          <t>Tilia x 'Harvest Gold'</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -30548,7 +30056,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Tilia X Mongolica 'Harvest Gold'</t>
+          <t>Tilia x 'Harvest Gold'</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -30586,7 +30094,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Tilia X Mongolica 'Harvest Gold'</t>
+          <t>Tilia x 'Harvest Gold'</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -30624,7 +30132,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Toona Sinensis</t>
+          <t>Toona sinensis</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -30662,7 +30170,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Toona Sinensis</t>
+          <t>Toona sinensis</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -30695,7 +30203,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>Tsuga Canadensis</t>
+          <t>Tsuga canadensis</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -30728,7 +30236,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Tsuga Canadensis</t>
+          <t>Tsuga canadensis</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -30761,7 +30269,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Tsuga Heterophylla</t>
+          <t>Tsuga heterophylla</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -30812,11 +30320,6 @@
           <t>200-250cm</t>
         </is>
       </c>
-      <c r="F851" t="inlineStr">
-        <is>
-          <t>0.</t>
-        </is>
-      </c>
       <c r="G851" t="n">
         <v>37.5</v>
       </c>
@@ -30870,7 +30373,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Ulmus Glabra 'Camperdownii'</t>
+          <t>Ulmus glabra 'Camperdownii'</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -30908,7 +30411,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Ulmus Hollandica ‘Wredei’</t>
+          <t>Ulmus hollandica</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -30941,7 +30444,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Ulmus Minor ‘Jacqueline Hillier’</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -30974,7 +30477,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Zelkova Serrata</t>
+          <t>Zelkova serrata</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -31012,7 +30515,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Zelkova Serrata</t>
+          <t>Zelkova serrata</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -31028,11 +30531,6 @@
       <c r="E857" t="inlineStr">
         <is>
           <t>75-100cm</t>
-        </is>
-      </c>
-      <c r="F857" t="inlineStr">
-        <is>
-          <t>0.</t>
         </is>
       </c>
       <c r="G857" t="n">
@@ -31050,7 +30548,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Zelkova Serrata 'Green Vase'</t>
+          <t>Zelkova serrata 'Green Vase'</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">

--- a/files/availability-list-2026.xlsx
+++ b/files/availability-list-2026.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abies alba</t>
+          <t>Abies Alba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abies concolor</t>
+          <t>Abies Concolor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abies concolor</t>
+          <t>Abies Concolor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Abies fraseri</t>
+          <t>Abies Fraseri</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Abies grandis</t>
+          <t>Abies Grandis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abies grandis</t>
+          <t>Abies Grandis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Abies grandis</t>
+          <t>Abies Grandis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abies koreana</t>
+          <t>Abies Koreana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Abies koreana</t>
+          <t>Abies Koreana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abies koreana</t>
+          <t>Abies Koreana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Abies koreana</t>
+          <t>Abies Koreana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abies lasiocarpa</t>
+          <t>Abies Lasiocarpa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abies nobilis</t>
+          <t>Abies Nobilis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abies nordmanniana</t>
+          <t>Abies Nordmanniana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abies nordmanniana</t>
+          <t>Abies Nordmanniana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abies nordmanniana</t>
+          <t>Abies Nordmanniana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abies pinsapo</t>
+          <t>Abies Pinsapo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abies pinsapo</t>
+          <t>Abies Pinsapo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Acacia dealbata</t>
+          <t>Acacia Dealbata</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Acacia melanoxylon</t>
+          <t>Acacia Melanoxylon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Acer buergerianum</t>
+          <t>Acer Buergerianum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Acer buergerianum</t>
+          <t>Acer Buergerianum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Acer campestre</t>
+          <t>Acer Campestre</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Acer campestre</t>
+          <t>Acer Campestre</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Acer campestre</t>
+          <t>Acer Campestre</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Acer campestre</t>
+          <t>Acer Campestre</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Acer campestre</t>
+          <t>Acer Campestre</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Acer campestre</t>
+          <t>Acer Campestre</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Acer carpinifolium</t>
+          <t>Acer Carpinifolium</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Acer davidii</t>
+          <t>Acer Davidii</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Acer davidii</t>
+          <t>Acer Davidii</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Acer davidii</t>
+          <t>Acer Davidii</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Acer davidii</t>
+          <t>Acer Davidii</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Acer davidii</t>
+          <t>Acer Davidii</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Acer ginnala</t>
+          <t>Acer Ginnala</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Acer ginnala</t>
+          <t>Acer Ginnala</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Acer griseum</t>
+          <t>Acer Griseum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Acer griseum</t>
+          <t>Acer Griseum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Acer griseum</t>
+          <t>Acer Griseum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Acer monspessulanum</t>
+          <t>Acer Monspessulanum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Acer monspessulanum</t>
+          <t>Acer Monspessulanum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Acer palmatum</t>
+          <t>Acer Palmatum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Acer palmatum</t>
+          <t>Acer Palmatum</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Acer plat.</t>
+          <t>Acer Plat.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Acer plat.</t>
+          <t>Acer Plat.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Acer plat.</t>
+          <t>Acer Plat.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Acer plat.</t>
+          <t>Acer Plat.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Acer plat.</t>
+          <t>Acer Plat.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Acer plat.</t>
+          <t>Acer Plat.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Acer plat.</t>
+          <t>Acer Plat.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Acer plat.</t>
+          <t>Acer Plat.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Acer pseudoplatanus</t>
+          <t>Acer Pseudoplatanus</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Acer pseudoplatanus</t>
+          <t>Acer Pseudoplatanus</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Acer pseudoplatanus</t>
+          <t>Acer Pseudoplatanus</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Acer pseudoplatanus</t>
+          <t>Acer Pseudoplatanus</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Acer pseudoplatanus</t>
+          <t>Acer Pseudoplatanus</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Acer pseudoplatanus</t>
+          <t>Acer Pseudoplatanus</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Acer pseudoplatanus</t>
+          <t>Acer Pseudoplatanus</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Acer pseudoplatanus</t>
+          <t>Acer Pseudoplatanus</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Acer rubrum</t>
+          <t>Acer Rubrum</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Acer rubrum</t>
+          <t>Acer Rubrum</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Acer rubrum</t>
+          <t>Acer Rubrum</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Acer rubrum</t>
+          <t>Acer Rubrum</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Acer saccharinum</t>
+          <t>Acer Saccharinum</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Acer saccharinum</t>
+          <t>Acer Saccharinum</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Acer saccharinum</t>
+          <t>Acer Saccharinum</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Acer saccharinum</t>
+          <t>Acer Saccharinum</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Acer saccharinum</t>
+          <t>Acer Saccharinum</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Acer saccharinum</t>
+          <t>Acer Saccharinum</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Acer saccharinum</t>
+          <t>Acer Saccharinum</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Aesculus hippocastanum</t>
+          <t>Aesculus Hippocastanum</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Aesculus hippocastanum</t>
+          <t>Aesculus Hippocastanum</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Aesculus hippocastanum</t>
+          <t>Aesculus Hippocastanum</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Aesculus indica</t>
+          <t>Aesculus Indica</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Albizia julibrissin</t>
+          <t>Albizia Julibrissin</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Alnus cordata</t>
+          <t>Alnus Cordata</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Alnus cordata</t>
+          <t>Alnus Cordata</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Alnus cordata</t>
+          <t>Alnus Cordata</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Alnus cordata</t>
+          <t>Alnus Cordata</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Alnus Glutinosa</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Alnus Glutinosa</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Alnus Glutinosa</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Alnus Glutinosa</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Alnus Glutinosa</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Alnus Glutinosa</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Alnus Glutinosa</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Alnus Glutinosa</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Alnus x</t>
+          <t>Alnus X</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Alnus x</t>
+          <t>Alnus X</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Amelanchier canadensis</t>
+          <t>Amelanchier Canadensis</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Amelanchier lamarckii</t>
+          <t>Amelanchier Lamarckii</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Amelanchier lamarckii</t>
+          <t>Amelanchier Lamarckii</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Amelanchier lamarckii</t>
+          <t>Amelanchier Lamarckii</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Amelanchier lamarckii</t>
+          <t>Amelanchier Lamarckii</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Amelanchier lamarckii</t>
+          <t>Amelanchier Lamarckii</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Amelanchier lamarckii</t>
+          <t>Amelanchier Lamarckii</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Amelanchier lamarckii</t>
+          <t>Amelanchier Lamarckii</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Amelanchier lamarckii</t>
+          <t>Amelanchier Lamarckii</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Amelanchier lamarckii</t>
+          <t>Amelanchier Lamarckii</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Aralia elata</t>
+          <t>Aralia Elata</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Aralia elata</t>
+          <t>Aralia Elata</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Aralia elata</t>
+          <t>Aralia Elata</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Araucaria araucana</t>
+          <t>Araucaria Araucana</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Arbutus unedo</t>
+          <t>Arbutus Unedo</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Arbutus unedo</t>
+          <t>Arbutus Unedo</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Betula albosinensis</t>
+          <t>Betula Albosinensis</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Betula ermanii</t>
+          <t>Betula Ermanii</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Betula ermanii</t>
+          <t>Betula Ermanii</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Betula nigra</t>
+          <t>Betula Nigra</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Betula nigra</t>
+          <t>Betula Nigra</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Betula nigra</t>
+          <t>Betula Nigra</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Betula nigra</t>
+          <t>Betula Nigra</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Betula papyrifera</t>
+          <t>Betula Papyrifera</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Betula papyrifera</t>
+          <t>Betula Papyrifera</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Betula papyrifera</t>
+          <t>Betula Papyrifera</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Betula Pendula</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Betula Pubescens</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Betula Pubescens</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Betula Pubescens</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Betula Pubescens</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Betula Pubescens</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Betula Pubescens</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Betula Pubescens</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Betula utilis</t>
+          <t>Betula Utilis</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Betula utilis</t>
+          <t>Betula Utilis</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Betula utilis</t>
+          <t>Betula Utilis</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Carpinus Betulus</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Carpinus Betulus</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Carpinus Betulus</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Carpinus Betulus</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Carpinus Betulus</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Carpinus Betulus</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Carpinus Betulus</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Carpinus Betulus</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Carpinus japonica</t>
+          <t>Carpinus Japonica</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Carpinus japonica</t>
+          <t>Carpinus Japonica</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Carya illinoinensis</t>
+          <t>Carya Illinoinensis</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Carya ovata</t>
+          <t>Carya Ovata</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Castanea sativa</t>
+          <t>Castanea Sativa</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Castanea sativa</t>
+          <t>Castanea Sativa</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Catalpa bignonioides</t>
+          <t>Catalpa Bignonioides</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Catalpa bignonioides</t>
+          <t>Catalpa Bignonioides</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Catalpa bignonioides</t>
+          <t>Catalpa Bignonioides</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Catalpa bignonioides</t>
+          <t>Catalpa Bignonioides</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Catalpa bignonioides</t>
+          <t>Catalpa Bignonioides</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Catalpa bignonioides</t>
+          <t>Catalpa Bignonioides</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Catalpa bignonioides</t>
+          <t>Catalpa Bignonioides</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Cedrus atlantica</t>
+          <t>Cedrus Atlantica</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Cedrus atlantica</t>
+          <t>Cedrus Atlantica</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Cedrus atlantica</t>
+          <t>Cedrus Atlantica</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Cedrus atlantica</t>
+          <t>Cedrus Atlantica</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Cedrus deodara</t>
+          <t>Cedrus Deodara</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Cedrus deodara</t>
+          <t>Cedrus Deodara</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Cedrus libani</t>
+          <t>Cedrus Libani</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Celtis sinensis</t>
+          <t>Celtis Sinensis</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Cercidiphyllum japonicum</t>
+          <t>Cercidiphyllum Japonicum</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Cercidiphyllum japonicum</t>
+          <t>Cercidiphyllum Japonicum</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Cercidiphyllum japonicum</t>
+          <t>Cercidiphyllum Japonicum</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Cercidiphyllum japonicum</t>
+          <t>Cercidiphyllum Japonicum</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Chamaecyparis l.</t>
+          <t>Chamaecyparis L.</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Chamaecyparis lawonsonia</t>
+          <t>Chamaecyparis Lawonsonia</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Cladrastis kentukea</t>
+          <t>Cladrastis Kentukea</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Cladrastis kentukea</t>
+          <t>Cladrastis Kentukea</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Cordyline australis</t>
+          <t>Cordyline Australis</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Cornus controversa</t>
+          <t>Cornus Controversa</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Cornus florida</t>
+          <t>Cornus Florida</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Cornus kousa</t>
+          <t>Cornus Kousa</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Cornus kousa</t>
+          <t>Cornus Kousa</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Cornus kousa</t>
+          <t>Cornus Kousa</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Cornus mas</t>
+          <t>Cornus Mas</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Cornus mas</t>
+          <t>Cornus Mas</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -11722,7 +11722,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Cornus mas</t>
+          <t>Cornus Mas</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Cornus mas</t>
+          <t>Cornus Mas</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Cornus wilsoniana</t>
+          <t>Cornus Wilsoniana</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Corylus avellana</t>
+          <t>Corylus Avellana</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Corylus avellana</t>
+          <t>Corylus Avellana</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Corylus colurna</t>
+          <t>Corylus Colurna</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Corylus colurna</t>
+          <t>Corylus Colurna</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Crataegus monogyna</t>
+          <t>Crataegus Monogyna</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Crateagus monogyna</t>
+          <t>Crateagus Monogyna</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Cupressus macrocarpa</t>
+          <t>Cupressus Macrocarpa</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Cupressus macrocarpa</t>
+          <t>Cupressus Macrocarpa</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Davidia involucrata</t>
+          <t>Davidia Involucrata</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Davidia involucrata</t>
+          <t>Davidia Involucrata</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Eucalyptus dalrympleana</t>
+          <t>Eucalyptus Dalrympleana</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Eucalyptus gunnii</t>
+          <t>Eucalyptus Gunnii</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Eucalyptus moorei</t>
+          <t>Eucalyptus Moorei</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Eucalyptus perriniana</t>
+          <t>Eucalyptus Perriniana</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Fagus syl.</t>
+          <t>Fagus Syl.</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Fagus Sylvatica</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Fagus Sylvatica</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Fagus Sylvatica</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -13589,7 +13589,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Fagus Sylvatica</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -13622,7 +13622,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Fargesia robusta</t>
+          <t>Fargesia Robusta</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Fraxinus angustifolia</t>
+          <t>Fraxinus Angustifolia</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Gift card</t>
+          <t>Gift Card</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Ginkgo biloba</t>
+          <t>Ginkgo Biloba</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Ginkgo biloba</t>
+          <t>Ginkgo Biloba</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -13921,7 +13921,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Ginkgo biloba</t>
+          <t>Ginkgo Biloba</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Ginkgo biloba</t>
+          <t>Ginkgo Biloba</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Ginkgo biloba</t>
+          <t>Ginkgo Biloba</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Ginkgo biloba</t>
+          <t>Ginkgo Biloba</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Halesia carolina</t>
+          <t>Halesia Carolina</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Halesia carolina</t>
+          <t>Halesia Carolina</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Halesia carolina</t>
+          <t>Halesia Carolina</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Heptacodium miconioides</t>
+          <t>Heptacodium Miconioides</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -14426,7 +14426,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Heptacodium miconioides</t>
+          <t>Heptacodium Miconioides</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Heptacodium miconioides</t>
+          <t>Heptacodium Miconioides</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Ilex aquifolium</t>
+          <t>Ilex Aquifolium</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Ilex aquifolium</t>
+          <t>Ilex Aquifolium</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Juglans nigra</t>
+          <t>Juglans Nigra</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Juglans nigra</t>
+          <t>Juglans Nigra</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -14733,7 +14733,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Juglans nigra</t>
+          <t>Juglans Nigra</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Juglans nigra</t>
+          <t>Juglans Nigra</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Juglans regia</t>
+          <t>Juglans Regia</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Juglans regia</t>
+          <t>Juglans Regia</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Juglans regia</t>
+          <t>Juglans Regia</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -15050,7 +15050,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Koelreuteria paniculata</t>
+          <t>Koelreuteria Paniculata</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Koelreuteria paniculata</t>
+          <t>Koelreuteria Paniculata</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -15121,7 +15121,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Koelreuteria paniculata</t>
+          <t>Koelreuteria Paniculata</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Koelreuteria paniculata</t>
+          <t>Koelreuteria Paniculata</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -15225,7 +15225,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Larix decidua</t>
+          <t>Larix Decidua</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Larix kaempferi</t>
+          <t>Larix Kaempferi</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Larix kaempferi</t>
+          <t>Larix Kaempferi</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Larix kaempferi</t>
+          <t>Larix Kaempferi</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -15357,7 +15357,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Laurus nobilis</t>
+          <t>Laurus Nobilis</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Laurus nobilis</t>
+          <t>Laurus Nobilis</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Liquidambar styraciflua</t>
+          <t>Liquidambar Styraciflua</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Liquidambar styraciflua</t>
+          <t>Liquidambar Styraciflua</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -15499,7 +15499,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Liquidambar styraciflua</t>
+          <t>Liquidambar Styraciflua</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -15537,7 +15537,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Liquidambar styraciflua</t>
+          <t>Liquidambar Styraciflua</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Liriodendron tulipifera</t>
+          <t>Liriodendron Tulipifera</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -15968,7 +15968,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Liriodendron tulipifera</t>
+          <t>Liriodendron Tulipifera</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Liriodendron tulipifera</t>
+          <t>Liriodendron Tulipifera</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -16034,7 +16034,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Liriodendron tulipifera</t>
+          <t>Liriodendron Tulipifera</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Liriodendron tulipifera</t>
+          <t>Liriodendron Tulipifera</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Magnolia grandiflora</t>
+          <t>Magnolia Grandiflora</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -16521,7 +16521,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Magnolia kobus</t>
+          <t>Magnolia Kobus</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Magnolia stellata</t>
+          <t>Magnolia Stellata</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Magnolia stellata</t>
+          <t>Magnolia Stellata</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Malus baccata</t>
+          <t>Malus Baccata</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Malus domestica</t>
+          <t>Malus Domestica</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Malus sylvestris</t>
+          <t>Malus Sylvestris</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Malus trilobata</t>
+          <t>Malus Trilobata</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -18601,7 +18601,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Malus trilobata</t>
+          <t>Malus Trilobata</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -18639,7 +18639,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Malus trilobata</t>
+          <t>Malus Trilobata</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -18677,7 +18677,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Malus trilobata</t>
+          <t>Malus Trilobata</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Malus trilobata</t>
+          <t>Malus Trilobata</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -18753,7 +18753,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Malus trilobata</t>
+          <t>Malus Trilobata</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Mespilus germanica</t>
+          <t>Mespilus Germanica</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Metasequoia glytostroboides</t>
+          <t>Metasequoia Glytostroboides</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Metasequoia glytostroboides</t>
+          <t>Metasequoia Glytostroboides</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -18900,7 +18900,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Metasequoia glytostroboides</t>
+          <t>Metasequoia Glytostroboides</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Metasequoia glytostroboides</t>
+          <t>Metasequoia Glytostroboides</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -18976,7 +18976,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Metasequoia glytostroboides</t>
+          <t>Metasequoia Glytostroboides</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -19014,7 +19014,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Metasequoia glytostroboides</t>
+          <t>Metasequoia Glytostroboides</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Morus alba</t>
+          <t>Morus Alba</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -19085,7 +19085,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Morus alba</t>
+          <t>Morus Alba</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Morus alba</t>
+          <t>Morus Alba</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -19151,7 +19151,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Morus nigra</t>
+          <t>Morus Nigra</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -19184,7 +19184,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Nothofagus antarctica</t>
+          <t>Nothofagus Antarctica</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -19217,7 +19217,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Nyssa sylvatica</t>
+          <t>Nyssa Sylvatica</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Nyssa sylvatica</t>
+          <t>Nyssa Sylvatica</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Nyssa sylvatica</t>
+          <t>Nyssa Sylvatica</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Ostrya carpinifolia</t>
+          <t>Ostrya Carpinifolia</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Ostrya carpinifolia</t>
+          <t>Ostrya Carpinifolia</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Ostrya carpinifolia</t>
+          <t>Ostrya Carpinifolia</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Parrotia persica</t>
+          <t>Parrotia Persica</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Parrotia persica</t>
+          <t>Parrotia Persica</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -19704,7 +19704,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Paulownia tomentosa</t>
+          <t>Paulownia Tomentosa</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -19742,7 +19742,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Paulownia tomentosa</t>
+          <t>Paulownia Tomentosa</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -19775,7 +19775,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Phellodendron amurense</t>
+          <t>Phellodendron Amurense</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -19808,7 +19808,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea Abies</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea Abies</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea Abies</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Picea omorika</t>
+          <t>Picea Omorika</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Picea pungens</t>
+          <t>Picea Pungens</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -20006,7 +20006,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Picea sitchensis</t>
+          <t>Picea Sitchensis</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Pinus armandii</t>
+          <t>Pinus Armandii</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -20072,7 +20072,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Pinus contorta</t>
+          <t>Pinus Contorta</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Pinus halepensis</t>
+          <t>Pinus Halepensis</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Pinus mugo</t>
+          <t>Pinus Mugo</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -20171,7 +20171,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Pinus mugo</t>
+          <t>Pinus Mugo</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Pinus mugo</t>
+          <t>Pinus Mugo</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -20237,7 +20237,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Pinus nigra</t>
+          <t>Pinus Nigra</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -20270,7 +20270,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Pinus nigra</t>
+          <t>Pinus Nigra</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -20303,7 +20303,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Pinus nigra</t>
+          <t>Pinus Nigra</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -20336,7 +20336,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Pinus nigra</t>
+          <t>Pinus Nigra</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Pinus pinaster</t>
+          <t>Pinus Pinaster</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Pinus pinaster</t>
+          <t>Pinus Pinaster</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -20445,7 +20445,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Pinus pinea</t>
+          <t>Pinus Pinea</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -20478,7 +20478,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Pinus ponderosa</t>
+          <t>Pinus Ponderosa</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Pinus strobus</t>
+          <t>Pinus Strobus</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -20544,7 +20544,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Pinus strobus</t>
+          <t>Pinus Strobus</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -20577,7 +20577,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Pinus strobus</t>
+          <t>Pinus Strobus</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -20610,7 +20610,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Pinus Sylvestris</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -20643,7 +20643,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Pinus Sylvestris</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -20676,7 +20676,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Pinus tabuliformis</t>
+          <t>Pinus Tabuliformis</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -20709,7 +20709,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Pinus tabuliformis</t>
+          <t>Pinus Tabuliformis</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Pinus wallichiana</t>
+          <t>Pinus Wallichiana</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -20775,7 +20775,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Pinus wallichiana</t>
+          <t>Pinus Wallichiana</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -20808,7 +20808,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Platanus orientalis</t>
+          <t>Platanus Orientalis</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -20841,7 +20841,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Platanus orientalis</t>
+          <t>Platanus Orientalis</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Platanus orientalis</t>
+          <t>Platanus Orientalis</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -20912,7 +20912,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Platanus orientalis</t>
+          <t>Platanus Orientalis</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -20950,7 +20950,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Platanus orientalis</t>
+          <t>Platanus Orientalis</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Platanus orientalis</t>
+          <t>Platanus Orientalis</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -21026,7 +21026,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Platanus x</t>
+          <t>Platanus X</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -21059,7 +21059,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Platanus x</t>
+          <t>Platanus X</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -21097,7 +21097,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Platanus x</t>
+          <t>Platanus X</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -21135,7 +21135,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Platanus x</t>
+          <t>Platanus X</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -21173,7 +21173,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Platanus x</t>
+          <t>Platanus X</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -21211,7 +21211,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Platanus x</t>
+          <t>Platanus X</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -21249,7 +21249,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Populus alba</t>
+          <t>Populus Alba</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -21282,7 +21282,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Populus Tremula</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Populus Tremula</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -21353,7 +21353,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Populus Tremula</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Populus Tremula</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -21429,7 +21429,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Populus Tremula</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -21467,7 +21467,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Populus Tremula</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -21959,7 +21959,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Prunus avium</t>
+          <t>Prunus Avium</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Prunus avium</t>
+          <t>Prunus Avium</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Prunus l.</t>
+          <t>Prunus L.</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -22664,7 +22664,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Prunus l.</t>
+          <t>Prunus L.</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -22882,7 +22882,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Prunus padus</t>
+          <t>Prunus Padus</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -23067,7 +23067,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Prunus serrulata</t>
+          <t>Prunus Serrulata</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -23100,7 +23100,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Prunus serrulata</t>
+          <t>Prunus Serrulata</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -23133,7 +23133,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Prunus serrulata</t>
+          <t>Prunus Serrulata</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -23171,7 +23171,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Prunus serrulata</t>
+          <t>Prunus Serrulata</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -23209,7 +23209,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Prunus serrulata</t>
+          <t>Prunus Serrulata</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -23247,7 +23247,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Prunus serrulata</t>
+          <t>Prunus Serrulata</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -23318,7 +23318,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Prunus serrulata</t>
+          <t>Prunus Serrulata</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -23465,7 +23465,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Pterocarya fraxinifolia</t>
+          <t>Pterocarya Fraxinifolia</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -23503,7 +23503,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Pterocarya fraxinifolia</t>
+          <t>Pterocarya Fraxinifolia</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -23536,7 +23536,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Pterocarya fraxinifolia</t>
+          <t>Pterocarya Fraxinifolia</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -23574,7 +23574,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Pyrus calleryana</t>
+          <t>Pyrus Calleryana</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Pyrus communis</t>
+          <t>Pyrus Communis</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -23967,7 +23967,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Pyrus communis</t>
+          <t>Pyrus Communis</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -24170,7 +24170,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Pyrus salicifolia</t>
+          <t>Pyrus Salicifolia</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Quercus acutissima</t>
+          <t>Quercus Acutissima</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -24246,7 +24246,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Quercus acutissima</t>
+          <t>Quercus Acutissima</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -24284,7 +24284,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Quercus acutissima</t>
+          <t>Quercus Acutissima</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -24322,7 +24322,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Quercus acutissima</t>
+          <t>Quercus Acutissima</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Quercus acutissima</t>
+          <t>Quercus Acutissima</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Quercus bicolor</t>
+          <t>Quercus Bicolor</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -24426,7 +24426,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Quercus buckleyi</t>
+          <t>Quercus Buckleyi</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -24568,7 +24568,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Quercus cerris</t>
+          <t>Quercus Cerris</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -24601,7 +24601,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Quercus cerris</t>
+          <t>Quercus Cerris</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -24639,7 +24639,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Quercus cerris</t>
+          <t>Quercus Cerris</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -24677,7 +24677,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Quercus cerris</t>
+          <t>Quercus Cerris</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -24715,7 +24715,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Quercus cerris</t>
+          <t>Quercus Cerris</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -24753,7 +24753,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Quercus cerris</t>
+          <t>Quercus Cerris</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -24791,7 +24791,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Quercus coccinea</t>
+          <t>Quercus Coccinea</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -24857,7 +24857,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Quercus ilex</t>
+          <t>Quercus Ilex</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -24890,7 +24890,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Quercus ilex</t>
+          <t>Quercus Ilex</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -24928,7 +24928,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Quercus ilex</t>
+          <t>Quercus Ilex</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -24966,7 +24966,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Quercus ilex</t>
+          <t>Quercus Ilex</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -24999,7 +24999,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Quercus imbricaria</t>
+          <t>Quercus Imbricaria</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -25032,7 +25032,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Quercus imbricaria</t>
+          <t>Quercus Imbricaria</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -25070,7 +25070,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Quercus macrocarpa</t>
+          <t>Quercus Macrocarpa</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -25103,7 +25103,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Quercus myrsinifolia</t>
+          <t>Quercus Myrsinifolia</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -25136,7 +25136,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Quercus myrsinifolia</t>
+          <t>Quercus Myrsinifolia</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -25169,7 +25169,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Quercus nigra</t>
+          <t>Quercus Nigra</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -25202,7 +25202,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Quercus nigra</t>
+          <t>Quercus Nigra</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -25240,7 +25240,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Quercus nigra</t>
+          <t>Quercus Nigra</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -25278,7 +25278,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Quercus nigra</t>
+          <t>Quercus Nigra</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -25311,7 +25311,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Quercus palustris</t>
+          <t>Quercus Palustris</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -25344,7 +25344,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Quercus palustris</t>
+          <t>Quercus Palustris</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Quercus palustris</t>
+          <t>Quercus Palustris</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -25415,7 +25415,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Quercus palustris</t>
+          <t>Quercus Palustris</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -25453,7 +25453,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Quercus palustris</t>
+          <t>Quercus Palustris</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -25628,7 +25628,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Quercus petraea</t>
+          <t>Quercus Petraea</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -25661,7 +25661,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Quercus petraea</t>
+          <t>Quercus Petraea</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Quercus petraea</t>
+          <t>Quercus Petraea</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Quercus phellos</t>
+          <t>Quercus Phellos</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Quercus phillyreoides</t>
+          <t>Quercus Phillyreoides</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Quercus phillyreoides</t>
+          <t>Quercus Phillyreoides</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -25836,7 +25836,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Quercus phillyreoides</t>
+          <t>Quercus Phillyreoides</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -25869,7 +25869,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Quercus pubescens</t>
+          <t>Quercus Pubescens</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -25902,7 +25902,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Quercus pubescens</t>
+          <t>Quercus Pubescens</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -25940,7 +25940,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Quercus pubescens</t>
+          <t>Quercus Pubescens</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -25978,7 +25978,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Quercus pubescens</t>
+          <t>Quercus Pubescens</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -26016,7 +26016,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Quercus pyrenaica</t>
+          <t>Quercus Pyrenaica</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Quercus Robur</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -26087,7 +26087,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Quercus Robur</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -26125,7 +26125,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Quercus Robur</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -26158,7 +26158,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Quercus Robur</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -26196,7 +26196,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Quercus Robur</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -26229,7 +26229,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Quercus Robur</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -26267,7 +26267,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Quercus Robur</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -26305,7 +26305,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Quercus Robur</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -26343,7 +26343,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Quercus Robur</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -26452,7 +26452,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Quercus rubra</t>
+          <t>Quercus Rubra</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -26485,7 +26485,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Quercus rubra</t>
+          <t>Quercus Rubra</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -26518,7 +26518,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Quercus rubra</t>
+          <t>Quercus Rubra</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -26556,7 +26556,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Quercus rubra</t>
+          <t>Quercus Rubra</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Quercus rubra</t>
+          <t>Quercus Rubra</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -26627,7 +26627,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Quercus suber</t>
+          <t>Quercus Suber</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -26660,7 +26660,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Quercus texana</t>
+          <t>Quercus Texana</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -26769,7 +26769,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Rhus typhina</t>
+          <t>Rhus Typhina</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -26802,7 +26802,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Rhus typhina</t>
+          <t>Rhus Typhina</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -26835,7 +26835,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Rhus typhina</t>
+          <t>Rhus Typhina</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -26868,7 +26868,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Rhus typhina</t>
+          <t>Rhus Typhina</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Rhus typhina</t>
+          <t>Rhus Typhina</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -26934,7 +26934,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Rhus typhina</t>
+          <t>Rhus Typhina</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -26972,7 +26972,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Rhus typhina</t>
+          <t>Rhus Typhina</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -27497,7 +27497,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Salix cinerea</t>
+          <t>Salix Cinerea</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Sambucus nigra</t>
+          <t>Sambucus Nigra</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -27596,7 +27596,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>Sequoia sempervirens</t>
+          <t>Sequoia Sempervirens</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -27629,7 +27629,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Sequoia sempervirens</t>
+          <t>Sequoia Sempervirens</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -27662,7 +27662,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>Sequoia sempervirens</t>
+          <t>Sequoia Sempervirens</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -27695,7 +27695,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Sophora japonica</t>
+          <t>Sophora Japonica</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -28159,7 +28159,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Sorbus Aucuparia</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -28192,7 +28192,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Sorbus Aucuparia</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -28230,7 +28230,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Sorbus Aucuparia</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -28268,7 +28268,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Sorbus Aucuparia</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -28306,7 +28306,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Sorbus Aucuparia</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -28519,7 +28519,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>Sorbus intermedia</t>
+          <t>Sorbus Intermedia</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Sorbus intermedia</t>
+          <t>Sorbus Intermedia</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -28590,7 +28590,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>Sorbus intermedia</t>
+          <t>Sorbus Intermedia</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -28628,7 +28628,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Sorbus pseudovilmorinii</t>
+          <t>Sorbus Pseudovilmorinii</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -28732,7 +28732,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Sorbus torminalis</t>
+          <t>Sorbus Torminalis</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -28765,7 +28765,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Sorbus torminalis</t>
+          <t>Sorbus Torminalis</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -28803,7 +28803,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Sorbus torminalis</t>
+          <t>Sorbus Torminalis</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -28836,7 +28836,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Sorbus vilmorinii</t>
+          <t>Sorbus Vilmorinii</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Stewartia pseudocamellia</t>
+          <t>Stewartia Pseudocamellia</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -28940,7 +28940,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>Taxodium distichum</t>
+          <t>Taxodium Distichum</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -28973,7 +28973,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Taxus Baccata</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -29006,7 +29006,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Taxus Baccata</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -29072,7 +29072,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Taxus Baccata</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -29105,7 +29105,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Tetradium daniellii</t>
+          <t>Tetradium Daniellii</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -29138,7 +29138,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Tetradium daniellii</t>
+          <t>Tetradium Daniellii</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -29303,7 +29303,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Thujopsis dolabrata</t>
+          <t>Thujopsis Dolabrata</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -29374,7 +29374,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Tilia cordata</t>
+          <t>Tilia Cordata</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -29412,7 +29412,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Tilia cordata</t>
+          <t>Tilia Cordata</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -29450,7 +29450,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Tilia cordata</t>
+          <t>Tilia Cordata</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -29488,7 +29488,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Tilia cordata</t>
+          <t>Tilia Cordata</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Tilia cordata</t>
+          <t>Tilia Cordata</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -29734,7 +29734,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Tilia henryana</t>
+          <t>Tilia Henryana</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>Tilia platyphyllos</t>
+          <t>Tilia Platyphyllos</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Tilia x</t>
+          <t>Tilia X</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -30132,7 +30132,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Toona sinensis</t>
+          <t>Toona Sinensis</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -30170,7 +30170,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Toona sinensis</t>
+          <t>Toona Sinensis</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -30203,7 +30203,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>Tsuga canadensis</t>
+          <t>Tsuga Canadensis</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -30236,7 +30236,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Tsuga canadensis</t>
+          <t>Tsuga Canadensis</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -30269,7 +30269,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Tsuga heterophylla</t>
+          <t>Tsuga Heterophylla</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -30411,7 +30411,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Ulmus hollandica</t>
+          <t>Ulmus Hollandica</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -30444,7 +30444,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Ulmus Minor</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -30477,7 +30477,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Zelkova serrata</t>
+          <t>Zelkova Serrata</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -30515,7 +30515,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Zelkova serrata</t>
+          <t>Zelkova Serrata</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">

--- a/files/availability-list-2026.xlsx
+++ b/files/availability-list-2026.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,9 +49,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,42 +456,42 @@
   <sheetData>
     <row r="1" ht="85" customHeight="1"/>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Botanical Name</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Common Name</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Pot Size</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Height (cm)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Girth (cm)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Price (GBP)</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>

--- a/files/availability-list-2026.xlsx
+++ b/files/availability-list-2026.xlsx
@@ -427,17 +427,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H574"/>
+  <dimension ref="A2:G574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -453,30 +452,25 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Common Name</t>
+          <t>Pot Size</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Pot Size</t>
+          <t>Height (cm)</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Height (cm)</t>
+          <t>Girth (cm)</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>Girth (cm)</t>
+          <t>Price (GBP)</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>Price (GBP)</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
@@ -496,11 +490,10 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -518,11 +511,10 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>8.5</v>
+      </c>
       <c r="G4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H4" t="n">
         <v>-10</v>
       </c>
     </row>
@@ -540,12 +532,11 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>70</v>
+      </c>
       <c r="G5" t="n">
-        <v>70</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -562,12 +553,11 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G6" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -584,12 +574,11 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G7" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -606,12 +595,11 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G8" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -628,12 +616,11 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>195</v>
+      </c>
       <c r="G9" t="n">
-        <v>195</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -650,12 +637,11 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>650</v>
+      </c>
       <c r="G10" t="n">
-        <v>650</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -672,12 +658,11 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>325</v>
+      </c>
       <c r="G11" t="n">
-        <v>325</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -694,12 +679,11 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>395</v>
+      </c>
       <c r="G12" t="n">
-        <v>395</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -716,12 +700,11 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G13" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -738,12 +721,11 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G14" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -760,12 +742,11 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G15" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
@@ -782,12 +763,11 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G16" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -804,12 +784,11 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>18</v>
+      </c>
       <c r="G17" t="n">
-        <v>18</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
@@ -826,12 +805,11 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G18" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
@@ -848,12 +826,11 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G19" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -870,12 +847,11 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>18</v>
+      </c>
       <c r="G20" t="n">
-        <v>18</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -892,12 +868,11 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>18</v>
+      </c>
       <c r="G21" t="n">
         <v>18</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -914,12 +889,11 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>45</v>
+      </c>
       <c r="G22" t="n">
-        <v>45</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -936,12 +910,11 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G23" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -958,12 +931,11 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G24" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -980,12 +952,11 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>195</v>
+      </c>
       <c r="G25" t="n">
-        <v>195</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1002,12 +973,11 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>270</v>
+      </c>
       <c r="G26" t="n">
-        <v>270</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1024,12 +994,11 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>42</v>
+      </c>
       <c r="G27" t="n">
-        <v>42</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -1046,12 +1015,11 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G28" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -1068,12 +1036,11 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G29" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
@@ -1090,12 +1057,11 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G30" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
@@ -1112,12 +1078,11 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G31" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
@@ -1134,12 +1099,11 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G32" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
@@ -1156,12 +1120,11 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G33" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
@@ -1178,12 +1141,11 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G34" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -1200,12 +1162,11 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>24</v>
+      </c>
       <c r="G35" t="n">
-        <v>24</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
@@ -1222,12 +1183,11 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G36" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37">
@@ -1244,12 +1204,11 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G37" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
@@ -1266,12 +1225,11 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G38" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
@@ -1288,12 +1246,11 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G39" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40">
@@ -1310,12 +1267,11 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>16.5</v>
+      </c>
       <c r="G40" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41">
@@ -1332,12 +1288,11 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G41" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -1354,12 +1309,11 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G42" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43">
@@ -1376,12 +1330,11 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G43" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44">
@@ -1398,12 +1351,11 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G44" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -1420,12 +1372,11 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G45" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46">
@@ -1442,12 +1393,11 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G46" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
@@ -1464,12 +1414,11 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G47" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48">
@@ -1486,12 +1435,11 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G48" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49">
@@ -1508,11 +1456,10 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
       <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1530,12 +1477,11 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>65</v>
+      </c>
       <c r="G50" t="n">
-        <v>65</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -1552,12 +1498,11 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G51" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52">
@@ -1574,11 +1519,10 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
       <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -1596,11 +1540,10 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
       <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1618,12 +1561,11 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G54" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -1640,12 +1582,11 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="n">
+        <v>135</v>
+      </c>
       <c r="G55" t="n">
-        <v>135</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -1662,11 +1603,10 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
       <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1684,12 +1624,11 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G57" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
@@ -1706,11 +1645,10 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
       <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1728,11 +1666,10 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
       <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1750,11 +1687,10 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
       <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1772,11 +1708,10 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>2.75</v>
+      </c>
       <c r="G61" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="H61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1794,11 +1729,10 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>105</v>
+      </c>
       <c r="G62" t="n">
-        <v>105</v>
-      </c>
-      <c r="H62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1816,12 +1750,11 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="n">
+        <v>125</v>
+      </c>
       <c r="G63" t="n">
-        <v>125</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -1838,12 +1771,11 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G64" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65">
@@ -1860,11 +1792,10 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>5</v>
+      </c>
       <c r="G65" t="n">
-        <v>5</v>
-      </c>
-      <c r="H65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1882,12 +1813,11 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G66" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67">
@@ -1904,12 +1834,11 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G67" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68">
@@ -1926,12 +1855,11 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>65</v>
+      </c>
       <c r="G68" t="n">
-        <v>65</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
@@ -1948,12 +1876,11 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G69" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
@@ -1970,12 +1897,11 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="n">
+        <v>85</v>
+      </c>
       <c r="G70" t="n">
-        <v>85</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71">
@@ -1992,12 +1918,11 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="n">
+        <v>125</v>
+      </c>
       <c r="G71" t="n">
-        <v>125</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72">
@@ -2014,11 +1939,10 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G72" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2036,12 +1960,11 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G73" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74">
@@ -2058,12 +1981,11 @@
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G74" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75">
@@ -2080,12 +2002,11 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G75" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76">
@@ -2102,12 +2023,11 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G76" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77">
@@ -2124,12 +2044,11 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>65</v>
+      </c>
       <c r="G77" t="n">
-        <v>65</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -2146,12 +2065,11 @@
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G78" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79">
@@ -2168,12 +2086,11 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G79" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="80">
@@ -2190,12 +2107,11 @@
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>225</v>
+      </c>
       <c r="G80" t="n">
-        <v>225</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -2212,12 +2128,11 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G81" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82">
@@ -2234,12 +2149,11 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G82" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83">
@@ -2256,12 +2170,11 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G83" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84">
@@ -2278,12 +2191,11 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="F84" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G84" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85">
@@ -2300,12 +2212,11 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G85" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86">
@@ -2322,12 +2233,11 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" t="n">
+        <v>125</v>
+      </c>
       <c r="G86" t="n">
-        <v>125</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87">
@@ -2344,12 +2254,11 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G87" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88">
@@ -2366,12 +2275,11 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G88" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
@@ -2388,12 +2296,11 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>60</v>
+      </c>
       <c r="G89" t="n">
-        <v>60</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="90">
@@ -2410,12 +2317,11 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G90" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="91">
@@ -2432,12 +2338,11 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G91" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92">
@@ -2454,11 +2359,10 @@
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>160</v>
+      </c>
       <c r="G92" t="n">
-        <v>160</v>
-      </c>
-      <c r="H92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2476,12 +2380,11 @@
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>65</v>
+      </c>
       <c r="G93" t="n">
-        <v>65</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -2498,11 +2401,10 @@
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G94" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2520,11 +2422,10 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G95" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2542,11 +2443,10 @@
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
+      <c r="F96" t="n">
+        <v>3</v>
+      </c>
       <c r="G96" t="n">
-        <v>3</v>
-      </c>
-      <c r="H96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2564,11 +2464,10 @@
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G97" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2586,11 +2485,10 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="F98" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G98" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2608,11 +2506,10 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+      <c r="F99" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G99" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2630,12 +2527,11 @@
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+      <c r="F100" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G100" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101">
@@ -2652,11 +2548,10 @@
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
+      <c r="F101" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G101" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2674,11 +2569,10 @@
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G102" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H102" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2696,11 +2590,10 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G103" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2718,11 +2611,10 @@
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+      <c r="F104" t="n">
+        <v>2</v>
+      </c>
       <c r="G104" t="n">
-        <v>2</v>
-      </c>
-      <c r="H104" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2740,11 +2632,10 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+      <c r="F105" t="n">
+        <v>5</v>
+      </c>
       <c r="G105" t="n">
-        <v>5</v>
-      </c>
-      <c r="H105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2762,11 +2653,10 @@
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+      <c r="F106" t="n">
+        <v>5</v>
+      </c>
       <c r="G106" t="n">
-        <v>5</v>
-      </c>
-      <c r="H106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2784,11 +2674,10 @@
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="n">
+        <v>3.5</v>
+      </c>
       <c r="G107" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2806,11 +2695,10 @@
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="F108" t="n">
+        <v>3</v>
+      </c>
       <c r="G108" t="n">
-        <v>3</v>
-      </c>
-      <c r="H108" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2828,11 +2716,10 @@
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
       <c r="G109" t="n">
-        <v>1</v>
-      </c>
-      <c r="H109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2850,11 +2737,10 @@
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
       <c r="G110" t="n">
-        <v>1</v>
-      </c>
-      <c r="H110" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2872,11 +2758,10 @@
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+      <c r="F111" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G111" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H111" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2894,11 +2779,10 @@
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+      <c r="F112" t="n">
+        <v>5</v>
+      </c>
       <c r="G112" t="n">
-        <v>5</v>
-      </c>
-      <c r="H112" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2916,11 +2800,10 @@
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+      <c r="F113" t="n">
+        <v>5</v>
+      </c>
       <c r="G113" t="n">
-        <v>5</v>
-      </c>
-      <c r="H113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2938,11 +2821,10 @@
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+      <c r="F114" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G114" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2960,11 +2842,10 @@
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+      <c r="F115" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G115" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2982,11 +2863,10 @@
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
       <c r="G116" t="n">
-        <v>1</v>
-      </c>
-      <c r="H116" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3004,11 +2884,10 @@
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" t="n">
+        <v>114</v>
+      </c>
       <c r="G117" t="n">
-        <v>114</v>
-      </c>
-      <c r="H117" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3026,11 +2905,10 @@
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
+      <c r="F118" t="n">
+        <v>3.6</v>
+      </c>
       <c r="G118" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H118" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3048,11 +2926,10 @@
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+      <c r="F119" t="n">
+        <v>120</v>
+      </c>
       <c r="G119" t="n">
-        <v>120</v>
-      </c>
-      <c r="H119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3070,12 +2947,11 @@
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
+      <c r="F120" t="n">
+        <v>385</v>
+      </c>
       <c r="G120" t="n">
-        <v>385</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -3092,11 +2968,10 @@
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+      <c r="F121" t="n">
+        <v>135</v>
+      </c>
       <c r="G121" t="n">
-        <v>135</v>
-      </c>
-      <c r="H121" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3114,11 +2989,10 @@
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="F122" t="n">
+        <v>3.3</v>
+      </c>
       <c r="G122" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3136,11 +3010,10 @@
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+      <c r="F123" t="n">
+        <v>36</v>
+      </c>
       <c r="G123" t="n">
-        <v>36</v>
-      </c>
-      <c r="H123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3158,11 +3031,10 @@
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
+      <c r="F124" t="n">
+        <v>125</v>
+      </c>
       <c r="G124" t="n">
-        <v>125</v>
-      </c>
-      <c r="H124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3180,12 +3052,11 @@
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
+      <c r="F125" t="n">
+        <v>80</v>
+      </c>
       <c r="G125" t="n">
-        <v>80</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -3202,12 +3073,11 @@
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
+      <c r="F126" t="n">
+        <v>55</v>
+      </c>
       <c r="G126" t="n">
-        <v>55</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
@@ -3224,12 +3094,11 @@
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+      <c r="F127" t="n">
+        <v>55</v>
+      </c>
       <c r="G127" t="n">
-        <v>55</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -3246,11 +3115,10 @@
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
       <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3268,11 +3136,10 @@
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
       <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3290,11 +3157,10 @@
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
       <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3312,12 +3178,11 @@
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
+      <c r="F131" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G131" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="132">
@@ -3334,12 +3199,11 @@
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+      <c r="F132" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G132" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="133">
@@ -3356,11 +3220,10 @@
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+      <c r="F133" t="n">
+        <v>695</v>
+      </c>
       <c r="G133" t="n">
-        <v>695</v>
-      </c>
-      <c r="H133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3378,11 +3241,10 @@
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+      <c r="F134" t="n">
+        <v>650</v>
+      </c>
       <c r="G134" t="n">
-        <v>650</v>
-      </c>
-      <c r="H134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3400,12 +3262,11 @@
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+      <c r="F135" t="n">
+        <v>140</v>
+      </c>
       <c r="G135" t="n">
-        <v>140</v>
-      </c>
-      <c r="H135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -3422,12 +3283,11 @@
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
+      <c r="F136" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G136" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H136" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="137">
@@ -3444,12 +3304,11 @@
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
+      <c r="F137" t="n">
+        <v>18</v>
+      </c>
       <c r="G137" t="n">
-        <v>18</v>
-      </c>
-      <c r="H137" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138">
@@ -3466,12 +3325,11 @@
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
+      <c r="F138" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G138" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139">
@@ -3488,12 +3346,11 @@
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
+      <c r="F139" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G139" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="140">
@@ -3510,11 +3367,10 @@
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" t="n">
+        <v>4.2</v>
+      </c>
       <c r="G140" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3532,12 +3388,11 @@
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
+      <c r="F141" t="n">
+        <v>170</v>
+      </c>
       <c r="G141" t="n">
-        <v>170</v>
-      </c>
-      <c r="H141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
@@ -3554,12 +3409,11 @@
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+      <c r="F142" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G142" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H142" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143">
@@ -3576,12 +3430,11 @@
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
+      <c r="F143" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G143" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H143" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="144">
@@ -3598,12 +3451,11 @@
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
+      <c r="F144" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G144" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="145">
@@ -3620,12 +3472,11 @@
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
+      <c r="F145" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G145" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H145" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="146">
@@ -3642,12 +3493,11 @@
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" t="n">
+        <v>18</v>
+      </c>
       <c r="G146" t="n">
-        <v>18</v>
-      </c>
-      <c r="H146" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="147">
@@ -3664,12 +3514,11 @@
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
+      <c r="F147" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G147" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H147" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="148">
@@ -3686,12 +3535,11 @@
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
+      <c r="F148" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G148" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H148" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149">
@@ -3708,12 +3556,11 @@
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
+      <c r="F149" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G149" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H149" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="150">
@@ -3730,12 +3577,11 @@
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
+      <c r="F150" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G150" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H150" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="151">
@@ -3752,12 +3598,11 @@
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
+      <c r="F151" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G151" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H151" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="152">
@@ -3774,12 +3619,11 @@
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G152" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H152" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="153">
@@ -3796,12 +3640,11 @@
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
+      <c r="F153" t="n">
+        <v>45</v>
+      </c>
       <c r="G153" t="n">
-        <v>45</v>
-      </c>
-      <c r="H153" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154">
@@ -3818,12 +3661,11 @@
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
+      <c r="F154" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G154" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H154" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="155">
@@ -3840,12 +3682,11 @@
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
+      <c r="F155" t="n">
+        <v>70</v>
+      </c>
       <c r="G155" t="n">
-        <v>70</v>
-      </c>
-      <c r="H155" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="156">
@@ -3862,12 +3703,11 @@
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
+      <c r="F156" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G156" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="157">
@@ -3884,12 +3724,11 @@
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
+      <c r="F157" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G157" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H157" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158">
@@ -3906,12 +3745,11 @@
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
+      <c r="F158" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G158" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H158" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="159">
@@ -3928,11 +3766,10 @@
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
+      <c r="F159" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G159" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H159" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3950,12 +3787,11 @@
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
+      <c r="F160" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G160" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H160" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="161">
@@ -3972,12 +3808,11 @@
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
+      <c r="F161" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G161" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H161" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162">
@@ -3994,12 +3829,11 @@
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
+      <c r="F162" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G162" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4016,12 +3850,11 @@
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
+      <c r="F163" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G163" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H163" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="164">
@@ -4038,12 +3871,11 @@
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
+      <c r="F164" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G164" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H164" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="165">
@@ -4060,12 +3892,11 @@
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
+      <c r="F165" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G165" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H165" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="166">
@@ -4082,11 +3913,10 @@
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
+      <c r="F166" t="n">
+        <v>45</v>
+      </c>
       <c r="G166" t="n">
-        <v>45</v>
-      </c>
-      <c r="H166" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4104,12 +3934,11 @@
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
+      <c r="F167" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G167" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H167" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168">
@@ -4126,12 +3955,11 @@
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G168" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H168" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="169">
@@ -4148,12 +3976,11 @@
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
+      <c r="F169" t="n">
+        <v>24</v>
+      </c>
       <c r="G169" t="n">
-        <v>24</v>
-      </c>
-      <c r="H169" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="170">
@@ -4170,11 +3997,10 @@
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
+      <c r="F170" t="n">
+        <v>24</v>
+      </c>
       <c r="G170" t="n">
-        <v>24</v>
-      </c>
-      <c r="H170" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4192,12 +4018,11 @@
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+      <c r="F171" t="n">
+        <v>24</v>
+      </c>
       <c r="G171" t="n">
-        <v>24</v>
-      </c>
-      <c r="H171" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="172">
@@ -4214,12 +4039,11 @@
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+      <c r="F172" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G172" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H172" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="173">
@@ -4236,11 +4060,10 @@
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
+      <c r="F173" t="n">
+        <v>16.5</v>
+      </c>
       <c r="G173" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H173" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4258,12 +4081,11 @@
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G174" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H174" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="175">
@@ -4280,12 +4102,11 @@
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="n">
+        <v>24</v>
+      </c>
       <c r="G175" t="n">
-        <v>24</v>
-      </c>
-      <c r="H175" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="176">
@@ -4302,12 +4123,11 @@
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G176" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H176" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="177">
@@ -4324,12 +4144,11 @@
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+      <c r="F177" t="n">
+        <v>60</v>
+      </c>
       <c r="G177" t="n">
-        <v>60</v>
-      </c>
-      <c r="H177" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178">
@@ -4346,12 +4165,11 @@
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
+      <c r="F178" t="n">
+        <v>42</v>
+      </c>
       <c r="G178" t="n">
-        <v>42</v>
-      </c>
-      <c r="H178" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="179">
@@ -4368,12 +4186,11 @@
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+      <c r="F179" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G179" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H179" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="180">
@@ -4390,11 +4207,10 @@
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+      <c r="F180" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G180" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H180" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4412,12 +4228,11 @@
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
+      <c r="F181" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G181" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H181" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="182">
@@ -4434,12 +4249,11 @@
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G182" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H182" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183">
@@ -4456,12 +4270,11 @@
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
+      <c r="F183" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G183" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H183" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="184">
@@ -4478,12 +4291,11 @@
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
+      <c r="F184" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G184" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H184" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="185">
@@ -4500,12 +4312,11 @@
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
+      <c r="F185" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G185" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H185" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="186">
@@ -4522,12 +4333,11 @@
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
+      <c r="F186" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G186" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H186" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="187">
@@ -4544,12 +4354,11 @@
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+      <c r="F187" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G187" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H187" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="188">
@@ -4566,12 +4375,11 @@
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
+      <c r="F188" t="n">
+        <v>18</v>
+      </c>
       <c r="G188" t="n">
-        <v>18</v>
-      </c>
-      <c r="H188" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="189">
@@ -4588,12 +4396,11 @@
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+      <c r="F189" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G189" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H189" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="190">
@@ -4610,11 +4417,10 @@
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
+      <c r="F190" t="n">
+        <v>495</v>
+      </c>
       <c r="G190" t="n">
-        <v>495</v>
-      </c>
-      <c r="H190" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4632,12 +4438,11 @@
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
+      <c r="F191" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G191" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H191" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="192">
@@ -4654,11 +4459,10 @@
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
+      <c r="F192" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G192" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H192" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4676,11 +4480,10 @@
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
+      <c r="F193" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G193" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H193" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4698,12 +4501,11 @@
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
+      <c r="F194" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G194" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H194" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="195">
@@ -4720,12 +4522,11 @@
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
+      <c r="F195" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G195" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H195" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196">
@@ -4742,12 +4543,11 @@
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
+      <c r="F196" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G196" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H196" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="197">
@@ -4764,12 +4564,11 @@
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
+      <c r="F197" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G197" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H197" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198">
@@ -4786,12 +4585,11 @@
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
+      <c r="F198" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G198" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -4808,12 +4606,11 @@
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
+      <c r="F199" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G199" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H199" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200">
@@ -4830,12 +4627,11 @@
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
+      <c r="F200" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G200" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H200" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="201">
@@ -4852,12 +4648,11 @@
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
+      <c r="F201" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G201" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -4874,11 +4669,10 @@
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
+      <c r="F202" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G202" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H202" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4896,12 +4690,11 @@
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
+      <c r="F203" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G203" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H203" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="204">
@@ -4918,12 +4711,11 @@
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
+      <c r="F204" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G204" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -4940,12 +4732,11 @@
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
+      <c r="F205" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G205" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H205" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="206">
@@ -4962,12 +4753,11 @@
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
+      <c r="F206" t="n">
+        <v>24</v>
+      </c>
       <c r="G206" t="n">
-        <v>24</v>
-      </c>
-      <c r="H206" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="207">
@@ -4984,12 +4774,11 @@
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
+      <c r="F207" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G207" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -5006,12 +4795,11 @@
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
+      <c r="F208" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G208" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -5028,11 +4816,10 @@
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
+      <c r="F209" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G209" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H209" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5050,12 +4837,11 @@
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
+      <c r="F210" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G210" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H210" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="211">
@@ -5072,12 +4858,11 @@
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
+      <c r="F211" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G211" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H211" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212">
@@ -5094,12 +4879,11 @@
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
+      <c r="F212" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G212" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H212" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213">
@@ -5116,12 +4900,11 @@
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
+      <c r="F213" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G213" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214">
@@ -5138,12 +4921,11 @@
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
+      <c r="F214" t="n">
+        <v>65</v>
+      </c>
       <c r="G214" t="n">
-        <v>65</v>
-      </c>
-      <c r="H214" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215">
@@ -5160,12 +4942,11 @@
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
+      <c r="F215" t="n">
+        <v>65</v>
+      </c>
       <c r="G215" t="n">
-        <v>65</v>
-      </c>
-      <c r="H215" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216">
@@ -5182,12 +4963,11 @@
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
+      <c r="F216" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G216" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H216" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217">
@@ -5204,12 +4984,11 @@
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
+      <c r="F217" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G217" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H217" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="218">
@@ -5226,12 +5005,11 @@
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
+      <c r="F218" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G218" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H218" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219">
@@ -5248,12 +5026,11 @@
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+      <c r="F219" t="n">
+        <v>24</v>
+      </c>
       <c r="G219" t="n">
-        <v>24</v>
-      </c>
-      <c r="H219" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220">
@@ -5270,12 +5047,11 @@
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+      <c r="F220" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G220" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H220" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="221">
@@ -5292,12 +5068,11 @@
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
+      <c r="F221" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G221" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H221" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222">
@@ -5314,11 +5089,10 @@
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
+      <c r="F222" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G222" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H222" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5336,12 +5110,11 @@
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
+      <c r="F223" t="n">
+        <v>60</v>
+      </c>
       <c r="G223" t="n">
-        <v>60</v>
-      </c>
-      <c r="H223" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="224">
@@ -5358,12 +5131,11 @@
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
+      <c r="F224" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G224" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H224" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225">
@@ -5380,12 +5152,11 @@
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
+      <c r="F225" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G225" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H225" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226">
@@ -5402,12 +5173,11 @@
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
+      <c r="F226" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G226" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H226" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="227">
@@ -5424,12 +5194,11 @@
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
+      <c r="F227" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G227" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H227" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="228">
@@ -5446,12 +5215,11 @@
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
+      <c r="F228" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G228" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H228" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="229">
@@ -5468,12 +5236,11 @@
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
+      <c r="F229" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G229" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H229" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="230">
@@ -5490,12 +5257,11 @@
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
+      <c r="F230" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G230" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H230" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="231">
@@ -5512,12 +5278,11 @@
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
+      <c r="F231" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G231" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H231" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="232">
@@ -5534,12 +5299,11 @@
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
+      <c r="F232" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G232" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H232" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="233">
@@ -5556,12 +5320,11 @@
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
+      <c r="F233" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G233" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H233" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="234">
@@ -5578,12 +5341,11 @@
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
+      <c r="F234" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G234" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H234" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235">
@@ -5600,12 +5362,11 @@
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
+      <c r="F235" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G235" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H235" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="236">
@@ -5622,12 +5383,11 @@
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
+      <c r="F236" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G236" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
@@ -5644,12 +5404,11 @@
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
+      <c r="F237" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G237" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H237" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
     </row>
     <row r="238">
@@ -5666,12 +5425,11 @@
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
+      <c r="F238" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G238" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H238" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="239">
@@ -5688,12 +5446,11 @@
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
+      <c r="F239" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G239" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
@@ -5710,12 +5467,11 @@
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
+      <c r="F240" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G240" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H240" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="241">
@@ -5732,12 +5488,11 @@
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr"/>
+      <c r="F241" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G241" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H241" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="242">
@@ -5754,12 +5509,11 @@
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
+      <c r="F242" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G242" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H242" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="243">
@@ -5776,11 +5530,10 @@
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
+      <c r="F243" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G243" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H243" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5798,12 +5551,11 @@
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
+      <c r="F244" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G244" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H244" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="245">
@@ -5820,12 +5572,11 @@
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
+      <c r="F245" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G245" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H245" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="246">
@@ -5842,12 +5593,11 @@
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
+      <c r="F246" t="n">
+        <v>24</v>
+      </c>
       <c r="G246" t="n">
-        <v>24</v>
-      </c>
-      <c r="H246" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="247">
@@ -5864,12 +5614,11 @@
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
+      <c r="F247" t="n">
+        <v>24</v>
+      </c>
       <c r="G247" t="n">
-        <v>24</v>
-      </c>
-      <c r="H247" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="248">
@@ -5886,12 +5635,11 @@
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
+      <c r="F248" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G248" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H248" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="249">
@@ -5908,12 +5656,11 @@
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
+      <c r="F249" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G249" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H249" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="250">
@@ -5930,12 +5677,11 @@
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
+      <c r="F250" t="n">
+        <v>24</v>
+      </c>
       <c r="G250" t="n">
-        <v>24</v>
-      </c>
-      <c r="H250" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="251">
@@ -5952,12 +5698,11 @@
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
+      <c r="F251" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G251" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H251" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="252">
@@ -5974,12 +5719,11 @@
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
+      <c r="F252" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G252" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H252" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="253">
@@ -5996,12 +5740,11 @@
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
+      <c r="F253" t="n">
+        <v>24</v>
+      </c>
       <c r="G253" t="n">
-        <v>24</v>
-      </c>
-      <c r="H253" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6018,12 +5761,11 @@
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
+      <c r="F254" t="n">
+        <v>24</v>
+      </c>
       <c r="G254" t="n">
-        <v>24</v>
-      </c>
-      <c r="H254" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="255">
@@ -6040,12 +5782,11 @@
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
+      <c r="F255" t="n">
+        <v>24</v>
+      </c>
       <c r="G255" t="n">
-        <v>24</v>
-      </c>
-      <c r="H255" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="256">
@@ -6062,12 +5803,11 @@
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
+      <c r="F256" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G256" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H256" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="257">
@@ -6084,11 +5824,10 @@
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
+      <c r="F257" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G257" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H257" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6106,12 +5845,11 @@
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
+      <c r="F258" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G258" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H258" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="259">
@@ -6128,12 +5866,11 @@
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
+      <c r="F259" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G259" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -6150,12 +5887,11 @@
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
+      <c r="F260" t="n">
+        <v>24</v>
+      </c>
       <c r="G260" t="n">
-        <v>24</v>
-      </c>
-      <c r="H260" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="261">
@@ -6172,12 +5908,11 @@
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
+      <c r="F261" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G261" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H261" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="262">
@@ -6194,12 +5929,11 @@
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
+      <c r="F262" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G262" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H262" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="263">
@@ -6216,11 +5950,10 @@
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
+      <c r="F263" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G263" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H263" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6238,12 +5971,11 @@
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
+      <c r="F264" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G264" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H264" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="265">
@@ -6260,12 +5992,11 @@
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
+      <c r="F265" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G265" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H265" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="266">
@@ -6282,12 +6013,11 @@
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
+      <c r="F266" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G266" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H266" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="267">
@@ -6304,12 +6034,11 @@
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr"/>
+      <c r="F267" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G267" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H267" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="268">
@@ -6326,12 +6055,11 @@
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
+      <c r="F268" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G268" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H268" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269">
@@ -6348,11 +6076,10 @@
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr"/>
-      <c r="F269" t="inlineStr"/>
+      <c r="F269" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G269" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H269" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6370,12 +6097,11 @@
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
+      <c r="F270" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G270" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -6392,11 +6118,10 @@
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
+      <c r="F271" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G271" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H271" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6414,11 +6139,10 @@
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
+      <c r="F272" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G272" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H272" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6436,12 +6160,11 @@
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
+      <c r="F273" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G273" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H273" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="274">
@@ -6458,11 +6181,10 @@
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
+      <c r="F274" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G274" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H274" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6480,12 +6202,11 @@
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
+      <c r="F275" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G275" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H275" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="276">
@@ -6502,11 +6223,10 @@
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
       <c r="G276" t="n">
-        <v>0</v>
-      </c>
-      <c r="H276" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6524,12 +6244,11 @@
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
+      <c r="F277" t="n">
+        <v>185</v>
+      </c>
       <c r="G277" t="n">
-        <v>185</v>
-      </c>
-      <c r="H277" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278">
@@ -6546,12 +6265,11 @@
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
+      <c r="F278" t="n">
+        <v>115</v>
+      </c>
       <c r="G278" t="n">
-        <v>115</v>
-      </c>
-      <c r="H278" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="279">
@@ -6568,11 +6286,10 @@
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
+      <c r="F279" t="n">
+        <v>325</v>
+      </c>
       <c r="G279" t="n">
-        <v>325</v>
-      </c>
-      <c r="H279" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6590,11 +6307,10 @@
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
+      <c r="F280" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G280" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H280" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6612,11 +6328,10 @@
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
+      <c r="F281" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G281" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H281" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6634,12 +6349,11 @@
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr"/>
+      <c r="F282" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G282" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H282" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="283">
@@ -6656,12 +6370,11 @@
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr"/>
+      <c r="F283" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G283" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H283" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="284">
@@ -6678,12 +6391,11 @@
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
+      <c r="F284" t="n">
+        <v>12</v>
+      </c>
       <c r="G284" t="n">
-        <v>12</v>
-      </c>
-      <c r="H284" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
     </row>
     <row r="285">
@@ -6700,11 +6412,10 @@
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
+      <c r="F285" t="n">
+        <v>0.6</v>
+      </c>
       <c r="G285" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H285" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6722,11 +6433,10 @@
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
+      <c r="F286" t="n">
+        <v>4.85</v>
+      </c>
       <c r="G286" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="H286" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6744,11 +6454,10 @@
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
+      <c r="F287" t="n">
+        <v>125</v>
+      </c>
       <c r="G287" t="n">
-        <v>125</v>
-      </c>
-      <c r="H287" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6766,12 +6475,11 @@
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
+      <c r="F288" t="n">
+        <v>24</v>
+      </c>
       <c r="G288" t="n">
-        <v>24</v>
-      </c>
-      <c r="H288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289">
@@ -6788,12 +6496,11 @@
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr"/>
-      <c r="F289" t="inlineStr"/>
+      <c r="F289" t="n">
+        <v>65</v>
+      </c>
       <c r="G289" t="n">
-        <v>65</v>
-      </c>
-      <c r="H289" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="290">
@@ -6810,12 +6517,11 @@
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
+      <c r="F290" t="n">
+        <v>45</v>
+      </c>
       <c r="G290" t="n">
-        <v>45</v>
-      </c>
-      <c r="H290" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="291">
@@ -6832,12 +6538,11 @@
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
-      <c r="F291" t="inlineStr"/>
+      <c r="F291" t="n">
+        <v>70</v>
+      </c>
       <c r="G291" t="n">
-        <v>70</v>
-      </c>
-      <c r="H291" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="292">
@@ -6854,12 +6559,11 @@
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
-      <c r="F292" t="inlineStr"/>
+      <c r="F292" t="n">
+        <v>70</v>
+      </c>
       <c r="G292" t="n">
-        <v>70</v>
-      </c>
-      <c r="H292" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
@@ -6876,12 +6580,11 @@
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr"/>
-      <c r="F293" t="inlineStr"/>
+      <c r="F293" t="n">
+        <v>70</v>
+      </c>
       <c r="G293" t="n">
-        <v>70</v>
-      </c>
-      <c r="H293" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="294">
@@ -6898,12 +6601,11 @@
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
-      <c r="F294" t="inlineStr"/>
+      <c r="F294" t="n">
+        <v>165</v>
+      </c>
       <c r="G294" t="n">
-        <v>165</v>
-      </c>
-      <c r="H294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -6920,12 +6622,11 @@
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr"/>
-      <c r="F295" t="inlineStr"/>
+      <c r="F295" t="n">
+        <v>90</v>
+      </c>
       <c r="G295" t="n">
-        <v>90</v>
-      </c>
-      <c r="H295" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="296">
@@ -6942,12 +6643,11 @@
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr"/>
+      <c r="F296" t="n">
+        <v>85</v>
+      </c>
       <c r="G296" t="n">
-        <v>85</v>
-      </c>
-      <c r="H296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
@@ -6964,11 +6664,10 @@
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
-      <c r="F297" t="inlineStr"/>
+      <c r="F297" t="n">
+        <v>70</v>
+      </c>
       <c r="G297" t="n">
-        <v>70</v>
-      </c>
-      <c r="H297" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6986,11 +6685,10 @@
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr"/>
+      <c r="F298" t="n">
+        <v>95</v>
+      </c>
       <c r="G298" t="n">
-        <v>95</v>
-      </c>
-      <c r="H298" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7008,12 +6706,11 @@
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr"/>
+      <c r="F299" t="n">
+        <v>75</v>
+      </c>
       <c r="G299" t="n">
-        <v>75</v>
-      </c>
-      <c r="H299" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7030,12 +6727,11 @@
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
+      <c r="F300" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G300" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H300" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="301">
@@ -7052,11 +6748,10 @@
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
-      <c r="F301" t="inlineStr"/>
+      <c r="F301" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G301" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H301" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7074,12 +6769,11 @@
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
-      <c r="F302" t="inlineStr"/>
+      <c r="F302" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G302" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H302" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="303">
@@ -7096,12 +6790,11 @@
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr"/>
+      <c r="F303" t="n">
+        <v>110</v>
+      </c>
       <c r="G303" t="n">
-        <v>110</v>
-      </c>
-      <c r="H303" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="304">
@@ -7118,11 +6811,10 @@
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
+      <c r="F304" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G304" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H304" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7140,11 +6832,10 @@
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
-      <c r="F305" t="inlineStr"/>
+      <c r="F305" t="n">
+        <v>145</v>
+      </c>
       <c r="G305" t="n">
-        <v>145</v>
-      </c>
-      <c r="H305" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7162,12 +6853,11 @@
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr"/>
+      <c r="F306" t="n">
+        <v>165</v>
+      </c>
       <c r="G306" t="n">
-        <v>165</v>
-      </c>
-      <c r="H306" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="307">
@@ -7184,12 +6874,11 @@
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr"/>
-      <c r="F307" t="inlineStr"/>
+      <c r="F307" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G307" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H307" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="308">
@@ -7206,12 +6895,11 @@
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
+      <c r="F308" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G308" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H308" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="309">
@@ -7228,12 +6916,11 @@
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr"/>
-      <c r="F309" t="inlineStr"/>
+      <c r="F309" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G309" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H309" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="310">
@@ -7250,12 +6937,11 @@
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr"/>
-      <c r="F310" t="inlineStr"/>
+      <c r="F310" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G310" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H310" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="311">
@@ -7272,12 +6958,11 @@
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr"/>
-      <c r="F311" t="inlineStr"/>
+      <c r="F311" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G311" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H311" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="312">
@@ -7294,11 +6979,10 @@
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr"/>
-      <c r="F312" t="inlineStr"/>
+      <c r="F312" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G312" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H312" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7316,12 +7000,11 @@
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr"/>
-      <c r="F313" t="inlineStr"/>
+      <c r="F313" t="n">
+        <v>24</v>
+      </c>
       <c r="G313" t="n">
-        <v>24</v>
-      </c>
-      <c r="H313" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
     </row>
     <row r="314">
@@ -7338,12 +7021,11 @@
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr"/>
-      <c r="F314" t="inlineStr"/>
+      <c r="F314" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G314" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H314" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="315">
@@ -7360,11 +7042,10 @@
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr"/>
-      <c r="F315" t="inlineStr"/>
+      <c r="F315" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G315" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H315" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7382,12 +7063,11 @@
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr"/>
+      <c r="F316" t="n">
+        <v>70</v>
+      </c>
       <c r="G316" t="n">
-        <v>70</v>
-      </c>
-      <c r="H316" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="317">
@@ -7404,11 +7084,10 @@
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr"/>
-      <c r="F317" t="inlineStr"/>
+      <c r="F317" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G317" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H317" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7426,11 +7105,10 @@
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr"/>
-      <c r="F318" t="inlineStr"/>
+      <c r="F318" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G318" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H318" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7448,11 +7126,10 @@
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr"/>
-      <c r="F319" t="inlineStr"/>
+      <c r="F319" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G319" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H319" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7470,11 +7147,10 @@
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr"/>
+      <c r="F320" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G320" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H320" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7492,11 +7168,10 @@
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr"/>
-      <c r="F321" t="inlineStr"/>
+      <c r="F321" t="n">
+        <v>1.25</v>
+      </c>
       <c r="G321" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H321" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7514,11 +7189,10 @@
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr"/>
-      <c r="F322" t="inlineStr"/>
+      <c r="F322" t="n">
+        <v>6</v>
+      </c>
       <c r="G322" t="n">
-        <v>6</v>
-      </c>
-      <c r="H322" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7536,11 +7210,10 @@
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr"/>
-      <c r="F323" t="inlineStr"/>
+      <c r="F323" t="n">
+        <v>6</v>
+      </c>
       <c r="G323" t="n">
-        <v>6</v>
-      </c>
-      <c r="H323" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7558,11 +7231,10 @@
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
+      <c r="F324" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G324" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H324" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7580,11 +7252,10 @@
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr"/>
-      <c r="F325" t="inlineStr"/>
+      <c r="F325" t="n">
+        <v>3.5</v>
+      </c>
       <c r="G325" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H325" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7602,11 +7273,10 @@
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr"/>
-      <c r="F326" t="inlineStr"/>
+      <c r="F326" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G326" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H326" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7624,11 +7294,10 @@
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr"/>
+      <c r="F327" t="n">
+        <v>135</v>
+      </c>
       <c r="G327" t="n">
-        <v>135</v>
-      </c>
-      <c r="H327" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7646,11 +7315,10 @@
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
+      <c r="F328" t="n">
+        <v>1</v>
+      </c>
       <c r="G328" t="n">
-        <v>1</v>
-      </c>
-      <c r="H328" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7668,11 +7336,10 @@
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr"/>
-      <c r="F329" t="inlineStr"/>
+      <c r="F329" t="n">
+        <v>7.5</v>
+      </c>
       <c r="G329" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H329" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7690,12 +7357,11 @@
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
+      <c r="F330" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G330" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -7712,12 +7378,11 @@
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr"/>
-      <c r="F331" t="inlineStr"/>
+      <c r="F331" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G331" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H331" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="332">
@@ -7734,12 +7399,11 @@
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
+      <c r="F332" t="n">
+        <v>625</v>
+      </c>
       <c r="G332" t="n">
-        <v>625</v>
-      </c>
-      <c r="H332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -7756,12 +7420,11 @@
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr"/>
+      <c r="F333" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G333" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H333" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="334">
@@ -7778,12 +7441,11 @@
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr"/>
+      <c r="F334" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G334" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H334" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="335">
@@ -7800,12 +7462,11 @@
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr"/>
+      <c r="F335" t="n">
+        <v>65</v>
+      </c>
       <c r="G335" t="n">
-        <v>65</v>
-      </c>
-      <c r="H335" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="336">
@@ -7822,12 +7483,11 @@
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr"/>
+      <c r="F336" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G336" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H336" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="337">
@@ -7844,12 +7504,11 @@
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr"/>
-      <c r="F337" t="inlineStr"/>
+      <c r="F337" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G337" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H337" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="338">
@@ -7866,12 +7525,11 @@
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr"/>
+      <c r="F338" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G338" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H338" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="339">
@@ -7888,12 +7546,11 @@
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr"/>
+      <c r="F339" t="n">
+        <v>45</v>
+      </c>
       <c r="G339" t="n">
-        <v>45</v>
-      </c>
-      <c r="H339" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="340">
@@ -7910,12 +7567,11 @@
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
+      <c r="F340" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G340" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H340" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="341">
@@ -7932,12 +7588,11 @@
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr"/>
+      <c r="F341" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G341" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -7954,12 +7609,11 @@
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr"/>
+      <c r="F342" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G342" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H342" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="343">
@@ -7976,12 +7630,11 @@
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr"/>
+      <c r="F343" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G343" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H343" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="344">
@@ -7998,12 +7651,11 @@
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
+      <c r="F344" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G344" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H344" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="345">
@@ -8020,11 +7672,10 @@
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr"/>
+      <c r="F345" t="n">
+        <v>45</v>
+      </c>
       <c r="G345" t="n">
-        <v>45</v>
-      </c>
-      <c r="H345" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8042,12 +7693,11 @@
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr"/>
+      <c r="F346" t="n">
+        <v>170</v>
+      </c>
       <c r="G346" t="n">
-        <v>170</v>
-      </c>
-      <c r="H346" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="347">
@@ -8058,21 +7708,16 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>After Plant</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>All Purpose</t>
-        </is>
-      </c>
+          <t>After Plant - All Purpose</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr"/>
+      <c r="F347" t="n">
+        <v>9.5</v>
+      </c>
       <c r="G347" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H347" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8090,12 +7735,11 @@
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
+      <c r="F348" t="n">
+        <v>9.5</v>
+      </c>
       <c r="G348" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H348" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="349">
@@ -8112,11 +7756,10 @@
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr"/>
+      <c r="F349" t="n">
+        <v>3</v>
+      </c>
       <c r="G349" t="n">
-        <v>3</v>
-      </c>
-      <c r="H349" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8134,11 +7777,10 @@
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
+      <c r="F350" t="n">
+        <v>55</v>
+      </c>
       <c r="G350" t="n">
-        <v>55</v>
-      </c>
-      <c r="H350" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8156,12 +7798,11 @@
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr"/>
+      <c r="F351" t="n">
+        <v>80</v>
+      </c>
       <c r="G351" t="n">
-        <v>80</v>
-      </c>
-      <c r="H351" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="352">
@@ -8178,12 +7819,11 @@
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
+      <c r="F352" t="n">
+        <v>45</v>
+      </c>
       <c r="G352" t="n">
-        <v>45</v>
-      </c>
-      <c r="H352" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="353">
@@ -8200,12 +7840,11 @@
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
+      <c r="F353" t="n">
+        <v>60</v>
+      </c>
       <c r="G353" t="n">
-        <v>60</v>
-      </c>
-      <c r="H353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="354">
@@ -8222,12 +7861,11 @@
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr"/>
+      <c r="F354" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G354" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H354" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="355">
@@ -8244,11 +7882,10 @@
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr"/>
-      <c r="F355" t="inlineStr"/>
+      <c r="F355" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G355" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H355" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8266,12 +7903,11 @@
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
+      <c r="F356" t="n">
+        <v>24</v>
+      </c>
       <c r="G356" t="n">
-        <v>24</v>
-      </c>
-      <c r="H356" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="357">
@@ -8288,11 +7924,10 @@
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
+      <c r="F357" t="n">
+        <v>0</v>
+      </c>
       <c r="G357" t="n">
-        <v>0</v>
-      </c>
-      <c r="H357" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8310,12 +7945,11 @@
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr"/>
+      <c r="F358" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G358" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H358" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="359">
@@ -8332,12 +7966,11 @@
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr"/>
+      <c r="F359" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G359" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H359" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="360">
@@ -8354,12 +7987,11 @@
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
+      <c r="F360" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G360" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H360" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="361">
@@ -8376,12 +8008,11 @@
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr"/>
-      <c r="F361" t="inlineStr"/>
+      <c r="F361" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G361" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H361" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="362">
@@ -8398,12 +8029,11 @@
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr"/>
-      <c r="F362" t="inlineStr"/>
+      <c r="F362" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G362" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H362" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="363">
@@ -8420,12 +8050,11 @@
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr"/>
-      <c r="F363" t="inlineStr"/>
+      <c r="F363" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G363" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H363" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="364">
@@ -8442,12 +8071,11 @@
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr"/>
+      <c r="F364" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G364" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H364" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="365">
@@ -8464,12 +8092,11 @@
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
-      <c r="F365" t="inlineStr"/>
+      <c r="F365" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G365" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H365" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="366">
@@ -8486,12 +8113,11 @@
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr"/>
+      <c r="F366" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G366" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H366" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -8508,11 +8134,10 @@
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr"/>
+      <c r="F367" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G367" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H367" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8530,12 +8155,11 @@
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
+      <c r="F368" t="n">
+        <v>85</v>
+      </c>
       <c r="G368" t="n">
-        <v>85</v>
-      </c>
-      <c r="H368" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="369">
@@ -8552,11 +8176,10 @@
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr"/>
+      <c r="F369" t="n">
+        <v>0</v>
+      </c>
       <c r="G369" t="n">
-        <v>0</v>
-      </c>
-      <c r="H369" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8574,12 +8197,11 @@
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr"/>
-      <c r="F370" t="inlineStr"/>
+      <c r="F370" t="n">
+        <v>18</v>
+      </c>
       <c r="G370" t="n">
-        <v>18</v>
-      </c>
-      <c r="H370" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="371">
@@ -8596,11 +8218,10 @@
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr"/>
-      <c r="F371" t="inlineStr"/>
+      <c r="F371" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G371" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H371" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8618,12 +8239,11 @@
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
+      <c r="F372" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G372" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H372" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="373">
@@ -8640,11 +8260,10 @@
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr"/>
+      <c r="F373" t="n">
+        <v>3</v>
+      </c>
       <c r="G373" t="n">
-        <v>3</v>
-      </c>
-      <c r="H373" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8662,12 +8281,11 @@
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr"/>
-      <c r="F374" t="inlineStr"/>
+      <c r="F374" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G374" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H374" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="375">
@@ -8684,12 +8302,11 @@
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr"/>
+      <c r="F375" t="n">
+        <v>24</v>
+      </c>
       <c r="G375" t="n">
-        <v>24</v>
-      </c>
-      <c r="H375" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="376">
@@ -8706,12 +8323,11 @@
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr"/>
-      <c r="F376" t="inlineStr"/>
+      <c r="F376" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G376" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H376" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="377">
@@ -8728,12 +8344,11 @@
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr"/>
-      <c r="F377" t="inlineStr"/>
+      <c r="F377" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G377" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H377" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="378">
@@ -8750,12 +8365,11 @@
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr"/>
-      <c r="F378" t="inlineStr"/>
+      <c r="F378" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G378" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H378" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="379">
@@ -8772,12 +8386,11 @@
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr"/>
-      <c r="F379" t="inlineStr"/>
+      <c r="F379" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G379" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H379" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="380">
@@ -8794,12 +8407,11 @@
       <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
+      <c r="F380" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G380" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H380" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="381">
@@ -8816,12 +8428,11 @@
       <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
-      <c r="F381" t="inlineStr"/>
+      <c r="F381" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G381" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H381" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="382">
@@ -8838,12 +8449,11 @@
       <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr"/>
+      <c r="F382" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G382" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H382" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="383">
@@ -8860,12 +8470,11 @@
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
-      <c r="F383" t="inlineStr"/>
+      <c r="F383" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G383" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H383" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="384">
@@ -8882,12 +8491,11 @@
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
-      <c r="F384" t="inlineStr"/>
+      <c r="F384" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G384" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H384" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="385">
@@ -8904,12 +8512,11 @@
       <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
-      <c r="F385" t="inlineStr"/>
+      <c r="F385" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G385" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H385" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="386">
@@ -8926,12 +8533,11 @@
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
-      <c r="F386" t="inlineStr"/>
+      <c r="F386" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G386" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H386" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="387">
@@ -8948,12 +8554,11 @@
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr"/>
+      <c r="F387" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G387" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H387" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="388">
@@ -8970,11 +8575,10 @@
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
+      <c r="F388" t="n">
+        <v>155</v>
+      </c>
       <c r="G388" t="n">
-        <v>155</v>
-      </c>
-      <c r="H388" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8992,12 +8596,11 @@
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
-      <c r="F389" t="inlineStr"/>
+      <c r="F389" t="n">
+        <v>165</v>
+      </c>
       <c r="G389" t="n">
-        <v>165</v>
-      </c>
-      <c r="H389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390">
@@ -9014,12 +8617,11 @@
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr"/>
+      <c r="F390" t="n">
+        <v>265</v>
+      </c>
       <c r="G390" t="n">
-        <v>265</v>
-      </c>
-      <c r="H390" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="391">
@@ -9036,12 +8638,11 @@
       <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr"/>
-      <c r="F391" t="inlineStr"/>
+      <c r="F391" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G391" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H391" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="392">
@@ -9058,12 +8659,11 @@
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr"/>
-      <c r="F392" t="inlineStr"/>
+      <c r="F392" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G392" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H392" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="393">
@@ -9080,12 +8680,11 @@
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr"/>
-      <c r="F393" t="inlineStr"/>
+      <c r="F393" t="n">
+        <v>55</v>
+      </c>
       <c r="G393" t="n">
-        <v>55</v>
-      </c>
-      <c r="H393" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="394">
@@ -9102,12 +8701,11 @@
       <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
+      <c r="F394" t="n">
+        <v>75</v>
+      </c>
       <c r="G394" t="n">
-        <v>75</v>
-      </c>
-      <c r="H394" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="395">
@@ -9124,11 +8722,10 @@
       <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr"/>
+      <c r="F395" t="n">
+        <v>2</v>
+      </c>
       <c r="G395" t="n">
-        <v>2</v>
-      </c>
-      <c r="H395" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9146,12 +8743,11 @@
       <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr"/>
+      <c r="F396" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G396" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H396" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="397">
@@ -9168,12 +8764,11 @@
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
+      <c r="F397" t="n">
+        <v>55</v>
+      </c>
       <c r="G397" t="n">
-        <v>55</v>
-      </c>
-      <c r="H397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398">
@@ -9190,11 +8785,10 @@
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
+      <c r="F398" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G398" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H398" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9212,12 +8806,11 @@
       <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
+      <c r="F399" t="n">
+        <v>75</v>
+      </c>
       <c r="G399" t="n">
-        <v>75</v>
-      </c>
-      <c r="H399" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="400">
@@ -9234,11 +8827,10 @@
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr"/>
-      <c r="F400" t="inlineStr"/>
+      <c r="F400" t="n">
+        <v>0.6</v>
+      </c>
       <c r="G400" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H400" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9256,11 +8848,10 @@
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr"/>
-      <c r="F401" t="inlineStr"/>
+      <c r="F401" t="n">
+        <v>1</v>
+      </c>
       <c r="G401" t="n">
-        <v>1</v>
-      </c>
-      <c r="H401" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9278,12 +8869,11 @@
       <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr"/>
-      <c r="F402" t="inlineStr"/>
+      <c r="F402" t="n">
+        <v>24</v>
+      </c>
       <c r="G402" t="n">
-        <v>24</v>
-      </c>
-      <c r="H402" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="403">
@@ -9300,12 +8890,11 @@
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
-      <c r="F403" t="inlineStr"/>
+      <c r="F403" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G403" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H403" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="404">
@@ -9322,11 +8911,10 @@
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr"/>
+      <c r="F404" t="n">
+        <v>1.2</v>
+      </c>
       <c r="G404" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H404" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9344,11 +8932,10 @@
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr"/>
-      <c r="F405" t="inlineStr"/>
+      <c r="F405" t="n">
+        <v>1.25</v>
+      </c>
       <c r="G405" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H405" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9366,11 +8953,10 @@
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr"/>
+      <c r="F406" t="n">
+        <v>425</v>
+      </c>
       <c r="G406" t="n">
-        <v>425</v>
-      </c>
-      <c r="H406" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9388,11 +8974,10 @@
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
-      <c r="F407" t="inlineStr"/>
+      <c r="F407" t="n">
+        <v>595</v>
+      </c>
       <c r="G407" t="n">
-        <v>595</v>
-      </c>
-      <c r="H407" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9410,12 +8995,11 @@
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr"/>
-      <c r="F408" t="inlineStr"/>
+      <c r="F408" t="n">
+        <v>130</v>
+      </c>
       <c r="G408" t="n">
-        <v>130</v>
-      </c>
-      <c r="H408" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -9432,11 +9016,10 @@
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
+      <c r="F409" t="n">
+        <v>3.5</v>
+      </c>
       <c r="G409" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H409" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9454,11 +9037,10 @@
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
+      <c r="F410" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G410" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H410" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9476,11 +9058,10 @@
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr"/>
+      <c r="F411" t="n">
+        <v>0.85</v>
+      </c>
       <c r="G411" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H411" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9498,11 +9079,10 @@
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="F412" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G412" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H412" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9520,12 +9100,11 @@
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="F413" t="n">
+        <v>18</v>
+      </c>
       <c r="G413" t="n">
-        <v>18</v>
-      </c>
-      <c r="H413" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="414">
@@ -9542,11 +9121,10 @@
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="F414" t="n">
+        <v>1</v>
+      </c>
       <c r="G414" t="n">
-        <v>1</v>
-      </c>
-      <c r="H414" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9564,11 +9142,10 @@
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="F415" t="n">
+        <v>1</v>
+      </c>
       <c r="G415" t="n">
-        <v>1</v>
-      </c>
-      <c r="H415" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9586,11 +9163,10 @@
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
+      <c r="F416" t="n">
+        <v>1</v>
+      </c>
       <c r="G416" t="n">
-        <v>1</v>
-      </c>
-      <c r="H416" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9608,11 +9184,10 @@
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
-      <c r="F417" t="inlineStr"/>
+      <c r="F417" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G417" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H417" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9630,12 +9205,11 @@
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
+      <c r="F418" t="n">
+        <v>55</v>
+      </c>
       <c r="G418" t="n">
-        <v>55</v>
-      </c>
-      <c r="H418" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="419">
@@ -9652,12 +9226,11 @@
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
+      <c r="F419" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G419" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H419" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="420">
@@ -9674,12 +9247,11 @@
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
+      <c r="F420" t="n">
+        <v>55</v>
+      </c>
       <c r="G420" t="n">
-        <v>55</v>
-      </c>
-      <c r="H420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -9696,12 +9268,11 @@
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
-      <c r="F421" t="inlineStr"/>
+      <c r="F421" t="n">
+        <v>48</v>
+      </c>
       <c r="G421" t="n">
-        <v>48</v>
-      </c>
-      <c r="H421" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="422">
@@ -9718,12 +9289,11 @@
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
-      <c r="F422" t="inlineStr"/>
+      <c r="F422" t="n">
+        <v>85</v>
+      </c>
       <c r="G422" t="n">
-        <v>85</v>
-      </c>
-      <c r="H422" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="423">
@@ -9740,11 +9310,10 @@
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr"/>
-      <c r="F423" t="inlineStr"/>
+      <c r="F423" t="n">
+        <v>48</v>
+      </c>
       <c r="G423" t="n">
-        <v>48</v>
-      </c>
-      <c r="H423" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9762,11 +9331,10 @@
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr"/>
+      <c r="F424" t="n">
+        <v>3</v>
+      </c>
       <c r="G424" t="n">
-        <v>3</v>
-      </c>
-      <c r="H424" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9784,12 +9352,11 @@
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr"/>
-      <c r="F425" t="inlineStr"/>
+      <c r="F425" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G425" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H425" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="426">
@@ -9806,12 +9373,11 @@
       <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr"/>
+      <c r="F426" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G426" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H426" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="427">
@@ -9828,12 +9394,11 @@
       <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr"/>
+      <c r="F427" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G427" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H427" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="428">
@@ -9850,12 +9415,11 @@
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr"/>
+      <c r="F428" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G428" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H428" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="429">
@@ -9872,12 +9436,11 @@
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr"/>
-      <c r="F429" t="inlineStr"/>
+      <c r="F429" t="n">
+        <v>24</v>
+      </c>
       <c r="G429" t="n">
-        <v>24</v>
-      </c>
-      <c r="H429" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="430">
@@ -9894,12 +9457,11 @@
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr"/>
-      <c r="F430" t="inlineStr"/>
+      <c r="F430" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G430" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H430" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="431">
@@ -9916,12 +9478,11 @@
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr"/>
-      <c r="F431" t="inlineStr"/>
+      <c r="F431" t="n">
+        <v>95</v>
+      </c>
       <c r="G431" t="n">
-        <v>95</v>
-      </c>
-      <c r="H431" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="432">
@@ -9938,11 +9499,10 @@
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr"/>
-      <c r="F432" t="inlineStr"/>
+      <c r="F432" t="n">
+        <v>125</v>
+      </c>
       <c r="G432" t="n">
-        <v>125</v>
-      </c>
-      <c r="H432" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9960,11 +9520,10 @@
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr"/>
-      <c r="F433" t="inlineStr"/>
+      <c r="F433" t="n">
+        <v>95</v>
+      </c>
       <c r="G433" t="n">
-        <v>95</v>
-      </c>
-      <c r="H433" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9982,12 +9541,11 @@
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
+      <c r="F434" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G434" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H434" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="435">
@@ -10004,11 +9562,10 @@
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr"/>
-      <c r="F435" t="inlineStr"/>
+      <c r="F435" t="n">
+        <v>350</v>
+      </c>
       <c r="G435" t="n">
-        <v>350</v>
-      </c>
-      <c r="H435" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10026,12 +9583,11 @@
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr"/>
-      <c r="F436" t="inlineStr"/>
+      <c r="F436" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G436" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H436" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="437">
@@ -10048,11 +9604,10 @@
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr"/>
-      <c r="F437" t="inlineStr"/>
+      <c r="F437" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G437" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H437" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10070,11 +9625,10 @@
       <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr"/>
       <c r="E438" t="inlineStr"/>
-      <c r="F438" t="inlineStr"/>
+      <c r="F438" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G438" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H438" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10092,12 +9646,11 @@
       <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr"/>
       <c r="E439" t="inlineStr"/>
-      <c r="F439" t="inlineStr"/>
+      <c r="F439" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G439" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H439" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="440">
@@ -10114,12 +9667,11 @@
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr"/>
       <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
+      <c r="F440" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G440" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H440" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="441">
@@ -10136,12 +9688,11 @@
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr"/>
       <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr"/>
+      <c r="F441" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G441" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H441" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="442">
@@ -10158,12 +9709,11 @@
       <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr"/>
       <c r="E442" t="inlineStr"/>
-      <c r="F442" t="inlineStr"/>
+      <c r="F442" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G442" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H442" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="443">
@@ -10180,11 +9730,10 @@
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr"/>
       <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr"/>
+      <c r="F443" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G443" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H443" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10202,12 +9751,11 @@
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr"/>
       <c r="E444" t="inlineStr"/>
-      <c r="F444" t="inlineStr"/>
+      <c r="F444" t="n">
+        <v>650</v>
+      </c>
       <c r="G444" t="n">
-        <v>650</v>
-      </c>
-      <c r="H444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445">
@@ -10224,12 +9772,11 @@
       <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr"/>
       <c r="E445" t="inlineStr"/>
-      <c r="F445" t="inlineStr"/>
+      <c r="F445" t="n">
+        <v>495</v>
+      </c>
       <c r="G445" t="n">
-        <v>495</v>
-      </c>
-      <c r="H445" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="446">
@@ -10246,11 +9793,10 @@
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr"/>
-      <c r="F446" t="inlineStr"/>
+      <c r="F446" t="n">
+        <v>495</v>
+      </c>
       <c r="G446" t="n">
-        <v>495</v>
-      </c>
-      <c r="H446" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10268,12 +9814,11 @@
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
-      <c r="F447" t="inlineStr"/>
+      <c r="F447" t="n">
+        <v>95</v>
+      </c>
       <c r="G447" t="n">
-        <v>95</v>
-      </c>
-      <c r="H447" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="448">
@@ -10290,12 +9835,11 @@
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr"/>
+      <c r="F448" t="n">
+        <v>90</v>
+      </c>
       <c r="G448" t="n">
-        <v>90</v>
-      </c>
-      <c r="H448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449">
@@ -10312,12 +9856,11 @@
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr"/>
-      <c r="F449" t="inlineStr"/>
+      <c r="F449" t="n">
+        <v>45</v>
+      </c>
       <c r="G449" t="n">
-        <v>45</v>
-      </c>
-      <c r="H449" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="450">
@@ -10334,12 +9877,11 @@
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr"/>
-      <c r="F450" t="inlineStr"/>
+      <c r="F450" t="n">
+        <v>295</v>
+      </c>
       <c r="G450" t="n">
-        <v>295</v>
-      </c>
-      <c r="H450" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
@@ -10356,12 +9898,11 @@
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
-      <c r="F451" t="inlineStr"/>
+      <c r="F451" t="n">
+        <v>24</v>
+      </c>
       <c r="G451" t="n">
-        <v>24</v>
-      </c>
-      <c r="H451" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="452">
@@ -10378,12 +9919,11 @@
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr"/>
-      <c r="F452" t="inlineStr"/>
+      <c r="F452" t="n">
+        <v>12</v>
+      </c>
       <c r="G452" t="n">
-        <v>12</v>
-      </c>
-      <c r="H452" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="453">
@@ -10400,12 +9940,11 @@
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr"/>
-      <c r="F453" t="inlineStr"/>
+      <c r="F453" t="n">
+        <v>16.5</v>
+      </c>
       <c r="G453" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H453" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="454">
@@ -10422,12 +9961,11 @@
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr"/>
-      <c r="F454" t="inlineStr"/>
+      <c r="F454" t="n">
+        <v>24</v>
+      </c>
       <c r="G454" t="n">
-        <v>24</v>
-      </c>
-      <c r="H454" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="455">
@@ -10444,12 +9982,11 @@
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr"/>
-      <c r="F455" t="inlineStr"/>
+      <c r="F455" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G455" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H455" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="456">
@@ -10466,12 +10003,11 @@
       <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr"/>
-      <c r="F456" t="inlineStr"/>
+      <c r="F456" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G456" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H456" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="457">
@@ -10488,12 +10024,11 @@
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr"/>
-      <c r="F457" t="inlineStr"/>
+      <c r="F457" t="n">
+        <v>18</v>
+      </c>
       <c r="G457" t="n">
-        <v>18</v>
-      </c>
-      <c r="H457" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="458">
@@ -10510,11 +10045,10 @@
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr"/>
-      <c r="F458" t="inlineStr"/>
+      <c r="F458" t="n">
+        <v>55</v>
+      </c>
       <c r="G458" t="n">
-        <v>55</v>
-      </c>
-      <c r="H458" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10532,12 +10066,11 @@
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
-      <c r="F459" t="inlineStr"/>
+      <c r="F459" t="n">
+        <v>18</v>
+      </c>
       <c r="G459" t="n">
-        <v>18</v>
-      </c>
-      <c r="H459" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="460">
@@ -10554,12 +10087,11 @@
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
-      <c r="F460" t="inlineStr"/>
+      <c r="F460" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G460" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H460" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="461">
@@ -10576,12 +10108,11 @@
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
-      <c r="F461" t="inlineStr"/>
+      <c r="F461" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G461" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H461" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="462">
@@ -10598,12 +10129,11 @@
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
-      <c r="F462" t="inlineStr"/>
+      <c r="F462" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G462" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H462" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="463">
@@ -10620,12 +10150,11 @@
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
-      <c r="F463" t="inlineStr"/>
+      <c r="F463" t="n">
+        <v>42</v>
+      </c>
       <c r="G463" t="n">
-        <v>42</v>
-      </c>
-      <c r="H463" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="464">
@@ -10642,12 +10171,11 @@
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
-      <c r="F464" t="inlineStr"/>
+      <c r="F464" t="n">
+        <v>48</v>
+      </c>
       <c r="G464" t="n">
-        <v>48</v>
-      </c>
-      <c r="H464" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="465">
@@ -10664,12 +10192,11 @@
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr"/>
-      <c r="F465" t="inlineStr"/>
+      <c r="F465" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G465" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H465" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="466">
@@ -10686,12 +10213,11 @@
       <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
-      <c r="F466" t="inlineStr"/>
+      <c r="F466" t="n">
+        <v>65</v>
+      </c>
       <c r="G466" t="n">
-        <v>65</v>
-      </c>
-      <c r="H466" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="467">
@@ -10708,12 +10234,11 @@
       <c r="C467" t="inlineStr"/>
       <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr"/>
-      <c r="F467" t="inlineStr"/>
+      <c r="F467" t="n">
+        <v>24</v>
+      </c>
       <c r="G467" t="n">
-        <v>24</v>
-      </c>
-      <c r="H467" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="468">
@@ -10730,12 +10255,11 @@
       <c r="C468" t="inlineStr"/>
       <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr"/>
-      <c r="F468" t="inlineStr"/>
+      <c r="F468" t="n">
+        <v>24</v>
+      </c>
       <c r="G468" t="n">
-        <v>24</v>
-      </c>
-      <c r="H468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469">
@@ -10752,12 +10276,11 @@
       <c r="C469" t="inlineStr"/>
       <c r="D469" t="inlineStr"/>
       <c r="E469" t="inlineStr"/>
-      <c r="F469" t="inlineStr"/>
+      <c r="F469" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G469" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H469" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="470">
@@ -10774,12 +10297,11 @@
       <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr"/>
-      <c r="F470" t="inlineStr"/>
+      <c r="F470" t="n">
+        <v>24</v>
+      </c>
       <c r="G470" t="n">
-        <v>24</v>
-      </c>
-      <c r="H470" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="471">
@@ -10796,12 +10318,11 @@
       <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr"/>
       <c r="E471" t="inlineStr"/>
-      <c r="F471" t="inlineStr"/>
+      <c r="F471" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G471" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H471" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="472">
@@ -10818,12 +10339,11 @@
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr"/>
-      <c r="F472" t="inlineStr"/>
+      <c r="F472" t="n">
+        <v>160</v>
+      </c>
       <c r="G472" t="n">
-        <v>160</v>
-      </c>
-      <c r="H472" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="473">
@@ -10840,12 +10360,11 @@
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr"/>
-      <c r="F473" t="inlineStr"/>
+      <c r="F473" t="n">
+        <v>595</v>
+      </c>
       <c r="G473" t="n">
-        <v>595</v>
-      </c>
-      <c r="H473" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
@@ -10862,12 +10381,11 @@
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr"/>
-      <c r="F474" t="inlineStr"/>
+      <c r="F474" t="n">
+        <v>70</v>
+      </c>
       <c r="G474" t="n">
-        <v>70</v>
-      </c>
-      <c r="H474" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="475">
@@ -10884,11 +10402,10 @@
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr"/>
-      <c r="F475" t="inlineStr"/>
+      <c r="F475" t="n">
+        <v>340</v>
+      </c>
       <c r="G475" t="n">
-        <v>340</v>
-      </c>
-      <c r="H475" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10906,11 +10423,10 @@
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr"/>
-      <c r="F476" t="inlineStr"/>
+      <c r="F476" t="n">
+        <v>165</v>
+      </c>
       <c r="G476" t="n">
-        <v>165</v>
-      </c>
-      <c r="H476" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10928,11 +10444,10 @@
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr"/>
-      <c r="F477" t="inlineStr"/>
+      <c r="F477" t="n">
+        <v>0</v>
+      </c>
       <c r="G477" t="n">
-        <v>0</v>
-      </c>
-      <c r="H477" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10950,12 +10465,11 @@
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr"/>
-      <c r="F478" t="inlineStr"/>
+      <c r="F478" t="n">
+        <v>65</v>
+      </c>
       <c r="G478" t="n">
-        <v>65</v>
-      </c>
-      <c r="H478" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="479">
@@ -10972,11 +10486,10 @@
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr"/>
-      <c r="F479" t="inlineStr"/>
+      <c r="F479" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G479" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H479" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10994,12 +10507,11 @@
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
-      <c r="F480" t="inlineStr"/>
+      <c r="F480" t="n">
+        <v>75</v>
+      </c>
       <c r="G480" t="n">
-        <v>75</v>
-      </c>
-      <c r="H480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481">
@@ -11016,11 +10528,10 @@
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr"/>
-      <c r="F481" t="inlineStr"/>
+      <c r="F481" t="n">
+        <v>75</v>
+      </c>
       <c r="G481" t="n">
-        <v>75</v>
-      </c>
-      <c r="H481" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11038,11 +10549,10 @@
       <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr"/>
-      <c r="F482" t="inlineStr"/>
+      <c r="F482" t="n">
+        <v>0</v>
+      </c>
       <c r="G482" t="n">
-        <v>0</v>
-      </c>
-      <c r="H482" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11060,11 +10570,10 @@
       <c r="C483" t="inlineStr"/>
       <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr"/>
-      <c r="F483" t="inlineStr"/>
+      <c r="F483" t="n">
+        <v>165</v>
+      </c>
       <c r="G483" t="n">
-        <v>165</v>
-      </c>
-      <c r="H483" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11082,11 +10591,10 @@
       <c r="C484" t="inlineStr"/>
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr"/>
-      <c r="F484" t="inlineStr"/>
+      <c r="F484" t="n">
+        <v>470</v>
+      </c>
       <c r="G484" t="n">
-        <v>470</v>
-      </c>
-      <c r="H484" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11104,12 +10612,11 @@
       <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr"/>
-      <c r="F485" t="inlineStr"/>
+      <c r="F485" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G485" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H485" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="486">
@@ -11126,12 +10633,11 @@
       <c r="C486" t="inlineStr"/>
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr"/>
-      <c r="F486" t="inlineStr"/>
+      <c r="F486" t="n">
+        <v>24</v>
+      </c>
       <c r="G486" t="n">
-        <v>24</v>
-      </c>
-      <c r="H486" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="487">
@@ -11148,12 +10654,11 @@
       <c r="C487" t="inlineStr"/>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr"/>
-      <c r="F487" t="inlineStr"/>
+      <c r="F487" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G487" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H487" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="488">
@@ -11170,12 +10675,11 @@
       <c r="C488" t="inlineStr"/>
       <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr"/>
-      <c r="F488" t="inlineStr"/>
+      <c r="F488" t="n">
+        <v>24</v>
+      </c>
       <c r="G488" t="n">
-        <v>24</v>
-      </c>
-      <c r="H488" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="489">
@@ -11192,12 +10696,11 @@
       <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr"/>
-      <c r="F489" t="inlineStr"/>
+      <c r="F489" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G489" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H489" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="490">
@@ -11214,12 +10717,11 @@
       <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
-      <c r="F490" t="inlineStr"/>
+      <c r="F490" t="n">
+        <v>55</v>
+      </c>
       <c r="G490" t="n">
-        <v>55</v>
-      </c>
-      <c r="H490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="491">
@@ -11236,12 +10738,11 @@
       <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
-      <c r="F491" t="inlineStr"/>
+      <c r="F491" t="n">
+        <v>225</v>
+      </c>
       <c r="G491" t="n">
-        <v>225</v>
-      </c>
-      <c r="H491" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="492">
@@ -11258,12 +10759,11 @@
       <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
-      <c r="F492" t="inlineStr"/>
+      <c r="F492" t="n">
+        <v>36</v>
+      </c>
       <c r="G492" t="n">
-        <v>36</v>
-      </c>
-      <c r="H492" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="493">
@@ -11280,12 +10780,11 @@
       <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
-      <c r="F493" t="inlineStr"/>
+      <c r="F493" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G493" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H493" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="494">
@@ -11302,12 +10801,11 @@
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
-      <c r="F494" t="inlineStr"/>
+      <c r="F494" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G494" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H494" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="495">
@@ -11324,12 +10822,11 @@
       <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
-      <c r="F495" t="inlineStr"/>
+      <c r="F495" t="n">
+        <v>145</v>
+      </c>
       <c r="G495" t="n">
-        <v>145</v>
-      </c>
-      <c r="H495" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="496">
@@ -11346,12 +10843,11 @@
       <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
-      <c r="F496" t="inlineStr"/>
+      <c r="F496" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G496" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H496" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="497">
@@ -11368,11 +10864,10 @@
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
-      <c r="F497" t="inlineStr"/>
+      <c r="F497" t="n">
+        <v>12.5</v>
+      </c>
       <c r="G497" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H497" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11384,21 +10879,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>DELIVERY</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>Pallet Mainland</t>
-        </is>
-      </c>
+          <t>DELIVERY - Pallet Mainland</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
-      <c r="F498" t="inlineStr"/>
+      <c r="F498" t="n">
+        <v>135</v>
+      </c>
       <c r="G498" t="n">
-        <v>135</v>
-      </c>
-      <c r="H498" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11416,11 +10906,10 @@
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr"/>
-      <c r="F499" t="inlineStr"/>
+      <c r="F499" t="n">
+        <v>0.8</v>
+      </c>
       <c r="G499" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H499" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11438,11 +10927,10 @@
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr"/>
-      <c r="F500" t="inlineStr"/>
+      <c r="F500" t="n">
+        <v>6</v>
+      </c>
       <c r="G500" t="n">
-        <v>6</v>
-      </c>
-      <c r="H500" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11460,12 +10948,11 @@
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr"/>
-      <c r="F501" t="inlineStr"/>
+      <c r="F501" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G501" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H501" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="502">
@@ -11482,11 +10969,10 @@
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
-      <c r="F502" t="inlineStr"/>
+      <c r="F502" t="n">
+        <v>7.5</v>
+      </c>
       <c r="G502" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H502" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11504,11 +10990,10 @@
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr"/>
-      <c r="F503" t="inlineStr"/>
+      <c r="F503" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G503" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H503" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11526,11 +11011,10 @@
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr"/>
-      <c r="F504" t="inlineStr"/>
+      <c r="F504" t="n">
+        <v>5</v>
+      </c>
       <c r="G504" t="n">
-        <v>5</v>
-      </c>
-      <c r="H504" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11542,21 +11026,16 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>DELIVERY</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>Trees Online</t>
-        </is>
-      </c>
+          <t>DELIVERY - Trees Online</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr"/>
-      <c r="F505" t="inlineStr"/>
+      <c r="F505" t="n">
+        <v>18</v>
+      </c>
       <c r="G505" t="n">
-        <v>18</v>
-      </c>
-      <c r="H505" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11574,12 +11053,11 @@
       <c r="C506" t="inlineStr"/>
       <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr"/>
-      <c r="F506" t="inlineStr"/>
+      <c r="F506" t="n">
+        <v>395</v>
+      </c>
       <c r="G506" t="n">
-        <v>395</v>
-      </c>
-      <c r="H506" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
@@ -11596,12 +11074,11 @@
       <c r="C507" t="inlineStr"/>
       <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr"/>
-      <c r="F507" t="inlineStr"/>
+      <c r="F507" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G507" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H507" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="508">
@@ -11618,12 +11095,11 @@
       <c r="C508" t="inlineStr"/>
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr"/>
-      <c r="F508" t="inlineStr"/>
+      <c r="F508" t="n">
+        <v>65</v>
+      </c>
       <c r="G508" t="n">
-        <v>65</v>
-      </c>
-      <c r="H508" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="509">
@@ -11640,12 +11116,11 @@
       <c r="C509" t="inlineStr"/>
       <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr"/>
-      <c r="F509" t="inlineStr"/>
+      <c r="F509" t="n">
+        <v>65</v>
+      </c>
       <c r="G509" t="n">
-        <v>65</v>
-      </c>
-      <c r="H509" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="510">
@@ -11662,12 +11137,11 @@
       <c r="C510" t="inlineStr"/>
       <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr"/>
-      <c r="F510" t="inlineStr"/>
+      <c r="F510" t="n">
+        <v>90</v>
+      </c>
       <c r="G510" t="n">
-        <v>90</v>
-      </c>
-      <c r="H510" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="511">
@@ -11684,12 +11158,11 @@
       <c r="C511" t="inlineStr"/>
       <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr"/>
-      <c r="F511" t="inlineStr"/>
+      <c r="F511" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G511" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H511" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="512">
@@ -11706,12 +11179,11 @@
       <c r="C512" t="inlineStr"/>
       <c r="D512" t="inlineStr"/>
       <c r="E512" t="inlineStr"/>
-      <c r="F512" t="inlineStr"/>
+      <c r="F512" t="n">
+        <v>85</v>
+      </c>
       <c r="G512" t="n">
-        <v>85</v>
-      </c>
-      <c r="H512" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="513">
@@ -11728,11 +11200,10 @@
       <c r="C513" t="inlineStr"/>
       <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr"/>
-      <c r="F513" t="inlineStr"/>
+      <c r="F513" t="n">
+        <v>195</v>
+      </c>
       <c r="G513" t="n">
-        <v>195</v>
-      </c>
-      <c r="H513" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11750,12 +11221,11 @@
       <c r="C514" t="inlineStr"/>
       <c r="D514" t="inlineStr"/>
       <c r="E514" t="inlineStr"/>
-      <c r="F514" t="inlineStr"/>
+      <c r="F514" t="n">
+        <v>45</v>
+      </c>
       <c r="G514" t="n">
-        <v>45</v>
-      </c>
-      <c r="H514" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="515">
@@ -11772,11 +11242,10 @@
       <c r="C515" t="inlineStr"/>
       <c r="D515" t="inlineStr"/>
       <c r="E515" t="inlineStr"/>
-      <c r="F515" t="inlineStr"/>
+      <c r="F515" t="n">
+        <v>525</v>
+      </c>
       <c r="G515" t="n">
-        <v>525</v>
-      </c>
-      <c r="H515" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11794,12 +11263,11 @@
       <c r="C516" t="inlineStr"/>
       <c r="D516" t="inlineStr"/>
       <c r="E516" t="inlineStr"/>
-      <c r="F516" t="inlineStr"/>
+      <c r="F516" t="n">
+        <v>95</v>
+      </c>
       <c r="G516" t="n">
-        <v>95</v>
-      </c>
-      <c r="H516" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517">
@@ -11816,12 +11284,11 @@
       <c r="C517" t="inlineStr"/>
       <c r="D517" t="inlineStr"/>
       <c r="E517" t="inlineStr"/>
-      <c r="F517" t="inlineStr"/>
+      <c r="F517" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G517" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H517" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="518">
@@ -11838,12 +11305,11 @@
       <c r="C518" t="inlineStr"/>
       <c r="D518" t="inlineStr"/>
       <c r="E518" t="inlineStr"/>
-      <c r="F518" t="inlineStr"/>
+      <c r="F518" t="n">
+        <v>650</v>
+      </c>
       <c r="G518" t="n">
-        <v>650</v>
-      </c>
-      <c r="H518" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="519">
@@ -11860,12 +11326,11 @@
       <c r="C519" t="inlineStr"/>
       <c r="D519" t="inlineStr"/>
       <c r="E519" t="inlineStr"/>
-      <c r="F519" t="inlineStr"/>
+      <c r="F519" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G519" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H519" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="520">
@@ -11882,12 +11347,11 @@
       <c r="C520" t="inlineStr"/>
       <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr"/>
-      <c r="F520" t="inlineStr"/>
+      <c r="F520" t="n">
+        <v>650</v>
+      </c>
       <c r="G520" t="n">
-        <v>650</v>
-      </c>
-      <c r="H520" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="521">
@@ -11904,12 +11368,11 @@
       <c r="C521" t="inlineStr"/>
       <c r="D521" t="inlineStr"/>
       <c r="E521" t="inlineStr"/>
-      <c r="F521" t="inlineStr"/>
+      <c r="F521" t="n">
+        <v>48</v>
+      </c>
       <c r="G521" t="n">
-        <v>48</v>
-      </c>
-      <c r="H521" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="522">
@@ -11926,11 +11389,10 @@
       <c r="C522" t="inlineStr"/>
       <c r="D522" t="inlineStr"/>
       <c r="E522" t="inlineStr"/>
-      <c r="F522" t="inlineStr"/>
+      <c r="F522" t="n">
+        <v>295</v>
+      </c>
       <c r="G522" t="n">
-        <v>295</v>
-      </c>
-      <c r="H522" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11948,11 +11410,10 @@
       <c r="C523" t="inlineStr"/>
       <c r="D523" t="inlineStr"/>
       <c r="E523" t="inlineStr"/>
-      <c r="F523" t="inlineStr"/>
+      <c r="F523" t="n">
+        <v>525</v>
+      </c>
       <c r="G523" t="n">
-        <v>525</v>
-      </c>
-      <c r="H523" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11970,12 +11431,11 @@
       <c r="C524" t="inlineStr"/>
       <c r="D524" t="inlineStr"/>
       <c r="E524" t="inlineStr"/>
-      <c r="F524" t="inlineStr"/>
+      <c r="F524" t="n">
+        <v>45</v>
+      </c>
       <c r="G524" t="n">
-        <v>45</v>
-      </c>
-      <c r="H524" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="525">
@@ -11992,12 +11452,11 @@
       <c r="C525" t="inlineStr"/>
       <c r="D525" t="inlineStr"/>
       <c r="E525" t="inlineStr"/>
-      <c r="F525" t="inlineStr"/>
+      <c r="F525" t="n">
+        <v>225</v>
+      </c>
       <c r="G525" t="n">
-        <v>225</v>
-      </c>
-      <c r="H525" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="526">
@@ -12014,12 +11473,11 @@
       <c r="C526" t="inlineStr"/>
       <c r="D526" t="inlineStr"/>
       <c r="E526" t="inlineStr"/>
-      <c r="F526" t="inlineStr"/>
+      <c r="F526" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G526" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H526" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="527">
@@ -12036,12 +11494,11 @@
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr"/>
-      <c r="F527" t="inlineStr"/>
+      <c r="F527" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G527" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H527" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="528">
@@ -12058,12 +11515,11 @@
       <c r="C528" t="inlineStr"/>
       <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr"/>
-      <c r="F528" t="inlineStr"/>
+      <c r="F528" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G528" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H528" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="529">
@@ -12080,12 +11536,11 @@
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr"/>
-      <c r="F529" t="inlineStr"/>
+      <c r="F529" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G529" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H529" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="530">
@@ -12102,12 +11557,11 @@
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
-      <c r="F530" t="inlineStr"/>
+      <c r="F530" t="n">
+        <v>65</v>
+      </c>
       <c r="G530" t="n">
-        <v>65</v>
-      </c>
-      <c r="H530" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="531">
@@ -12124,12 +11578,11 @@
       <c r="C531" t="inlineStr"/>
       <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr"/>
-      <c r="F531" t="inlineStr"/>
+      <c r="F531" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G531" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H531" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
     </row>
     <row r="532">
@@ -12146,12 +11599,11 @@
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr"/>
-      <c r="F532" t="inlineStr"/>
+      <c r="F532" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G532" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H532" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="533">
@@ -12168,12 +11620,11 @@
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr"/>
-      <c r="F533" t="inlineStr"/>
+      <c r="F533" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G533" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H533" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="534">
@@ -12190,12 +11641,11 @@
       <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr"/>
       <c r="E534" t="inlineStr"/>
-      <c r="F534" t="inlineStr"/>
+      <c r="F534" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G534" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H534" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="535">
@@ -12212,11 +11662,10 @@
       <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr"/>
-      <c r="F535" t="inlineStr"/>
+      <c r="F535" t="n">
+        <v>425</v>
+      </c>
       <c r="G535" t="n">
-        <v>425</v>
-      </c>
-      <c r="H535" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12234,12 +11683,11 @@
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
-      <c r="F536" t="inlineStr"/>
+      <c r="F536" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G536" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H536" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="537">
@@ -12256,12 +11704,11 @@
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr"/>
+      <c r="F537" t="n">
+        <v>285</v>
+      </c>
       <c r="G537" t="n">
-        <v>285</v>
-      </c>
-      <c r="H537" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="538">
@@ -12278,12 +11725,11 @@
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr"/>
-      <c r="F538" t="inlineStr"/>
+      <c r="F538" t="n">
+        <v>65</v>
+      </c>
       <c r="G538" t="n">
-        <v>65</v>
-      </c>
-      <c r="H538" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="539">
@@ -12300,12 +11746,11 @@
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
       <c r="E539" t="inlineStr"/>
-      <c r="F539" t="inlineStr"/>
+      <c r="F539" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G539" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H539" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="540">
@@ -12322,12 +11767,11 @@
       <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr"/>
-      <c r="F540" t="inlineStr"/>
+      <c r="F540" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G540" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H540" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="541">
@@ -12344,12 +11788,11 @@
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr"/>
-      <c r="F541" t="inlineStr"/>
+      <c r="F541" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G541" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H541" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="542">
@@ -12366,12 +11809,11 @@
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr"/>
-      <c r="F542" t="inlineStr"/>
+      <c r="F542" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G542" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H542" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="543">
@@ -12388,12 +11830,11 @@
       <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr"/>
-      <c r="F543" t="inlineStr"/>
+      <c r="F543" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G543" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H543" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="544">
@@ -12410,12 +11851,11 @@
       <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr"/>
+      <c r="F544" t="n">
+        <v>24</v>
+      </c>
       <c r="G544" t="n">
-        <v>24</v>
-      </c>
-      <c r="H544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="545">
@@ -12432,11 +11872,10 @@
       <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr"/>
-      <c r="F545" t="inlineStr"/>
+      <c r="F545" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G545" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H545" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12454,12 +11893,11 @@
       <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr"/>
-      <c r="F546" t="inlineStr"/>
+      <c r="F546" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G546" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H546" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="547">
@@ -12476,11 +11914,10 @@
       <c r="C547" t="inlineStr"/>
       <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr"/>
-      <c r="F547" t="inlineStr"/>
+      <c r="F547" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G547" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H547" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12498,12 +11935,11 @@
       <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr"/>
-      <c r="F548" t="inlineStr"/>
+      <c r="F548" t="n">
+        <v>31.5</v>
+      </c>
       <c r="G548" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H548" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="549">
@@ -12520,11 +11956,10 @@
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr"/>
       <c r="E549" t="inlineStr"/>
-      <c r="F549" t="inlineStr"/>
+      <c r="F549" t="n">
+        <v>0</v>
+      </c>
       <c r="G549" t="n">
-        <v>0</v>
-      </c>
-      <c r="H549" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12542,12 +11977,11 @@
       <c r="C550" t="inlineStr"/>
       <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr"/>
-      <c r="F550" t="inlineStr"/>
+      <c r="F550" t="n">
+        <v>75</v>
+      </c>
       <c r="G550" t="n">
-        <v>75</v>
-      </c>
-      <c r="H550" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="551">
@@ -12564,12 +11998,11 @@
       <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr"/>
       <c r="E551" t="inlineStr"/>
-      <c r="F551" t="inlineStr"/>
+      <c r="F551" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G551" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H551" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="552">
@@ -12586,11 +12019,10 @@
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr"/>
-      <c r="F552" t="inlineStr"/>
+      <c r="F552" t="n">
+        <v>115</v>
+      </c>
       <c r="G552" t="n">
-        <v>115</v>
-      </c>
-      <c r="H552" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12608,11 +12040,10 @@
       <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr"/>
-      <c r="F553" t="inlineStr"/>
+      <c r="F553" t="n">
+        <v>285</v>
+      </c>
       <c r="G553" t="n">
-        <v>285</v>
-      </c>
-      <c r="H553" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12630,12 +12061,11 @@
       <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr"/>
-      <c r="F554" t="inlineStr"/>
+      <c r="F554" t="n">
+        <v>28.5</v>
+      </c>
       <c r="G554" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H554" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="555">
@@ -12652,12 +12082,11 @@
       <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr"/>
       <c r="E555" t="inlineStr"/>
-      <c r="F555" t="inlineStr"/>
+      <c r="F555" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G555" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H555" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="556">
@@ -12674,11 +12103,10 @@
       <c r="C556" t="inlineStr"/>
       <c r="D556" t="inlineStr"/>
       <c r="E556" t="inlineStr"/>
-      <c r="F556" t="inlineStr"/>
+      <c r="F556" t="n">
+        <v>37.5</v>
+      </c>
       <c r="G556" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H556" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12696,12 +12124,11 @@
       <c r="C557" t="inlineStr"/>
       <c r="D557" t="inlineStr"/>
       <c r="E557" t="inlineStr"/>
-      <c r="F557" t="inlineStr"/>
+      <c r="F557" t="n">
+        <v>45</v>
+      </c>
       <c r="G557" t="n">
-        <v>45</v>
-      </c>
-      <c r="H557" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="558">
@@ -12718,12 +12145,11 @@
       <c r="C558" t="inlineStr"/>
       <c r="D558" t="inlineStr"/>
       <c r="E558" t="inlineStr"/>
-      <c r="F558" t="inlineStr"/>
+      <c r="F558" t="n">
+        <v>70</v>
+      </c>
       <c r="G558" t="n">
-        <v>70</v>
-      </c>
-      <c r="H558" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="559">
@@ -12740,12 +12166,11 @@
       <c r="C559" t="inlineStr"/>
       <c r="D559" t="inlineStr"/>
       <c r="E559" t="inlineStr"/>
-      <c r="F559" t="inlineStr"/>
+      <c r="F559" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G559" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H559" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="560">
@@ -12762,11 +12187,10 @@
       <c r="C560" t="inlineStr"/>
       <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr"/>
-      <c r="F560" t="inlineStr"/>
+      <c r="F560" t="n">
+        <v>60</v>
+      </c>
       <c r="G560" t="n">
-        <v>60</v>
-      </c>
-      <c r="H560" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12784,12 +12208,11 @@
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr"/>
-      <c r="F561" t="inlineStr"/>
+      <c r="F561" t="n">
+        <v>60</v>
+      </c>
       <c r="G561" t="n">
-        <v>60</v>
-      </c>
-      <c r="H561" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="562">
@@ -12806,12 +12229,11 @@
       <c r="C562" t="inlineStr"/>
       <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr"/>
-      <c r="F562" t="inlineStr"/>
+      <c r="F562" t="n">
+        <v>75</v>
+      </c>
       <c r="G562" t="n">
-        <v>75</v>
-      </c>
-      <c r="H562" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="563">
@@ -12828,11 +12250,10 @@
       <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr"/>
-      <c r="F563" t="inlineStr"/>
+      <c r="F563" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G563" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H563" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12850,11 +12271,10 @@
       <c r="C564" t="inlineStr"/>
       <c r="D564" t="inlineStr"/>
       <c r="E564" t="inlineStr"/>
-      <c r="F564" t="inlineStr"/>
+      <c r="F564" t="n">
+        <v>21.5</v>
+      </c>
       <c r="G564" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H564" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12872,11 +12292,10 @@
       <c r="C565" t="inlineStr"/>
       <c r="D565" t="inlineStr"/>
       <c r="E565" t="inlineStr"/>
-      <c r="F565" t="inlineStr"/>
+      <c r="F565" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G565" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H565" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12894,11 +12313,10 @@
       <c r="C566" t="inlineStr"/>
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr"/>
-      <c r="F566" t="inlineStr"/>
+      <c r="F566" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G566" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H566" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12916,11 +12334,10 @@
       <c r="C567" t="inlineStr"/>
       <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr"/>
-      <c r="F567" t="inlineStr"/>
+      <c r="F567" t="n">
+        <v>17.5</v>
+      </c>
       <c r="G567" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H567" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12932,21 +12349,16 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>DELIVERY</t>
-        </is>
-      </c>
-      <c r="C568" t="inlineStr">
-        <is>
-          <t>Pallet ROI</t>
-        </is>
-      </c>
+          <t>DELIVERY - Pallet ROI</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr"/>
       <c r="D568" t="inlineStr"/>
       <c r="E568" t="inlineStr"/>
-      <c r="F568" t="inlineStr"/>
+      <c r="F568" t="n">
+        <v>92</v>
+      </c>
       <c r="G568" t="n">
-        <v>92</v>
-      </c>
-      <c r="H568" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12958,21 +12370,16 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>DELIVERY</t>
-        </is>
-      </c>
-      <c r="C569" t="inlineStr">
-        <is>
-          <t>Pallet NI</t>
-        </is>
-      </c>
+          <t>DELIVERY - Pallet NI</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr"/>
       <c r="D569" t="inlineStr"/>
       <c r="E569" t="inlineStr"/>
-      <c r="F569" t="inlineStr"/>
+      <c r="F569" t="n">
+        <v>54</v>
+      </c>
       <c r="G569" t="n">
-        <v>54</v>
-      </c>
-      <c r="H569" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12990,11 +12397,10 @@
       <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr"/>
       <c r="E570" t="inlineStr"/>
-      <c r="F570" t="inlineStr"/>
+      <c r="F570" t="n">
+        <v>70</v>
+      </c>
       <c r="G570" t="n">
-        <v>70</v>
-      </c>
-      <c r="H570" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13012,11 +12418,10 @@
       <c r="C571" t="inlineStr"/>
       <c r="D571" t="inlineStr"/>
       <c r="E571" t="inlineStr"/>
-      <c r="F571" t="inlineStr"/>
+      <c r="F571" t="n">
+        <v>42</v>
+      </c>
       <c r="G571" t="n">
-        <v>42</v>
-      </c>
-      <c r="H571" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13034,11 +12439,10 @@
       <c r="C572" t="inlineStr"/>
       <c r="D572" t="inlineStr"/>
       <c r="E572" t="inlineStr"/>
-      <c r="F572" t="inlineStr"/>
+      <c r="F572" t="n">
+        <v>30</v>
+      </c>
       <c r="G572" t="n">
-        <v>30</v>
-      </c>
-      <c r="H572" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13056,11 +12460,10 @@
       <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr"/>
-      <c r="F573" t="inlineStr"/>
+      <c r="F573" t="n">
+        <v>18</v>
+      </c>
       <c r="G573" t="n">
-        <v>18</v>
-      </c>
-      <c r="H573" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13074,11 +12477,10 @@
       <c r="C574" t="inlineStr"/>
       <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr"/>
-      <c r="F574" t="inlineStr"/>
+      <c r="F574" t="n">
+        <v>5</v>
+      </c>
       <c r="G574" t="n">
-        <v>5</v>
-      </c>
-      <c r="H574" t="n">
         <v>0</v>
       </c>
     </row>
